--- a/GEV_Model.xlsx
+++ b/GEV_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Industrial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3FF8B6-0338-45E4-A131-D4190D0A58D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA5DFA4-8F72-4870-BF93-28C796BF0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1893,9 +1893,6 @@
     <t xml:space="preserve">Financial Stmts. Notes/Observations </t>
   </si>
   <si>
-    <t>11/5/2025</t>
-  </si>
-  <si>
     <t>Q3'25</t>
   </si>
   <si>
@@ -1954,6 +1951,9 @@
   </si>
   <si>
     <t>Electrification Software</t>
+  </si>
+  <si>
+    <t>12/29/25</t>
   </si>
 </sst>
 </file>
@@ -2473,11 +2473,11 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -10439,10 +10439,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="73">
-        <v>552.5</v>
+        <v>663.16</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4" spans="2:18">
@@ -10453,7 +10453,7 @@
         <v>271.32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="2:18">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="C5" s="72">
         <f>C3*C4</f>
-        <v>149904.29999999999</v>
+        <v>179928.57119999998</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -10473,7 +10473,7 @@
         <v>7945</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C8" s="72">
         <f>C5-C6+C7</f>
-        <v>141959.29999999999</v>
+        <v>171983.57119999998</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15">
@@ -10728,6 +10728,9 @@
     <hyperlink ref="Q13" r:id="rId3" xr:uid="{F5D8B61A-D6AC-4492-A18C-0BC09C1A4F05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D3" twoDigitTextYear="1"/>
+  </ignoredErrors>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
@@ -11953,7 +11956,7 @@
     </row>
     <row r="15" spans="2:91">
       <c r="B15" s="62" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C15" s="1">
         <v>2882</v>
@@ -12004,7 +12007,7 @@
     </row>
     <row r="16" spans="2:91">
       <c r="B16" s="62" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C16" s="1">
         <v>221</v>
@@ -12055,7 +12058,7 @@
     </row>
     <row r="17" spans="2:90">
       <c r="B17" s="62" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C17" s="1">
         <v>178</v>
@@ -12106,7 +12109,7 @@
     </row>
     <row r="18" spans="2:90">
       <c r="B18" s="62" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C18" s="1">
         <v>540</v>
@@ -12156,8 +12159,8 @@
       </c>
     </row>
     <row r="19" spans="2:90" ht="15">
-      <c r="B19" s="75" t="s">
-        <v>591</v>
+      <c r="B19" s="74" t="s">
+        <v>590</v>
       </c>
       <c r="C19" s="2">
         <f t="shared" ref="C19:L19" si="24">SUM(C15:C18)</f>
@@ -12262,7 +12265,7 @@
     </row>
     <row r="20" spans="2:90">
       <c r="B20" s="62" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C20" s="1">
         <v>1422</v>
@@ -12324,7 +12327,7 @@
     </row>
     <row r="21" spans="2:90">
       <c r="B21" s="62" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C21" s="1">
         <v>249</v>
@@ -12386,7 +12389,7 @@
     </row>
     <row r="22" spans="2:90">
       <c r="B22" s="62" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C22" s="1">
         <v>80</v>
@@ -12447,8 +12450,8 @@
       <c r="AL22" s="70"/>
     </row>
     <row r="23" spans="2:90" ht="15">
-      <c r="B23" s="75" t="s">
-        <v>592</v>
+      <c r="B23" s="74" t="s">
+        <v>591</v>
       </c>
       <c r="C23" s="2">
         <f t="shared" ref="C23:L23" si="28">SUM(C20:C22)</f>
@@ -12553,7 +12556,7 @@
     </row>
     <row r="24" spans="2:90">
       <c r="B24" s="62" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C24" s="1">
         <v>835</v>
@@ -12615,7 +12618,7 @@
     </row>
     <row r="25" spans="2:90">
       <c r="B25" s="62" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C25" s="1">
         <f>183+95</f>
@@ -12681,7 +12684,7 @@
     </row>
     <row r="26" spans="2:90">
       <c r="B26" s="62" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C26" s="1">
         <v>218</v>
@@ -12742,8 +12745,8 @@
       <c r="AL26" s="70"/>
     </row>
     <row r="27" spans="2:90" ht="15">
-      <c r="B27" s="75" t="s">
-        <v>593</v>
+      <c r="B27" s="74" t="s">
+        <v>592</v>
       </c>
       <c r="C27" s="2">
         <f t="shared" ref="C27:L27" si="32">SUM(C24:C26)</f>
@@ -12863,7 +12866,7 @@
         <v>8252</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" ref="C28:L28" si="34">F27+F23+F19</f>
+        <f t="shared" ref="F28" si="34">F27+F23+F19</f>
         <v>10103</v>
       </c>
       <c r="G28" s="2">
@@ -13010,38 +13013,38 @@
     </row>
     <row r="30" spans="2:90">
       <c r="B30" s="62" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C30" s="63"/>
       <c r="D30" s="63"/>
       <c r="E30" s="63"/>
       <c r="F30" s="63"/>
       <c r="G30" s="63">
-        <f>G19/C19-1</f>
+        <f t="shared" ref="G30:M30" si="36">G19/C19-1</f>
         <v>5.6006281078251785E-2</v>
       </c>
       <c r="H30" s="63">
-        <f>H19/D19-1</f>
+        <f t="shared" si="36"/>
         <v>7.8431372549019551E-2</v>
       </c>
       <c r="I30" s="63">
-        <f>I19/E19-1</f>
+        <f t="shared" si="36"/>
         <v>8.0657590547135838E-2</v>
       </c>
       <c r="J30" s="63">
-        <f>J19/F19-1</f>
+        <f t="shared" si="36"/>
         <v>-2.8617420854945452E-2</v>
       </c>
       <c r="K30" s="63">
-        <f>K19/G19-1</f>
+        <f t="shared" si="36"/>
         <v>9.6158612143742328E-2</v>
       </c>
       <c r="L30" s="63">
-        <f>L19/H19-1</f>
+        <f t="shared" si="36"/>
         <v>6.8013468013468081E-2</v>
       </c>
       <c r="M30" s="63">
-        <f>M19/I19-1</f>
+        <f t="shared" si="36"/>
         <v>0.1502258141193249</v>
       </c>
       <c r="Y30" s="63"/>
@@ -13089,38 +13092,38 @@
     </row>
     <row r="31" spans="2:90">
       <c r="B31" s="62" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C31" s="63"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
       <c r="F31" s="63"/>
       <c r="G31" s="63">
-        <f>G23/C23-1</f>
+        <f t="shared" ref="G31:M31" si="37">G23/C23-1</f>
         <v>-6.3963449457452914E-2</v>
       </c>
       <c r="H31" s="63">
-        <f>H23/D23-1</f>
+        <f t="shared" si="37"/>
         <v>-0.2072279892349097</v>
       </c>
       <c r="I31" s="63">
-        <f>I23/E23-1</f>
+        <f t="shared" si="37"/>
         <v>1.3855213023901136E-3</v>
       </c>
       <c r="J31" s="63">
-        <f>J23/F23-1</f>
+        <f t="shared" si="37"/>
         <v>0.20139157325086976</v>
       </c>
       <c r="K31" s="63">
-        <f>K23/G23-1</f>
+        <f t="shared" si="37"/>
         <v>0.12873703477730314</v>
       </c>
       <c r="L31" s="63">
-        <f>L23/H23-1</f>
+        <f t="shared" si="37"/>
         <v>8.8748787584869149E-2</v>
       </c>
       <c r="M31" s="63">
-        <f>M23/I23-1</f>
+        <f t="shared" si="37"/>
         <v>-8.4053960567277763E-2</v>
       </c>
       <c r="Y31" s="63"/>
@@ -13168,47 +13171,47 @@
     </row>
     <row r="32" spans="2:90">
       <c r="B32" s="62" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C32" s="63"/>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
       <c r="F32" s="63"/>
       <c r="G32" s="63">
-        <f t="shared" ref="G32:G33" si="36">G27/C27-1</f>
+        <f t="shared" ref="G32:G33" si="38">G27/C27-1</f>
         <v>0.24042073628850491</v>
       </c>
       <c r="H32" s="63">
-        <f t="shared" ref="H32:H33" si="37">H27/D27-1</f>
+        <f t="shared" ref="H32:H33" si="39">H27/D27-1</f>
         <v>0.19003322259136213</v>
       </c>
       <c r="I32" s="63">
-        <f t="shared" ref="I32:I33" si="38">I27/E27-1</f>
+        <f t="shared" ref="I32:I33" si="40">I27/E27-1</f>
         <v>0.22257450856055794</v>
       </c>
       <c r="J32" s="63">
-        <f t="shared" ref="J32:J33" si="39">J27/F27-1</f>
+        <f t="shared" ref="J32:J33" si="41">J27/F27-1</f>
         <v>0.1324675324675324</v>
       </c>
       <c r="K32" s="63">
-        <f t="shared" ref="K32:K33" si="40">K27/G27-1</f>
+        <f t="shared" ref="K32:K33" si="42">K27/G27-1</f>
         <v>0.13870381586917024</v>
       </c>
       <c r="L32" s="63">
-        <f t="shared" ref="L32:L33" si="41">L27/H27-1</f>
+        <f t="shared" ref="L32:L33" si="43">L27/H27-1</f>
         <v>0.22892238972640988</v>
       </c>
       <c r="M32" s="63">
-        <f t="shared" ref="M32" si="42">M27/I27-1</f>
+        <f t="shared" ref="M32" si="44">M27/I27-1</f>
         <v>0.34958506224066399</v>
       </c>
       <c r="Y32" s="63"/>
       <c r="Z32" s="63">
-        <f t="shared" ref="Z32:AA33" si="43">Z27/Y27-1</f>
+        <f t="shared" ref="Z32:AA33" si="45">Z27/Y27-1</f>
         <v>0.2486209613869188</v>
       </c>
       <c r="AA32" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.19122751656674031</v>
       </c>
       <c r="AB32" s="65">
@@ -13254,27 +13257,27 @@
       <c r="E33" s="64"/>
       <c r="F33" s="64"/>
       <c r="G33" s="64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.4057461155086592E-2</v>
       </c>
       <c r="H33" s="64">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>1.0469269614484578E-2</v>
       </c>
       <c r="I33" s="64">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>8.010179350460489E-2</v>
       </c>
       <c r="J33" s="64">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>4.5135108383648426E-2</v>
       </c>
       <c r="K33" s="64">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.10648849703815944</v>
       </c>
       <c r="L33" s="64">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.11055582642613349</v>
       </c>
       <c r="M33" s="64">
@@ -13288,11 +13291,11 @@
       <c r="R33" s="34"/>
       <c r="Y33" s="64"/>
       <c r="Z33" s="64">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.12281648344236862</v>
       </c>
       <c r="AA33" s="64">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>4.9225132148005724E-2</v>
       </c>
       <c r="AB33" s="66">
@@ -13300,43 +13303,43 @@
         <v>9.8180907399455952E-2</v>
       </c>
       <c r="AC33" s="66">
-        <f t="shared" ref="AC33:AL33" si="44">AC28/AB28-1</f>
+        <f t="shared" ref="AC33:AL33" si="46">AC28/AB28-1</f>
         <v>0.14722812098021776</v>
       </c>
       <c r="AD33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.1588927229339816</v>
       </c>
       <c r="AE33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.16029880321459977</v>
       </c>
       <c r="AF33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.15288463177441813</v>
       </c>
       <c r="AG33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.13935777351696443</v>
       </c>
       <c r="AH33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.10671444130183216</v>
       </c>
       <c r="AI33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>7.4174308925179622E-2</v>
       </c>
       <c r="AJ33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>5.5453448604443567E-2</v>
       </c>
       <c r="AK33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4.0194526106577699E-2</v>
       </c>
       <c r="AL33" s="66">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>2.9840746147842934E-2</v>
       </c>
       <c r="AM33" s="34"/>
@@ -13410,46 +13413,46 @@
     </row>
     <row r="35" spans="2:90">
       <c r="B35" s="62" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C35" s="63">
-        <f t="shared" ref="C35:L35" si="45">C19/C28</f>
+        <f t="shared" ref="C35:L35" si="47">C19/C28</f>
         <v>0.56009967751392553</v>
       </c>
       <c r="D35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.50880650326394872</v>
       </c>
       <c r="E35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.47176442074648572</v>
       </c>
       <c r="F35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.5533999802038998</v>
       </c>
       <c r="G35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.55586168893787025</v>
       </c>
       <c r="H35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.54302779132130663</v>
       </c>
       <c r="I35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.4720071805228318</v>
       </c>
       <c r="J35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.51434794961644092</v>
       </c>
       <c r="K35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.55067231075697209</v>
       </c>
       <c r="L35" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.52222588080342447</v>
       </c>
       <c r="M35" s="63">
@@ -13457,11 +13460,11 @@
         <v>0.48540475473969302</v>
       </c>
       <c r="Y35" s="63">
-        <f t="shared" ref="Y35:Z35" si="46">Y19/Y28</f>
+        <f t="shared" ref="Y35:Z35" si="48">Y19/Y28</f>
         <v>0.54373777567950365</v>
       </c>
       <c r="Z35" s="63">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.52366650648726576</v>
       </c>
       <c r="AA35" s="63">
@@ -13471,46 +13474,46 @@
     </row>
     <row r="36" spans="2:90">
       <c r="B36" s="62" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C36" s="63">
-        <f t="shared" ref="C36:L36" si="47">C23/C28</f>
+        <f t="shared" ref="C36:L36" si="49">C23/C28</f>
         <v>0.2566695983582527</v>
       </c>
       <c r="D36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.32035965020322699</v>
       </c>
       <c r="E36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.3498545807077072</v>
       </c>
       <c r="F36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.25606255567653174</v>
       </c>
       <c r="G36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.22578867612618819</v>
       </c>
       <c r="H36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.25134080936128717</v>
       </c>
       <c r="I36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.32435767979355995</v>
       </c>
       <c r="J36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.29434605549767973</v>
       </c>
       <c r="K36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.23032868525896413</v>
       </c>
       <c r="L36" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.24640544396882888</v>
       </c>
       <c r="M36" s="63">
@@ -13518,11 +13521,11 @@
         <v>0.26562343264118771</v>
       </c>
       <c r="Y36" s="63">
-        <f t="shared" ref="Y36:Z36" si="48">Y23/Y28</f>
+        <f t="shared" ref="Y36:Z36" si="50">Y23/Y28</f>
         <v>0.30029675591825722</v>
       </c>
       <c r="Z36" s="63">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.29511052378664104</v>
       </c>
       <c r="AA36" s="63">
@@ -13532,46 +13535,46 @@
     </row>
     <row r="37" spans="2:90">
       <c r="B37" s="62" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C37" s="63">
-        <f t="shared" ref="C37:L37" si="49">C27/C28</f>
+        <f t="shared" ref="C37:L37" si="51">C27/C28</f>
         <v>0.19510407505130462</v>
       </c>
       <c r="D37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.18536765611528513</v>
       </c>
       <c r="E37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.19110518662142512</v>
       </c>
       <c r="F37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.19053746411956846</v>
       </c>
       <c r="G37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.22744179639068743</v>
       </c>
       <c r="H37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.21830814236957582</v>
       </c>
       <c r="I37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.2163132503085381</v>
       </c>
       <c r="J37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.20645894497584999</v>
       </c>
       <c r="K37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.23406374501992031</v>
       </c>
       <c r="L37" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0.24157611678191199</v>
       </c>
       <c r="M37" s="63">
@@ -13579,11 +13582,11 @@
         <v>0.26100912829772294</v>
       </c>
       <c r="Y37" s="63">
-        <f t="shared" ref="Y37:Z37" si="50">Y27/Y28</f>
+        <f t="shared" ref="Y37:Z37" si="52">Y27/Y28</f>
         <v>0.17117420921292237</v>
       </c>
       <c r="Z37" s="63">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0.19035319557904853</v>
       </c>
       <c r="AA37" s="63">
@@ -13596,47 +13599,47 @@
         <v>545</v>
       </c>
       <c r="C39" s="1">
-        <f>C4</f>
+        <f t="shared" ref="C39:M39" si="53">C4</f>
         <v>3489</v>
       </c>
       <c r="D39" s="1">
-        <f>D4</f>
+        <f t="shared" si="53"/>
         <v>4388</v>
       </c>
       <c r="E39" s="1">
-        <f>E4</f>
+        <f t="shared" si="53"/>
         <v>4869</v>
       </c>
       <c r="F39" s="1">
-        <f>F4</f>
+        <f t="shared" si="53"/>
         <v>5512</v>
       </c>
       <c r="G39" s="1">
-        <f>G4</f>
+        <f t="shared" si="53"/>
         <v>3617</v>
       </c>
       <c r="H39" s="1">
-        <f>H4</f>
+        <f t="shared" si="53"/>
         <v>4194</v>
       </c>
       <c r="I39" s="1">
-        <f>I4</f>
+        <f t="shared" si="53"/>
         <v>5290</v>
       </c>
       <c r="J39" s="1">
-        <f>J4</f>
+        <f t="shared" si="53"/>
         <v>5851</v>
       </c>
       <c r="K39" s="1">
-        <f>K4</f>
+        <f t="shared" si="53"/>
         <v>4197</v>
       </c>
       <c r="L39" s="1">
-        <f>L4</f>
+        <f t="shared" si="53"/>
         <v>4894</v>
       </c>
       <c r="M39" s="1">
-        <f>M4</f>
+        <f t="shared" si="53"/>
         <v>5880</v>
       </c>
       <c r="Y39" s="1">
@@ -13644,55 +13647,55 @@
         <v>15819</v>
       </c>
       <c r="Z39" s="1">
-        <f t="shared" ref="Z39:Z56" si="51">SUM(C39:F39)</f>
+        <f t="shared" ref="Z39:Z56" si="54">SUM(C39:F39)</f>
         <v>18258</v>
       </c>
       <c r="AA39" s="1">
-        <f t="shared" ref="AA39:AA45" si="52">SUM(G39:J39)</f>
+        <f t="shared" ref="AA39:AA45" si="55">SUM(G39:J39)</f>
         <v>18952</v>
       </c>
       <c r="AB39" s="70">
-        <f>AB4</f>
+        <f t="shared" ref="AB39:AL39" si="56">AB4</f>
         <v>21557.899999999998</v>
       </c>
       <c r="AC39" s="70">
-        <f>AC4</f>
+        <f t="shared" si="56"/>
         <v>25718.574699999997</v>
       </c>
       <c r="AD39" s="70">
-        <f>AD4</f>
+        <f t="shared" si="56"/>
         <v>30733.696766499997</v>
       </c>
       <c r="AE39" s="70">
-        <f>AE4</f>
+        <f t="shared" si="56"/>
         <v>36680.667090817748</v>
       </c>
       <c r="AF39" s="70">
-        <f>AF4</f>
+        <f t="shared" si="56"/>
         <v>42402.851156985314</v>
       </c>
       <c r="AG39" s="70">
-        <f>AG4</f>
+        <f t="shared" si="56"/>
         <v>47872.81895623642</v>
       </c>
       <c r="AH39" s="70">
-        <f>AH4</f>
+        <f t="shared" si="56"/>
         <v>51702.644472735337</v>
       </c>
       <c r="AI39" s="70">
-        <f>AI4</f>
+        <f t="shared" si="56"/>
         <v>54804.803141099459</v>
       </c>
       <c r="AJ39" s="70">
-        <f>AJ4</f>
+        <f t="shared" si="56"/>
         <v>56996.995266743441</v>
       </c>
       <c r="AK39" s="70">
-        <f>AK4</f>
+        <f t="shared" si="56"/>
         <v>58706.905124745746</v>
       </c>
       <c r="AL39" s="70">
-        <f>AL4</f>
+        <f t="shared" si="56"/>
         <v>59881.043227240662</v>
       </c>
     </row>
@@ -13701,47 +13704,47 @@
         <v>546</v>
       </c>
       <c r="C40" s="1">
-        <f>C5</f>
+        <f t="shared" ref="C40:M40" si="57">C5</f>
         <v>3333</v>
       </c>
       <c r="D40" s="1">
-        <f>D5</f>
+        <f t="shared" si="57"/>
         <v>3731</v>
       </c>
       <c r="E40" s="1">
-        <f>E5</f>
+        <f t="shared" si="57"/>
         <v>3383</v>
       </c>
       <c r="F40" s="1">
-        <f>F5</f>
+        <f t="shared" si="57"/>
         <v>4534</v>
       </c>
       <c r="G40" s="1">
-        <f>G5</f>
+        <f t="shared" si="57"/>
         <v>3642</v>
       </c>
       <c r="H40" s="1">
-        <f>H5</f>
+        <f t="shared" si="57"/>
         <v>4010</v>
       </c>
       <c r="I40" s="1">
-        <f>I5</f>
+        <f t="shared" si="57"/>
         <v>3623</v>
       </c>
       <c r="J40" s="1">
-        <f>J5</f>
+        <f t="shared" si="57"/>
         <v>4708</v>
       </c>
       <c r="K40" s="1">
-        <f>K5</f>
+        <f t="shared" si="57"/>
         <v>3835</v>
       </c>
       <c r="L40" s="1">
-        <f>L5</f>
+        <f t="shared" si="57"/>
         <v>4217</v>
       </c>
       <c r="M40" s="1">
-        <f>M5</f>
+        <f t="shared" si="57"/>
         <v>4089</v>
       </c>
       <c r="Y40" s="1">
@@ -13749,55 +13752,55 @@
         <v>13835</v>
       </c>
       <c r="Z40" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>14981</v>
       </c>
       <c r="AA40" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>15983</v>
       </c>
       <c r="AB40" s="70">
-        <f>AB5</f>
+        <f t="shared" ref="AB40:AL40" si="58">AB5</f>
         <v>16814.116000000002</v>
       </c>
       <c r="AC40" s="70">
-        <f>AC5</f>
+        <f t="shared" si="58"/>
         <v>18293.758208000003</v>
       </c>
       <c r="AD40" s="70">
-        <f>AD5</f>
+        <f t="shared" si="58"/>
         <v>20287.777852672003</v>
       </c>
       <c r="AE40" s="70">
-        <f>AE5</f>
+        <f t="shared" si="58"/>
         <v>22499.145638613252</v>
       </c>
       <c r="AF40" s="70">
-        <f>AF5</f>
+        <f t="shared" si="58"/>
         <v>25829.019193128013</v>
       </c>
       <c r="AG40" s="70">
-        <f>AG5</f>
+        <f t="shared" si="58"/>
         <v>29845.431677659417</v>
       </c>
       <c r="AH40" s="70">
-        <f>AH5</f>
+        <f t="shared" si="58"/>
         <v>34322.246429308325</v>
       </c>
       <c r="AI40" s="70">
-        <f>AI5</f>
+        <f t="shared" si="58"/>
         <v>39127.360929411494</v>
       </c>
       <c r="AJ40" s="70">
-        <f>AJ5</f>
+        <f t="shared" si="58"/>
         <v>42257.549803764414</v>
       </c>
       <c r="AK40" s="70">
-        <f>AK5</f>
+        <f t="shared" si="58"/>
         <v>45215.578290027923</v>
       </c>
       <c r="AL40" s="70">
-        <f>AL5</f>
+        <f t="shared" si="58"/>
         <v>47476.357204529319</v>
       </c>
     </row>
@@ -13806,39 +13809,39 @@
         <v>62</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" ref="C41" si="53">SUM(C39:C40)</f>
+        <f t="shared" ref="C41" si="59">SUM(C39:C40)</f>
         <v>6822</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41" si="54">SUM(D39:D40)</f>
+        <f t="shared" ref="D41" si="60">SUM(D39:D40)</f>
         <v>8119</v>
       </c>
       <c r="E41" s="2">
-        <f t="shared" ref="E41" si="55">SUM(E39:E40)</f>
+        <f t="shared" ref="E41" si="61">SUM(E39:E40)</f>
         <v>8252</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" ref="F41" si="56">SUM(F39:F40)</f>
+        <f t="shared" ref="F41" si="62">SUM(F39:F40)</f>
         <v>10046</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" ref="G41:K41" si="57">SUM(G39:G40)</f>
+        <f t="shared" ref="G41:K41" si="63">SUM(G39:G40)</f>
         <v>7259</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>8204</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>8913</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>10559</v>
       </c>
       <c r="K41" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>8032</v>
       </c>
       <c r="L41" s="2">
@@ -13859,55 +13862,55 @@
         <v>29654</v>
       </c>
       <c r="Z41" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>33239</v>
       </c>
       <c r="AA41" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>34935</v>
       </c>
       <c r="AB41" s="71">
-        <f>AB6</f>
+        <f t="shared" ref="AB41:AL41" si="64">AB6</f>
         <v>38372.016000000003</v>
       </c>
       <c r="AC41" s="71">
-        <f>AC6</f>
+        <f t="shared" si="64"/>
         <v>44012.332907999997</v>
       </c>
       <c r="AD41" s="71">
-        <f>AD6</f>
+        <f t="shared" si="64"/>
         <v>51021.474619172004</v>
       </c>
       <c r="AE41" s="71">
-        <f>AE6</f>
+        <f t="shared" si="64"/>
         <v>59179.812729430996</v>
       </c>
       <c r="AF41" s="71">
-        <f>AF6</f>
+        <f t="shared" si="64"/>
         <v>68231.870350113328</v>
       </c>
       <c r="AG41" s="71">
-        <f>AG6</f>
+        <f t="shared" si="64"/>
         <v>77718.250633895834</v>
       </c>
       <c r="AH41" s="71">
-        <f>AH6</f>
+        <f t="shared" si="64"/>
         <v>86024.890902043669</v>
       </c>
       <c r="AI41" s="71">
-        <f>AI6</f>
+        <f t="shared" si="64"/>
         <v>93932.164070510946</v>
       </c>
       <c r="AJ41" s="71">
-        <f>AJ6</f>
+        <f t="shared" si="64"/>
         <v>99254.545070507855</v>
       </c>
       <c r="AK41" s="71">
-        <f>AK6</f>
+        <f t="shared" si="64"/>
         <v>103922.48341477367</v>
       </c>
       <c r="AL41" s="71">
-        <f>AL6</f>
+        <f t="shared" si="64"/>
         <v>107357.40043176999</v>
       </c>
       <c r="AM41" s="34"/>
@@ -14006,11 +14009,11 @@
         <v>16972</v>
       </c>
       <c r="Z42" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>18705</v>
       </c>
       <c r="AA42" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>17989</v>
       </c>
       <c r="AB42" s="70">
@@ -14018,43 +14021,43 @@
         <v>19240.425749999999</v>
       </c>
       <c r="AC42" s="70">
-        <f t="shared" ref="AC42:AL42" si="58">AC39*(1-AC58)</f>
+        <f t="shared" ref="AC42:AL42" si="65">AC39*(1-AC58)</f>
         <v>22632.345735999999</v>
       </c>
       <c r="AD42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>26430.979219189998</v>
       </c>
       <c r="AE42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>31361.970362649172</v>
       </c>
       <c r="AF42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>36042.423483437517</v>
       </c>
       <c r="AG42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>40452.532018019774</v>
       </c>
       <c r="AH42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>43430.221357097682</v>
       </c>
       <c r="AI42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>46036.034638523546</v>
       </c>
       <c r="AJ42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>47877.47602406449</v>
       </c>
       <c r="AK42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>49313.800304786426</v>
       </c>
       <c r="AL42" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>50300.076310882156</v>
       </c>
     </row>
@@ -14101,11 +14104,11 @@
         <v>9224</v>
       </c>
       <c r="Z43" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>9716</v>
       </c>
       <c r="AA43" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>10861</v>
       </c>
       <c r="AB43" s="70">
@@ -14113,43 +14116,43 @@
         <v>11685.810620000002</v>
       </c>
       <c r="AC43" s="70">
-        <f t="shared" ref="AC43:AL43" si="59">AC40*(1-AC59)</f>
+        <f t="shared" ref="AC43:AL43" si="66">AC40*(1-AC59)</f>
         <v>12439.75558144</v>
       </c>
       <c r="AD43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>13187.055604236803</v>
       </c>
       <c r="AE43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>14399.453208712483</v>
       </c>
       <c r="AF43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>16401.427187636287</v>
       </c>
       <c r="AG43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>18802.621956925432</v>
       </c>
       <c r="AH43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>21623.015250464246</v>
       </c>
       <c r="AI43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>24650.237385529243</v>
       </c>
       <c r="AJ43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>26622.256376371581</v>
       </c>
       <c r="AK43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>28485.814322717593</v>
       </c>
       <c r="AL43" s="70">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>29910.105038853471</v>
       </c>
     </row>
@@ -14158,39 +14161,39 @@
         <v>64</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" ref="C44:K44" si="60">SUM(C42:C43)</f>
+        <f t="shared" ref="C44:K44" si="67">SUM(C42:C43)</f>
         <v>5903</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>6972</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>7201</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>8345</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>6109</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>6502</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>7804</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>8435</v>
       </c>
       <c r="K44" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>6562</v>
       </c>
       <c r="L44" s="1">
@@ -14206,11 +14209,11 @@
         <v>26196</v>
       </c>
       <c r="Z44" s="1">
-        <f t="shared" ref="Z44" si="61">SUM(C44:F44)</f>
+        <f t="shared" ref="Z44" si="68">SUM(C44:F44)</f>
         <v>28421</v>
       </c>
       <c r="AA44" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>28850</v>
       </c>
       <c r="AB44" s="70">
@@ -14218,43 +14221,43 @@
         <v>30926.236369999999</v>
       </c>
       <c r="AC44" s="70">
-        <f t="shared" ref="AC44:AL44" si="62">AC43+AC42</f>
+        <f t="shared" ref="AC44:AL44" si="69">AC43+AC42</f>
         <v>35072.10131744</v>
       </c>
       <c r="AD44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>39618.034823426802</v>
       </c>
       <c r="AE44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>45761.423571361651</v>
       </c>
       <c r="AF44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>52443.8506710738</v>
       </c>
       <c r="AG44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>59255.153974945206</v>
       </c>
       <c r="AH44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>65053.236607561928</v>
       </c>
       <c r="AI44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>70686.272024052785</v>
       </c>
       <c r="AJ44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>74499.732400436071</v>
       </c>
       <c r="AK44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>77799.614627504023</v>
       </c>
       <c r="AL44" s="70">
-        <f t="shared" si="62"/>
+        <f t="shared" si="69"/>
         <v>80210.18134973562</v>
       </c>
     </row>
@@ -14263,59 +14266,59 @@
         <v>65</v>
       </c>
       <c r="C45" s="1">
-        <f t="shared" ref="C45" si="63">C41-SUM(C42:C43)</f>
+        <f t="shared" ref="C45" si="70">C41-SUM(C42:C43)</f>
         <v>919</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" ref="D45" si="64">D41-SUM(D42:D43)</f>
+        <f t="shared" ref="D45" si="71">D41-SUM(D42:D43)</f>
         <v>1147</v>
       </c>
       <c r="E45" s="1">
-        <f t="shared" ref="E45" si="65">E41-SUM(E42:E43)</f>
+        <f t="shared" ref="E45" si="72">E41-SUM(E42:E43)</f>
         <v>1051</v>
       </c>
       <c r="F45" s="1">
-        <f t="shared" ref="F45" si="66">F41-SUM(F42:F43)</f>
+        <f t="shared" ref="F45" si="73">F41-SUM(F42:F43)</f>
         <v>1701</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" ref="G45:L45" si="67">G41-SUM(G42:G43)</f>
+        <f t="shared" ref="G45:L45" si="74">G41-SUM(G42:G43)</f>
         <v>1150</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>1702</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>1109</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>2124</v>
       </c>
       <c r="K45" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>1470</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>1846</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" ref="M45" si="68">M41-SUM(M42:M43)</f>
+        <f t="shared" ref="M45" si="75">M41-SUM(M42:M43)</f>
         <v>1898</v>
       </c>
       <c r="Y45" s="1">
-        <f t="shared" ref="Y45" si="69">Y41-SUM(Y42:Y43)</f>
+        <f t="shared" ref="Y45" si="76">Y41-SUM(Y42:Y43)</f>
         <v>3458</v>
       </c>
       <c r="Z45" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4818</v>
       </c>
       <c r="AA45" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>6085</v>
       </c>
       <c r="AB45" s="70">
@@ -14323,43 +14326,43 @@
         <v>7445.7796300000045</v>
       </c>
       <c r="AC45" s="70">
-        <f t="shared" ref="AC45:AL45" si="70">AC41-SUM(AC42:AC43)</f>
+        <f t="shared" ref="AC45:AL45" si="77">AC41-SUM(AC42:AC43)</f>
         <v>8940.2315905599971</v>
       </c>
       <c r="AD45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>11403.439795745202</v>
       </c>
       <c r="AE45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>13418.389158069345</v>
       </c>
       <c r="AF45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>15788.019679039528</v>
       </c>
       <c r="AG45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>18463.096658950628</v>
       </c>
       <c r="AH45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>20971.654294481741</v>
       </c>
       <c r="AI45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>23245.892046458161</v>
       </c>
       <c r="AJ45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>24754.812670071784</v>
       </c>
       <c r="AK45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>26122.868787269646</v>
       </c>
       <c r="AL45" s="70">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>27147.219082034368</v>
       </c>
     </row>
@@ -14406,11 +14409,11 @@
         <v>5360</v>
       </c>
       <c r="Z46" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4845</v>
       </c>
       <c r="AA46" s="1">
-        <f t="shared" ref="AA46:AA56" si="71">SUM(G46:J46)</f>
+        <f t="shared" ref="AA46:AA56" si="78">SUM(G46:J46)</f>
         <v>4632</v>
       </c>
       <c r="AB46" s="70">
@@ -14418,43 +14421,43 @@
         <v>5087.7108376127098</v>
       </c>
       <c r="AC46" s="70">
-        <f t="shared" ref="AC46:AL46" si="72">AC41*AC61</f>
+        <f t="shared" ref="AC46:AL46" si="79">AC41*AC61</f>
         <v>5835.5553464965215</v>
       </c>
       <c r="AD46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>6764.8910959211316</v>
       </c>
       <c r="AE46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>7846.597754765261</v>
       </c>
       <c r="AF46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>9046.8018738149403</v>
       </c>
       <c r="AG46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>10304.592441282539</v>
       </c>
       <c r="AH46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>11405.962348884108</v>
       </c>
       <c r="AI46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>12454.380534552933</v>
       </c>
       <c r="AJ46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>13160.070209434447</v>
       </c>
       <c r="AK46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>13778.987925496827</v>
       </c>
       <c r="AL46" s="70">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>14234.42046085469</v>
       </c>
     </row>
@@ -14501,11 +14504,11 @@
         <v>979</v>
       </c>
       <c r="Z47" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>896</v>
       </c>
       <c r="AA47" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>982</v>
       </c>
       <c r="AB47" s="70">
@@ -14513,43 +14516,43 @@
         <v>1078.6122717045944</v>
       </c>
       <c r="AC47" s="70">
-        <f t="shared" ref="AC47:AL47" si="73">AC41*AC62</f>
+        <f t="shared" ref="AC47:AL47" si="80">AC41*AC62</f>
         <v>1237.1578908159725</v>
       </c>
       <c r="AD47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>1434.1802798347476</v>
       </c>
       <c r="AE47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>1663.5058279748457</v>
       </c>
       <c r="AF47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>1917.9532469961725</v>
       </c>
       <c r="AG47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>2184.6091919990185</v>
       </c>
       <c r="AH47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>2418.1034167971056</v>
       </c>
       <c r="AI47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>2640.3716936379487</v>
       </c>
       <c r="AJ47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>2789.980342328287</v>
       </c>
       <c r="AK47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>2921.1930360185411</v>
       </c>
       <c r="AL47" s="70">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>3017.7463066837877</v>
       </c>
     </row>
@@ -14558,39 +14561,39 @@
         <v>551</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" ref="C48" si="74">C45-SUM(C46:C47)</f>
+        <f t="shared" ref="C48" si="81">C45-SUM(C46:C47)</f>
         <v>-469</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="75">D45-SUM(D46:D47)</f>
+        <f t="shared" ref="D48" si="82">D45-SUM(D46:D47)</f>
         <v>-341</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" ref="E48" si="76">E45-SUM(E46:E47)</f>
+        <f t="shared" ref="E48" si="83">E45-SUM(E46:E47)</f>
         <v>-307</v>
       </c>
       <c r="F48" s="1">
-        <f t="shared" ref="F48" si="77">F45-SUM(F46:F47)</f>
+        <f t="shared" ref="F48" si="84">F45-SUM(F46:F47)</f>
         <v>194</v>
       </c>
       <c r="G48" s="1">
-        <f t="shared" ref="G48:K48" si="78">G45-SUM(G46:G47)</f>
+        <f t="shared" ref="G48:K48" si="85">G45-SUM(G46:G47)</f>
         <v>-289</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>527</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>-359</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>592</v>
       </c>
       <c r="K48" s="1">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>43</v>
       </c>
       <c r="L48" s="1">
@@ -14602,15 +14605,15 @@
         <v>367</v>
       </c>
       <c r="Y48" s="1">
-        <f t="shared" ref="Y48" si="79">Y45-SUM(Y46:Y47)</f>
+        <f t="shared" ref="Y48" si="86">Y45-SUM(Y46:Y47)</f>
         <v>-2881</v>
       </c>
       <c r="Z48" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-923</v>
       </c>
       <c r="AA48" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>471</v>
       </c>
       <c r="AB48" s="70">
@@ -14618,43 +14621,43 @@
         <v>1279.4565206827001</v>
       </c>
       <c r="AC48" s="70">
-        <f t="shared" ref="AC48:AL48" si="80">AC45-SUM(AC46:AC47)</f>
+        <f t="shared" ref="AC48:AL48" si="87">AC45-SUM(AC46:AC47)</f>
         <v>1867.518353247503</v>
       </c>
       <c r="AD48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>3204.3684199893232</v>
       </c>
       <c r="AE48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>3908.2855753292388</v>
       </c>
       <c r="AF48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>4823.2645582284149</v>
       </c>
       <c r="AG48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>5973.8950256690696</v>
       </c>
       <c r="AH48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>7147.5885288005265</v>
       </c>
       <c r="AI48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>8151.1398182672783</v>
       </c>
       <c r="AJ48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>8804.7621183090505</v>
       </c>
       <c r="AK48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>9422.6878257542776</v>
       </c>
       <c r="AL48" s="70">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>9895.0523144958897</v>
       </c>
     </row>
@@ -14701,55 +14704,55 @@
         <v>-151</v>
       </c>
       <c r="Z49" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-98</v>
       </c>
       <c r="AA49" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>120</v>
       </c>
       <c r="AB49" s="70">
-        <f>AA67*$AK$69</f>
+        <f t="shared" ref="AB49:AL49" si="88">AA67*$AK$69</f>
         <v>943.57500000000005</v>
       </c>
       <c r="AC49" s="70">
-        <f>AB67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>1300.4202085320605</v>
       </c>
       <c r="AD49" s="70">
-        <f>AC67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>1753.6795256436876</v>
       </c>
       <c r="AE49" s="70">
-        <f>AD67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>2385.1462534508469</v>
       </c>
       <c r="AF49" s="70">
-        <f>AE67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>3150.9315412427018</v>
       </c>
       <c r="AG49" s="70">
-        <f>AF67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>4083.4068582680679</v>
       </c>
       <c r="AH49" s="70">
-        <f>AG67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>5220.1995842551169</v>
       </c>
       <c r="AI49" s="70">
-        <f>AH67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>6583.1298747430683</v>
       </c>
       <c r="AJ49" s="70">
-        <f>AI67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>8178.5431687500804</v>
       </c>
       <c r="AK49" s="70">
-        <f>AJ67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>9997.1317023309257</v>
       </c>
       <c r="AL49" s="70">
-        <f>AK67*$AK$69</f>
+        <f t="shared" si="88"/>
         <v>12057.403138145832</v>
       </c>
     </row>
@@ -14796,11 +14799,11 @@
         <v>188</v>
       </c>
       <c r="Z50" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>567</v>
       </c>
       <c r="AA50" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>536</v>
       </c>
       <c r="AB50" s="70">
@@ -14816,35 +14819,35 @@
         <v>588.12599999999998</v>
       </c>
       <c r="AE50" s="70">
-        <f t="shared" ref="AE50:AL50" si="81">AD50*1.1</f>
+        <f t="shared" ref="AE50:AL50" si="89">AD50*1.1</f>
         <v>646.93860000000006</v>
       </c>
       <c r="AF50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>711.63246000000015</v>
       </c>
       <c r="AG50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>782.79570600000022</v>
       </c>
       <c r="AH50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>861.07527660000028</v>
       </c>
       <c r="AI50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>947.18280426000035</v>
       </c>
       <c r="AJ50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>1041.9010846860006</v>
       </c>
       <c r="AK50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>1146.0911931546007</v>
       </c>
       <c r="AL50" s="70">
-        <f t="shared" si="81"/>
+        <f t="shared" si="89"/>
         <v>1260.7003124700609</v>
       </c>
     </row>
@@ -14891,11 +14894,11 @@
         <v>370</v>
       </c>
       <c r="Z51" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>324</v>
       </c>
       <c r="AA51" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>1372</v>
       </c>
       <c r="AB51" s="70">
@@ -14915,31 +14918,31 @@
         <v>1488.7466630400002</v>
       </c>
       <c r="AF51" s="70">
-        <f t="shared" ref="AF51:AL51" si="82">AE51*1.06</f>
+        <f t="shared" ref="AF51:AL51" si="90">AE51*1.06</f>
         <v>1578.0714628224002</v>
       </c>
       <c r="AG51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>1672.7557505917443</v>
       </c>
       <c r="AH51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>1773.1210956272491</v>
       </c>
       <c r="AI51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>1879.5083613648842</v>
       </c>
       <c r="AJ51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>1992.2788630467774</v>
       </c>
       <c r="AK51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>2111.8155948295839</v>
       </c>
       <c r="AL51" s="70">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>2238.5245305193589</v>
       </c>
     </row>
@@ -14948,39 +14951,39 @@
         <v>555</v>
       </c>
       <c r="C52" s="1">
-        <f t="shared" ref="C52" si="83">C48+SUM(C49:C51)</f>
+        <f t="shared" ref="C52" si="91">C48+SUM(C49:C51)</f>
         <v>-415</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" ref="D52" si="84">D48+SUM(D49:D51)</f>
+        <f t="shared" ref="D52" si="92">D48+SUM(D49:D51)</f>
         <v>-27</v>
       </c>
       <c r="E52" s="1">
-        <f t="shared" ref="E52" si="85">E48+SUM(E49:E51)</f>
+        <f t="shared" ref="E52" si="93">E48+SUM(E49:E51)</f>
         <v>-16</v>
       </c>
       <c r="F52" s="1">
-        <f t="shared" ref="F52" si="86">F48+SUM(F49:F51)</f>
+        <f t="shared" ref="F52" si="94">F48+SUM(F49:F51)</f>
         <v>328</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" ref="G52:K52" si="87">G48+SUM(G49:G51)</f>
+        <f t="shared" ref="G52:K52" si="95">G48+SUM(G49:G51)</f>
         <v>-96</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="95"/>
         <v>1602</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="95"/>
         <v>-122</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="95"/>
         <v>1115</v>
       </c>
       <c r="K52" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="95"/>
         <v>332</v>
       </c>
       <c r="L52" s="1">
@@ -14992,15 +14995,15 @@
         <v>747</v>
       </c>
       <c r="Y52" s="1">
-        <f t="shared" ref="Y52" si="88">Y48+SUM(Y49:Y51)</f>
+        <f t="shared" ref="Y52" si="96">Y48+SUM(Y49:Y51)</f>
         <v>-2474</v>
       </c>
       <c r="Z52" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-130</v>
       </c>
       <c r="AA52" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>2499</v>
       </c>
       <c r="AB52" s="70">
@@ -15008,43 +15011,43 @@
         <v>4056.2115206827002</v>
       </c>
       <c r="AC52" s="70">
-        <f t="shared" ref="AC52:AL52" si="89">AC48+SUM(AC49:AC51)</f>
+        <f t="shared" ref="AC52:AL52" si="97">AC48+SUM(AC49:AC51)</f>
         <v>5053.0581617795633</v>
       </c>
       <c r="AD52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>6950.6519296330107</v>
       </c>
       <c r="AE52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>8429.117091820086</v>
       </c>
       <c r="AF52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>10263.900022293517</v>
       </c>
       <c r="AG52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>12512.853340528882</v>
       </c>
       <c r="AH52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>15001.984485282894</v>
       </c>
       <c r="AI52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>17560.960858635233</v>
       </c>
       <c r="AJ52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>20017.485234791908</v>
       </c>
       <c r="AK52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>22677.726316069391</v>
       </c>
       <c r="AL52" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="97"/>
         <v>25451.68029563114</v>
       </c>
     </row>
@@ -15091,11 +15094,11 @@
         <v>248</v>
       </c>
       <c r="Z53" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>344</v>
       </c>
       <c r="AA53" s="1">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>939</v>
       </c>
       <c r="AB53" s="70">
@@ -15103,43 +15106,43 @@
         <v>953.20970736043455</v>
       </c>
       <c r="AC53" s="70">
-        <f t="shared" ref="AC53:AL53" si="90">AC52*AC64</f>
+        <f t="shared" ref="AC53:AL53" si="98">AC52*AC64</f>
         <v>1111.6727955915039</v>
       </c>
       <c r="AD53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>1459.6369052229322</v>
       </c>
       <c r="AE53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>1770.114589282218</v>
       </c>
       <c r="AF53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>2155.4190046816384</v>
       </c>
       <c r="AG53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>2627.699201511065</v>
       </c>
       <c r="AH53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>3150.4167419094074</v>
       </c>
       <c r="AI53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>3687.8017803133989</v>
       </c>
       <c r="AJ53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>4203.6718993063005</v>
       </c>
       <c r="AK53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>4762.3225263745717</v>
       </c>
       <c r="AL53" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>5344.8528620825391</v>
       </c>
     </row>
@@ -15176,7 +15179,7 @@
         <v>-96</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" ref="J54" si="91">J52-J53</f>
+        <f t="shared" ref="J54" si="99">J52-J53</f>
         <v>485</v>
       </c>
       <c r="K54" s="2">
@@ -15201,11 +15204,11 @@
         <v>-2736</v>
       </c>
       <c r="Z54" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-438</v>
       </c>
       <c r="AA54" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>1553</v>
       </c>
       <c r="AB54" s="71">
@@ -15213,243 +15216,243 @@
         <v>3103.0018133222657</v>
       </c>
       <c r="AC54" s="71">
-        <f t="shared" ref="AC54:AL54" si="92">AC52-AC53</f>
+        <f t="shared" ref="AC54:AL54" si="100">AC52-AC53</f>
         <v>3941.3853661880594</v>
       </c>
       <c r="AD54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>5491.0150244100787</v>
       </c>
       <c r="AE54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>6659.0025025378682</v>
       </c>
       <c r="AF54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>8108.481017611879</v>
       </c>
       <c r="AG54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>9885.1541390178172</v>
       </c>
       <c r="AH54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>11851.567743373485</v>
       </c>
       <c r="AI54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>13873.159078321834</v>
       </c>
       <c r="AJ54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>15813.813335485607</v>
       </c>
       <c r="AK54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>17915.403789694821</v>
       </c>
       <c r="AL54" s="71">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>20106.827433548602</v>
       </c>
       <c r="AM54" s="71">
-        <f>AL54*(1+$AK$70)</f>
+        <f t="shared" ref="AM54:BR54" si="101">AL54*(1+$AK$70)</f>
         <v>20458.696913635704</v>
       </c>
       <c r="AN54" s="71">
-        <f>AM54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>20816.724109624331</v>
       </c>
       <c r="AO54" s="71">
-        <f>AN54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>21181.016781542759</v>
       </c>
       <c r="AP54" s="71">
-        <f>AO54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>21551.684575219759</v>
       </c>
       <c r="AQ54" s="71">
-        <f>AP54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>21928.839055286106</v>
       </c>
       <c r="AR54" s="71">
-        <f>AQ54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>22312.593738753614</v>
       </c>
       <c r="AS54" s="71">
-        <f>AR54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>22703.064129181803</v>
       </c>
       <c r="AT54" s="71">
-        <f>AS54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>23100.367751442485</v>
       </c>
       <c r="AU54" s="71">
-        <f>AT54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>23504.62418709273</v>
       </c>
       <c r="AV54" s="71">
-        <f>AU54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>23915.955110366853</v>
       </c>
       <c r="AW54" s="71">
-        <f>AV54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>24334.484324798275</v>
       </c>
       <c r="AX54" s="71">
-        <f>AW54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>24760.337800482248</v>
       </c>
       <c r="AY54" s="71">
-        <f>AX54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>25193.643711990688</v>
       </c>
       <c r="AZ54" s="71">
-        <f>AY54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>25634.532476950528</v>
       </c>
       <c r="BA54" s="71">
-        <f>AZ54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>26083.136795297163</v>
       </c>
       <c r="BB54" s="71">
-        <f>BA54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>26539.591689214867</v>
       </c>
       <c r="BC54" s="71">
-        <f>BB54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>27004.034543776128</v>
       </c>
       <c r="BD54" s="71">
-        <f>BC54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>27476.605148292212</v>
       </c>
       <c r="BE54" s="71">
-        <f>BD54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>27957.445738387327</v>
       </c>
       <c r="BF54" s="71">
-        <f>BE54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>28446.701038809108</v>
       </c>
       <c r="BG54" s="71">
-        <f>BF54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>28944.51830698827</v>
       </c>
       <c r="BH54" s="71">
-        <f>BG54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>29451.047377360566</v>
       </c>
       <c r="BI54" s="71">
-        <f>BH54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>29966.440706464378</v>
       </c>
       <c r="BJ54" s="71">
-        <f>BI54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>30490.853418827508</v>
       </c>
       <c r="BK54" s="71">
-        <f>BJ54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>31024.443353656992</v>
       </c>
       <c r="BL54" s="71">
-        <f>BK54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>31567.371112345991</v>
       </c>
       <c r="BM54" s="71">
-        <f>BL54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>32119.800106812047</v>
       </c>
       <c r="BN54" s="71">
-        <f>BM54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>32681.896608681258</v>
       </c>
       <c r="BO54" s="71">
-        <f>BN54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>33253.82979933318</v>
       </c>
       <c r="BP54" s="71">
-        <f>BO54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>33835.771820821516</v>
       </c>
       <c r="BQ54" s="71">
-        <f>BP54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>34427.897827685898</v>
       </c>
       <c r="BR54" s="71">
-        <f>BQ54*(1+$AK$70)</f>
+        <f t="shared" si="101"/>
         <v>35030.386039670404</v>
       </c>
       <c r="BS54" s="71">
-        <f>BR54*(1+$AK$70)</f>
+        <f t="shared" ref="BS54:CJ54" si="102">BR54*(1+$AK$70)</f>
         <v>35643.417795364636</v>
       </c>
       <c r="BT54" s="71">
-        <f>BS54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>36267.177606783516</v>
       </c>
       <c r="BU54" s="71">
-        <f>BT54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>36901.853214902229</v>
       </c>
       <c r="BV54" s="71">
-        <f>BU54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>37547.63564616302</v>
       </c>
       <c r="BW54" s="71">
-        <f>BV54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>38204.719269970876</v>
       </c>
       <c r="BX54" s="71">
-        <f>BW54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>38873.301857195365</v>
       </c>
       <c r="BY54" s="71">
-        <f>BX54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>39553.584639696288</v>
       </c>
       <c r="BZ54" s="71">
-        <f>BY54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>40245.772370890976</v>
       </c>
       <c r="CA54" s="71">
-        <f>BZ54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>40950.07338738157</v>
       </c>
       <c r="CB54" s="71">
-        <f>CA54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>41666.699671660754</v>
       </c>
       <c r="CC54" s="71">
-        <f>CB54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>42395.866915914819</v>
       </c>
       <c r="CD54" s="71">
-        <f>CC54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>43137.794586943332</v>
       </c>
       <c r="CE54" s="71">
-        <f>CD54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>43892.70599221484</v>
       </c>
       <c r="CF54" s="71">
-        <f>CE54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>44660.828347078605</v>
       </c>
       <c r="CG54" s="71">
-        <f>CF54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>45442.392843152484</v>
       </c>
       <c r="CH54" s="71">
-        <f>CG54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>46237.634717907655</v>
       </c>
       <c r="CI54" s="71">
-        <f>CH54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>47046.793325471044</v>
       </c>
       <c r="CJ54" s="71">
-        <f>CI54*(1+$AK$70)</f>
+        <f t="shared" si="102"/>
         <v>47870.112208666789</v>
       </c>
       <c r="CK54" s="34"/>
@@ -15518,39 +15521,39 @@
         <v>557</v>
       </c>
       <c r="C56" s="39">
-        <f t="shared" ref="C56" si="93">C54/C55</f>
+        <f t="shared" ref="C56" si="103">C54/C55</f>
         <v>-1.1496350364963503</v>
       </c>
       <c r="D56" s="39">
-        <f t="shared" ref="D56" si="94">D54/D55</f>
+        <f t="shared" ref="D56" si="104">D54/D55</f>
         <v>-0.54744525547445255</v>
       </c>
       <c r="E56" s="39">
-        <f t="shared" ref="E56" si="95">E54/E55</f>
+        <f t="shared" ref="E56" si="105">E54/E55</f>
         <v>-0.62043795620437958</v>
       </c>
       <c r="F56" s="39">
-        <f t="shared" ref="F56" si="96">F54/F55</f>
+        <f t="shared" ref="F56" si="106">F54/F55</f>
         <v>0.71897810218978098</v>
       </c>
       <c r="G56" s="39">
-        <f t="shared" ref="G56:K56" si="97">G54/G55</f>
+        <f t="shared" ref="G56:K56" si="107">G54/G55</f>
         <v>-0.47445255474452552</v>
       </c>
       <c r="H56" s="39">
-        <f t="shared" si="97"/>
+        <f t="shared" si="107"/>
         <v>4.7226277372262775</v>
       </c>
       <c r="I56" s="39">
-        <f t="shared" si="97"/>
+        <f t="shared" si="107"/>
         <v>-0.34909090909090912</v>
       </c>
       <c r="J56" s="39">
-        <f t="shared" si="97"/>
+        <f t="shared" si="107"/>
         <v>1.7636363636363637</v>
       </c>
       <c r="K56" s="39">
-        <f t="shared" si="97"/>
+        <f t="shared" si="107"/>
         <v>0.92363636363636359</v>
       </c>
       <c r="L56" s="39">
@@ -15562,15 +15565,15 @@
         <v>1.6654411764705883</v>
       </c>
       <c r="Y56" s="39">
-        <f t="shared" ref="Y56" si="98">Y54/Y55</f>
+        <f t="shared" ref="Y56" si="108">Y54/Y55</f>
         <v>-9.985401459854014</v>
       </c>
       <c r="Z56" s="39">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-1.5985401459854014</v>
       </c>
       <c r="AA56" s="39">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>5.6627206370272063</v>
       </c>
     </row>
@@ -15579,39 +15582,39 @@
         <v>558</v>
       </c>
       <c r="C58" s="63">
-        <f t="shared" ref="C58:F58" si="99">1-C42/C39</f>
+        <f t="shared" ref="C58:F58" si="109">1-C42/C39</f>
         <v>-2.4648896531957565E-2</v>
       </c>
       <c r="D58" s="63">
-        <f t="shared" si="99"/>
+        <f t="shared" si="109"/>
         <v>-5.3099361896080222E-2</v>
       </c>
       <c r="E58" s="63">
-        <f t="shared" si="99"/>
+        <f t="shared" si="109"/>
         <v>-2.7931813514068704E-2</v>
       </c>
       <c r="F58" s="63">
-        <f t="shared" si="99"/>
+        <f t="shared" si="109"/>
         <v>1.4513788098693414E-3</v>
       </c>
       <c r="G58" s="63">
-        <f t="shared" ref="G58:K58" si="100">1-G42/G39</f>
+        <f t="shared" ref="G58:K58" si="110">1-G42/G39</f>
         <v>-2.1011888305225268E-2</v>
       </c>
       <c r="H58" s="63">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>8.1306628516928936E-2</v>
       </c>
       <c r="I58" s="63">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>4.0453686200378036E-2</v>
       </c>
       <c r="J58" s="63">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>8.2720902409844421E-2</v>
       </c>
       <c r="K58" s="63">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>6.7190850607576791E-2</v>
       </c>
       <c r="L58" s="63">
@@ -15623,15 +15626,15 @@
         <v>0.12159863945578231</v>
       </c>
       <c r="Y58" s="63">
-        <f t="shared" ref="Y58:AA58" si="101">1-Y42/Y39</f>
+        <f t="shared" ref="Y58:AA58" si="111">1-Y42/Y39</f>
         <v>-7.2887034578671184E-2</v>
       </c>
       <c r="Z58" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="111"/>
         <v>-2.4482418665790373E-2</v>
       </c>
       <c r="AA58" s="63">
-        <f t="shared" si="101"/>
+        <f t="shared" si="111"/>
         <v>5.0812579147319514E-2</v>
       </c>
       <c r="AB58" s="65">
@@ -15673,39 +15676,39 @@
         <v>559</v>
       </c>
       <c r="C59" s="63">
-        <f t="shared" ref="C59:F59" si="102">1-C43/C40</f>
+        <f t="shared" ref="C59:F59" si="112">1-C43/C40</f>
         <v>0.30153015301530151</v>
       </c>
       <c r="D59" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="112"/>
         <v>0.36987402841061379</v>
       </c>
       <c r="E59" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="112"/>
         <v>0.350872007094295</v>
       </c>
       <c r="F59" s="63">
-        <f t="shared" si="102"/>
+        <f t="shared" si="112"/>
         <v>0.37340097044552267</v>
       </c>
       <c r="G59" s="63">
-        <f t="shared" ref="G59:K59" si="103">1-G43/G40</f>
+        <f t="shared" ref="G59:K59" si="113">1-G43/G40</f>
         <v>0.33662822624931354</v>
       </c>
       <c r="H59" s="63">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>0.33940149625935168</v>
       </c>
       <c r="I59" s="63">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>0.24703284570797679</v>
       </c>
       <c r="J59" s="63">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>0.34834324553950724</v>
       </c>
       <c r="K59" s="63">
-        <f t="shared" si="103"/>
+        <f t="shared" si="113"/>
         <v>0.30977835723598435</v>
       </c>
       <c r="L59" s="63">
@@ -15717,15 +15720,15 @@
         <v>0.28931279041330393</v>
       </c>
       <c r="Y59" s="63">
-        <f t="shared" ref="Y59:AA59" si="104">1-Y43/Y40</f>
+        <f t="shared" ref="Y59:AA59" si="114">1-Y43/Y40</f>
         <v>0.33328514636790751</v>
       </c>
       <c r="Z59" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.35144516387424074</v>
       </c>
       <c r="AA59" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="114"/>
         <v>0.32046549458799978</v>
       </c>
       <c r="AB59" s="65">
@@ -15767,39 +15770,39 @@
         <v>66</v>
       </c>
       <c r="C60" s="63">
-        <f t="shared" ref="C60:F60" si="105">C45/C41</f>
+        <f t="shared" ref="C60:F60" si="115">C45/C41</f>
         <v>0.13471122837877456</v>
       </c>
       <c r="D60" s="63">
-        <f t="shared" si="105"/>
+        <f t="shared" si="115"/>
         <v>0.14127355585663259</v>
       </c>
       <c r="E60" s="63">
-        <f t="shared" si="105"/>
+        <f t="shared" si="115"/>
         <v>0.12736306349975762</v>
       </c>
       <c r="F60" s="63">
-        <f t="shared" si="105"/>
+        <f t="shared" si="115"/>
         <v>0.16932112283495918</v>
       </c>
       <c r="G60" s="63">
-        <f t="shared" ref="G60:K60" si="106">G45/G41</f>
+        <f t="shared" ref="G60:K60" si="116">G45/G41</f>
         <v>0.15842402534784406</v>
       </c>
       <c r="H60" s="63">
-        <f t="shared" si="106"/>
+        <f t="shared" si="116"/>
         <v>0.20745977571916138</v>
       </c>
       <c r="I60" s="63">
-        <f t="shared" si="106"/>
+        <f t="shared" si="116"/>
         <v>0.12442499719510827</v>
       </c>
       <c r="J60" s="63">
-        <f t="shared" si="106"/>
+        <f t="shared" si="116"/>
         <v>0.20115541244436025</v>
       </c>
       <c r="K60" s="63">
-        <f t="shared" si="106"/>
+        <f t="shared" si="116"/>
         <v>0.18301792828685259</v>
       </c>
       <c r="L60" s="63">
@@ -15811,59 +15814,59 @@
         <v>0.19039020964991474</v>
       </c>
       <c r="Y60" s="63">
-        <f t="shared" ref="Y60:AL60" si="107">Y45/Y41</f>
+        <f t="shared" ref="Y60:AL60" si="117">Y45/Y41</f>
         <v>0.11661158696971741</v>
       </c>
       <c r="Z60" s="63">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.14495020909172959</v>
       </c>
       <c r="AA60" s="63">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.17418062115357091</v>
       </c>
       <c r="AB60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.19404191924656772</v>
       </c>
       <c r="AC60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.20313014557187803</v>
       </c>
       <c r="AD60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.22350274822241625</v>
       </c>
       <c r="AE60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.22673929739213558</v>
       </c>
       <c r="AF60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.23138776055863028</v>
       </c>
       <c r="AG60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.23756449107332558</v>
       </c>
       <c r="AH60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.24378588655650971</v>
       </c>
       <c r="AI60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.24747531664455683</v>
       </c>
       <c r="AJ60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.24940734605641088</v>
       </c>
       <c r="AK60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.2513687888212649</v>
       </c>
       <c r="AL60" s="65">
-        <f t="shared" si="107"/>
+        <f t="shared" si="117"/>
         <v>0.25286770146122839</v>
       </c>
     </row>
@@ -15872,39 +15875,39 @@
         <v>68</v>
       </c>
       <c r="C61" s="63">
-        <f t="shared" ref="C61:F61" si="108">C46/C41</f>
+        <f t="shared" ref="C61:F61" si="118">C46/C41</f>
         <v>0.17384931105247728</v>
       </c>
       <c r="D61" s="63">
-        <f t="shared" si="108"/>
+        <f t="shared" si="118"/>
         <v>0.15666954058381574</v>
       </c>
       <c r="E61" s="63">
-        <f t="shared" si="108"/>
+        <f t="shared" si="118"/>
         <v>0.13754241396025205</v>
       </c>
       <c r="F61" s="63">
-        <f t="shared" si="108"/>
+        <f t="shared" si="118"/>
         <v>0.12462671710133387</v>
       </c>
       <c r="G61" s="63">
-        <f t="shared" ref="G61:K61" si="109">G46/G41</f>
+        <f t="shared" ref="G61:K61" si="119">G46/G41</f>
         <v>0.16558754649400745</v>
       </c>
       <c r="H61" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="119"/>
         <v>0.11433447098976109</v>
       </c>
       <c r="I61" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="119"/>
         <v>0.13755189049702682</v>
       </c>
       <c r="J61" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="119"/>
         <v>0.1198977175868927</v>
       </c>
       <c r="K61" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="119"/>
         <v>0.14790836653386455</v>
       </c>
       <c r="L61" s="63">
@@ -15916,15 +15919,15 @@
         <v>0.12247968702979235</v>
       </c>
       <c r="Y61" s="63">
-        <f t="shared" ref="Y61:AA61" si="110">Y46/Y41</f>
+        <f t="shared" ref="Y61:AA61" si="120">Y46/Y41</f>
         <v>0.18075133202940583</v>
       </c>
       <c r="Z61" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="120"/>
         <v>0.14576250789734949</v>
       </c>
       <c r="AA61" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="120"/>
         <v>0.1325890940317733</v>
       </c>
       <c r="AB61" s="65">
@@ -15966,39 +15969,39 @@
         <v>67</v>
       </c>
       <c r="C62" s="63">
-        <f t="shared" ref="C62:F62" si="111">C47/C41</f>
+        <f t="shared" ref="C62:F62" si="121">C47/C41</f>
         <v>2.9610085019055994E-2</v>
       </c>
       <c r="D62" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="121"/>
         <v>2.6604261608572485E-2</v>
       </c>
       <c r="E62" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="121"/>
         <v>2.7023751817741155E-2</v>
       </c>
       <c r="F62" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="121"/>
         <v>2.5383237109297234E-2</v>
       </c>
       <c r="G62" s="63">
-        <f t="shared" ref="G62:K62" si="112">G47/G41</f>
+        <f t="shared" ref="G62:K62" si="122">G47/G41</f>
         <v>3.2649125223860036E-2</v>
       </c>
       <c r="H62" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="122"/>
         <v>2.8888347147732814E-2</v>
       </c>
       <c r="I62" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="122"/>
         <v>2.7151351957814429E-2</v>
       </c>
       <c r="J62" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="122"/>
         <v>2.5191779524576192E-2</v>
       </c>
       <c r="K62" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="122"/>
         <v>2.9755976095617531E-2</v>
       </c>
       <c r="L62" s="63">
@@ -16010,15 +16013,15 @@
         <v>3.1096398836392817E-2</v>
       </c>
       <c r="Y62" s="63">
-        <f t="shared" ref="Y62:AA62" si="113">Y47/Y41</f>
+        <f t="shared" ref="Y62:AA62" si="123">Y47/Y41</f>
         <v>3.3014095906117216E-2</v>
       </c>
       <c r="Z62" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="123"/>
         <v>2.6956286290201269E-2</v>
       </c>
       <c r="AA62" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="123"/>
         <v>2.8109345928152282E-2</v>
       </c>
       <c r="AB62" s="65">
@@ -16060,39 +16063,39 @@
         <v>69</v>
       </c>
       <c r="C63" s="63">
-        <f t="shared" ref="C63:F63" si="114">C48/C41</f>
+        <f t="shared" ref="C63:F63" si="124">C48/C41</f>
         <v>-6.8748167692758724E-2</v>
       </c>
       <c r="D63" s="63">
-        <f t="shared" si="114"/>
+        <f t="shared" si="124"/>
         <v>-4.2000246335755637E-2</v>
       </c>
       <c r="E63" s="63">
-        <f t="shared" si="114"/>
+        <f t="shared" si="124"/>
         <v>-3.7203102278235582E-2</v>
       </c>
       <c r="F63" s="63">
-        <f t="shared" si="114"/>
+        <f t="shared" si="124"/>
         <v>1.9311168624328089E-2</v>
       </c>
       <c r="G63" s="63">
-        <f t="shared" ref="G63:K63" si="115">G48/G41</f>
+        <f t="shared" ref="G63:K63" si="125">G48/G41</f>
         <v>-3.9812646370023422E-2</v>
       </c>
       <c r="H63" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="125"/>
         <v>6.4236957581667475E-2</v>
       </c>
       <c r="I63" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="125"/>
         <v>-4.0278245259732975E-2</v>
       </c>
       <c r="J63" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="125"/>
         <v>5.6065915332891375E-2</v>
       </c>
       <c r="K63" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="125"/>
         <v>5.3535856573705175E-3</v>
       </c>
       <c r="L63" s="63">
@@ -16104,15 +16107,15 @@
         <v>3.6814123783729565E-2</v>
       </c>
       <c r="Y63" s="63">
-        <f t="shared" ref="Y63:AA63" si="116">Y48/Y41</f>
+        <f t="shared" ref="Y63:AA63" si="126">Y48/Y41</f>
         <v>-9.7153840965805621E-2</v>
       </c>
       <c r="Z63" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="126"/>
         <v>-2.7768585095821172E-2</v>
       </c>
       <c r="AA63" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="126"/>
         <v>1.3482181193645342E-2</v>
       </c>
       <c r="AB63" s="65">
@@ -16120,43 +16123,43 @@
         <v>3.3343479286642122E-2</v>
       </c>
       <c r="AC63" s="65">
-        <f t="shared" ref="AC63:AL63" si="117">AC48/AC41</f>
+        <f t="shared" ref="AC63:AL63" si="127">AC48/AC41</f>
         <v>4.2431705611952454E-2</v>
       </c>
       <c r="AD63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>6.2804308262490685E-2</v>
       </c>
       <c r="AE63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>6.6040857432209998E-2</v>
       </c>
       <c r="AF63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>7.0689320598704711E-2</v>
       </c>
       <c r="AG63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>7.6866051113400002E-2</v>
       </c>
       <c r="AH63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>8.3087446596584097E-2</v>
       </c>
       <c r="AI63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>8.6776876684631243E-2</v>
       </c>
       <c r="AJ63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>8.870890609648531E-2</v>
       </c>
       <c r="AK63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>9.0670348861339317E-2</v>
       </c>
       <c r="AL63" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="127"/>
         <v>9.2169261501302835E-2</v>
       </c>
     </row>
@@ -16165,39 +16168,39 @@
         <v>70</v>
       </c>
       <c r="C64" s="63">
-        <f t="shared" ref="C64:F64" si="118">C53/C52</f>
+        <f t="shared" ref="C64:F64" si="128">C53/C52</f>
         <v>0.16626506024096385</v>
       </c>
       <c r="D64" s="63">
-        <f t="shared" si="118"/>
+        <f t="shared" si="128"/>
         <v>-4.5185185185185182</v>
       </c>
       <c r="E64" s="67">
-        <f t="shared" si="118"/>
+        <f t="shared" si="128"/>
         <v>-10.5625</v>
       </c>
       <c r="F64" s="63">
-        <f t="shared" si="118"/>
+        <f t="shared" si="128"/>
         <v>0.37195121951219512</v>
       </c>
       <c r="G64" s="63">
-        <f t="shared" ref="G64:K64" si="119">G53/G52</f>
+        <f t="shared" ref="G64:K64" si="129">G53/G52</f>
         <v>-0.10416666666666667</v>
       </c>
       <c r="H64" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="129"/>
         <v>0.2009987515605493</v>
       </c>
       <c r="I64" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="129"/>
         <v>0.18852459016393441</v>
       </c>
       <c r="J64" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="129"/>
         <v>0.56502242152466364</v>
       </c>
       <c r="K64" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="129"/>
         <v>0.20481927710843373</v>
       </c>
       <c r="L64" s="63">
@@ -16209,15 +16212,15 @@
         <v>0.39223560910307897</v>
       </c>
       <c r="Y64" s="63">
-        <f t="shared" ref="Y64:AA64" si="120">Y53/Y52</f>
+        <f t="shared" ref="Y64:AA64" si="130">Y53/Y52</f>
         <v>-0.10024252223120453</v>
       </c>
       <c r="Z64" s="63">
-        <f t="shared" si="120"/>
+        <f t="shared" si="130"/>
         <v>-2.6461538461538461</v>
       </c>
       <c r="AA64" s="63">
-        <f t="shared" si="120"/>
+        <f t="shared" si="130"/>
         <v>0.37575030012004801</v>
       </c>
       <c r="AB64" s="65">
@@ -16259,39 +16262,39 @@
         <v>71</v>
       </c>
       <c r="C65" s="63">
-        <f t="shared" ref="C65:F65" si="121">C54/C41</f>
+        <f t="shared" ref="C65:F65" si="131">C54/C41</f>
         <v>-4.6174142480211081E-2</v>
       </c>
       <c r="D65" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="131"/>
         <v>-1.847518167261978E-2</v>
       </c>
       <c r="E65" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="131"/>
         <v>-2.0601066408143482E-2</v>
       </c>
       <c r="F65" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="131"/>
         <v>1.9609794943261E-2</v>
       </c>
       <c r="G65" s="63">
-        <f t="shared" ref="G65:K65" si="122">G54/G41</f>
+        <f t="shared" ref="G65:K65" si="132">G54/G41</f>
         <v>-1.7908802865408458E-2</v>
       </c>
       <c r="H65" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="132"/>
         <v>0.15772793759141882</v>
       </c>
       <c r="I65" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="132"/>
         <v>-1.0770784247728038E-2</v>
       </c>
       <c r="J65" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="132"/>
         <v>4.5932379960223507E-2</v>
       </c>
       <c r="K65" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="132"/>
         <v>3.1623505976095617E-2</v>
       </c>
       <c r="L65" s="63">
@@ -16303,15 +16306,15 @@
         <v>4.5440866686728858E-2</v>
       </c>
       <c r="Y65" s="63">
-        <f t="shared" ref="Y65:AA65" si="123">Y54/Y41</f>
+        <f t="shared" ref="Y65:AA65" si="133">Y54/Y41</f>
         <v>-9.226411276724894E-2</v>
       </c>
       <c r="Z65" s="63">
-        <f t="shared" si="123"/>
+        <f t="shared" si="133"/>
         <v>-1.3177291735611781E-2</v>
       </c>
       <c r="AA65" s="63">
-        <f t="shared" si="123"/>
+        <f t="shared" si="133"/>
         <v>4.4453985973951622E-2</v>
       </c>
       <c r="AB65" s="65">
@@ -16389,43 +16392,43 @@
         <v>11308.001813322266</v>
       </c>
       <c r="AC67" s="70">
-        <f t="shared" ref="AC67:AL67" si="124">AB67+AC54</f>
+        <f t="shared" ref="AC67:AL67" si="134">AB67+AC54</f>
         <v>15249.387179510326</v>
       </c>
       <c r="AD67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>20740.402203920406</v>
       </c>
       <c r="AE67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>27399.404706458274</v>
       </c>
       <c r="AF67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>35507.885724070155</v>
       </c>
       <c r="AG67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>45393.039863087972</v>
       </c>
       <c r="AH67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>57244.607606461461</v>
       </c>
       <c r="AI67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>71117.766684783302</v>
       </c>
       <c r="AJ67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>86931.580020268913</v>
       </c>
       <c r="AK67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>104846.98380996374</v>
       </c>
       <c r="AL67" s="70">
-        <f t="shared" si="124"/>
+        <f t="shared" si="134"/>
         <v>124953.81124351235</v>
       </c>
     </row>
@@ -16460,11 +16463,11 @@
         <v>7374</v>
       </c>
       <c r="Z68" s="1">
-        <f t="shared" ref="Z68:Z80" si="125">F68</f>
+        <f t="shared" ref="Z68:Z80" si="135">F68</f>
         <v>7489</v>
       </c>
       <c r="AA68" s="1">
-        <f t="shared" ref="AA68:AA80" si="126">J68</f>
+        <f t="shared" ref="AA68:AA80" si="136">J68</f>
         <v>8177</v>
       </c>
     </row>
@@ -16497,11 +16500,11 @@
         <v>10032</v>
       </c>
       <c r="Z69" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>8253</v>
       </c>
       <c r="AA69" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>8587</v>
       </c>
       <c r="AC69" s="45" t="s">
@@ -16554,11 +16557,11 @@
         <v>9485</v>
       </c>
       <c r="Z70" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>8339</v>
       </c>
       <c r="AA70" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>8621</v>
       </c>
       <c r="AC70" s="46">
@@ -16613,11 +16616,11 @@
         <v>934</v>
       </c>
       <c r="Z71" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>352</v>
       </c>
       <c r="AA71" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>564</v>
       </c>
       <c r="AC71" s="50">
@@ -16643,7 +16646,7 @@
         <v>123</v>
       </c>
       <c r="AK71" s="49">
-        <v>3.9899999999999998E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="AL71" s="46"/>
     </row>
@@ -16676,11 +16679,11 @@
         <v>508</v>
       </c>
       <c r="Z72" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>1444</v>
       </c>
       <c r="AA72" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="AC72" s="52">
@@ -16698,7 +16701,7 @@
       </c>
       <c r="AK72" s="49">
         <f>6.95%-AK71</f>
-        <v>2.9600000000000008E-2</v>
+        <v>2.8400000000000009E-2</v>
       </c>
       <c r="AL72" s="46"/>
     </row>
@@ -16731,11 +16734,11 @@
         <v>5555</v>
       </c>
       <c r="Z73" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>5228</v>
       </c>
       <c r="AA73" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>5150</v>
       </c>
       <c r="AD73" s="46"/>
@@ -16782,11 +16785,11 @@
         <v>4327</v>
       </c>
       <c r="Z74" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>4437</v>
       </c>
       <c r="AA74" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>4263</v>
       </c>
       <c r="AC74" s="46"/>
@@ -16801,7 +16804,7 @@
       </c>
       <c r="AK74" s="49">
         <f>+AK71+(AK72*AK73)</f>
-        <v>8.6964000000000014E-2</v>
+        <v>8.6256000000000013E-2</v>
       </c>
       <c r="AL74" s="53"/>
     </row>
@@ -16834,11 +16837,11 @@
         <v>747</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>1042</v>
       </c>
       <c r="AA75" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>813</v>
       </c>
       <c r="AC75" s="46"/>
@@ -16878,11 +16881,11 @@
         <v>486</v>
       </c>
       <c r="Z76" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>621</v>
       </c>
       <c r="AA76" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>555</v>
       </c>
       <c r="AC76" s="53"/>
@@ -16897,7 +16900,7 @@
       </c>
       <c r="AK76" s="50">
         <f>NPV(AK74,AB54:CJ54)</f>
-        <v>176948.66432300746</v>
+        <v>179081.73830516095</v>
       </c>
       <c r="AL76" s="46"/>
     </row>
@@ -16930,11 +16933,11 @@
         <v>1916</v>
       </c>
       <c r="Z77" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>3555</v>
       </c>
       <c r="AA77" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>2149</v>
       </c>
       <c r="AC77" s="46"/>
@@ -16984,11 +16987,11 @@
         <v>1684</v>
       </c>
       <c r="Z78" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>1582</v>
       </c>
       <c r="AA78" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>1639</v>
       </c>
       <c r="AC78" s="46"/>
@@ -17003,7 +17006,7 @@
       </c>
       <c r="AK78" s="55">
         <f>AK76/AK77</f>
-        <v>652.17700251735016</v>
+        <v>660.03884087115193</v>
       </c>
       <c r="AL78" s="45"/>
     </row>
@@ -17036,11 +17039,11 @@
         <v>3406</v>
       </c>
       <c r="Z79" s="1">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>2228</v>
       </c>
       <c r="AA79" s="1">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>2762</v>
       </c>
       <c r="AC79" s="46"/>
@@ -17055,7 +17058,7 @@
       </c>
       <c r="AK79" s="55">
         <f>Main!C3</f>
-        <v>552.5</v>
+        <v>663.16</v>
       </c>
       <c r="AL79" s="68"/>
     </row>
@@ -17064,27 +17067,27 @@
         <v>571</v>
       </c>
       <c r="F80" s="2">
-        <f t="shared" ref="F80:K80" si="127">SUM(F67:F79)</f>
+        <f t="shared" ref="F80:K80" si="137">SUM(F67:F79)</f>
         <v>46121</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>47872</v>
       </c>
       <c r="H80" s="2">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>48050</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>50853</v>
       </c>
       <c r="J80" s="2">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>51485</v>
       </c>
       <c r="K80" s="2">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>51559</v>
       </c>
       <c r="L80" s="2">
@@ -17101,11 +17104,11 @@
       <c r="Q80" s="34"/>
       <c r="R80" s="34"/>
       <c r="Z80" s="2">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>46121</v>
       </c>
       <c r="AA80" s="2">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>51485</v>
       </c>
       <c r="AB80" s="34"/>
@@ -17121,11 +17124,11 @@
       </c>
       <c r="AK80" s="49">
         <f>AK78/AK79-1</f>
-        <v>0.18041086428479658</v>
+        <v>-4.7064948562157705E-3</v>
       </c>
       <c r="AL80" s="56" t="str">
         <f>IF(AK80&gt;0,"Upside","Downside")</f>
-        <v>Upside</v>
+        <v>Downside</v>
       </c>
       <c r="AM80" s="34"/>
       <c r="AN80" s="34"/>
@@ -17188,11 +17191,11 @@
       <c r="AG81" s="53"/>
       <c r="AH81" s="53"/>
       <c r="AI81" s="53"/>
-      <c r="AJ81" s="74" t="str" cm="1">
+      <c r="AJ81" s="75" t="str" cm="1">
         <f t="array" ref="AJ81">_xlfn.IFS(AK80&gt;=25%,"Strong Buy",AK80&gt;=10.00001%,"Buy",AND(AK80&lt;=10%,AK80&gt;=-4.9999%),"Hold",AND(AK80&lt;=-5%,AK80&gt;=-14.999999%),"Sell",AK80&lt;=-15%,"Strong Sell")</f>
-        <v>Buy</v>
-      </c>
-      <c r="AK81" s="74"/>
+        <v>Hold</v>
+      </c>
+      <c r="AK81" s="75"/>
     </row>
     <row r="82" spans="2:90" ht="14.25" customHeight="1">
       <c r="B82" s="1" t="s">
@@ -17223,11 +17226,11 @@
         <v>9543</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" ref="Z82:Z91" si="128">F82</f>
+        <f t="shared" ref="Z82:Z91" si="138">F82</f>
         <v>7900</v>
       </c>
       <c r="AA82" s="1">
-        <f t="shared" ref="AA82:AA91" si="129">J82</f>
+        <f t="shared" ref="AA82:AA91" si="139">J82</f>
         <v>8602</v>
       </c>
     </row>
@@ -17264,11 +17267,11 @@
         <v>20151</v>
       </c>
       <c r="Z83" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>15606</v>
       </c>
       <c r="AA83" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>17587</v>
       </c>
     </row>
@@ -17301,11 +17304,11 @@
         <v>5499</v>
       </c>
       <c r="Z84" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>4352</v>
       </c>
       <c r="AA84" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>5496</v>
       </c>
     </row>
@@ -17338,11 +17341,11 @@
         <v>80</v>
       </c>
       <c r="Z85" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>1448</v>
       </c>
       <c r="AA85" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
     </row>
@@ -17375,11 +17378,11 @@
         <v>820</v>
       </c>
       <c r="Z86" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>382</v>
       </c>
       <c r="AA86" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>827</v>
       </c>
     </row>
@@ -17412,11 +17415,11 @@
         <v>3195</v>
       </c>
       <c r="Z87" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>3273</v>
       </c>
       <c r="AA87" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>3264</v>
       </c>
     </row>
@@ -17449,11 +17452,11 @@
         <v>5382</v>
       </c>
       <c r="Z88" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>4780</v>
       </c>
       <c r="AA88" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>5116</v>
       </c>
     </row>
@@ -17462,27 +17465,27 @@
         <v>577</v>
       </c>
       <c r="F89" s="2">
-        <f t="shared" ref="F89:K89" si="130">SUM(F82:F88)</f>
+        <f t="shared" ref="F89:K89" si="140">SUM(F82:F88)</f>
         <v>37741</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>37892</v>
       </c>
       <c r="H89" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>38003</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>40336</v>
       </c>
       <c r="J89" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>40892</v>
       </c>
       <c r="K89" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>41887</v>
       </c>
       <c r="L89" s="2">
@@ -17499,11 +17502,11 @@
       <c r="Q89" s="34"/>
       <c r="R89" s="34"/>
       <c r="Z89" s="2">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>37741</v>
       </c>
       <c r="AA89" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>40892</v>
       </c>
       <c r="AB89" s="34"/>
@@ -17599,11 +17602,11 @@
         <v>9729</v>
       </c>
       <c r="Z90" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>8380</v>
       </c>
       <c r="AA90" s="1">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>10593</v>
       </c>
     </row>
@@ -17612,27 +17615,27 @@
         <v>579</v>
       </c>
       <c r="F91" s="2">
-        <f t="shared" ref="F91:K91" si="131">F89+F90</f>
+        <f t="shared" ref="F91:K91" si="141">F89+F90</f>
         <v>46121</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>47872</v>
       </c>
       <c r="H91" s="2">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>48052</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>50853</v>
       </c>
       <c r="J91" s="2">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>51485</v>
       </c>
       <c r="K91" s="2">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>51559</v>
       </c>
       <c r="L91" s="2">
@@ -17649,11 +17652,11 @@
       <c r="Q91" s="34"/>
       <c r="R91" s="34"/>
       <c r="Z91" s="2">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>46121</v>
       </c>
       <c r="AA91" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>51485</v>
       </c>
       <c r="AB91" s="34"/>
@@ -17726,27 +17729,27 @@
         <v>73</v>
       </c>
       <c r="F93" s="39">
-        <f t="shared" ref="F93:K93" si="132">SUM(F67:F72)/SUM(F82:F85)</f>
+        <f t="shared" ref="F93:K93" si="142">SUM(F67:F72)/SUM(F82:F85)</f>
         <v>0.9359175595441207</v>
       </c>
       <c r="G93" s="39">
-        <f t="shared" si="132"/>
+        <f t="shared" si="142"/>
         <v>0.99078465916790892</v>
       </c>
       <c r="H93" s="39">
-        <f t="shared" si="132"/>
+        <f t="shared" si="142"/>
         <v>1.0569757440220195</v>
       </c>
       <c r="I93" s="39">
-        <f t="shared" si="132"/>
+        <f t="shared" si="142"/>
         <v>1.0610911885245902</v>
       </c>
       <c r="J93" s="39">
-        <f t="shared" si="132"/>
+        <f t="shared" si="142"/>
         <v>1.0779233075587817</v>
       </c>
       <c r="K93" s="39">
-        <f t="shared" si="132"/>
+        <f t="shared" si="142"/>
         <v>1.038560411311054</v>
       </c>
       <c r="L93" s="39">
@@ -17758,11 +17761,11 @@
         <v>1.0284920477418988</v>
       </c>
       <c r="Z93" s="39">
-        <f t="shared" ref="Z93:AA93" si="133">SUM(Z67:Z72)/SUM(Z82:Z85)</f>
+        <f t="shared" ref="Z93:AA93" si="143">SUM(Z67:Z72)/SUM(Z82:Z85)</f>
         <v>0.9359175595441207</v>
       </c>
       <c r="AA93" s="39">
-        <f t="shared" si="133"/>
+        <f t="shared" si="143"/>
         <v>1.0779233075587817</v>
       </c>
     </row>
@@ -17771,27 +17774,27 @@
         <v>74</v>
       </c>
       <c r="F94" s="39">
-        <f t="shared" ref="F94:K94" si="134">(SUM(F67:F72)-F69)/SUM(F82:F85)</f>
+        <f t="shared" ref="F94:K94" si="144">(SUM(F67:F72)-F69)/SUM(F82:F85)</f>
         <v>0.65430287313178193</v>
       </c>
       <c r="G94" s="39">
-        <f t="shared" si="134"/>
+        <f t="shared" si="144"/>
         <v>0.69064236346388397</v>
       </c>
       <c r="H94" s="39">
-        <f t="shared" si="134"/>
+        <f t="shared" si="144"/>
         <v>0.73542060897987271</v>
       </c>
       <c r="I94" s="39">
-        <f t="shared" si="134"/>
+        <f t="shared" si="144"/>
         <v>0.76085425204918034</v>
       </c>
       <c r="J94" s="39">
-        <f t="shared" si="134"/>
+        <f t="shared" si="144"/>
         <v>0.80691178791226137</v>
       </c>
       <c r="K94" s="39">
-        <f t="shared" si="134"/>
+        <f t="shared" si="144"/>
         <v>0.75835475578406175</v>
       </c>
       <c r="L94" s="39">
@@ -17803,11 +17806,11 @@
         <v>0.74408187565560058</v>
       </c>
       <c r="Z94" s="39">
-        <f t="shared" ref="Z94:AA94" si="135">(SUM(Z67:Z72)-Z69)/SUM(Z82:Z85)</f>
+        <f t="shared" ref="Z94:AA94" si="145">(SUM(Z67:Z72)-Z69)/SUM(Z82:Z85)</f>
         <v>0.65430287313178193</v>
       </c>
       <c r="AA94" s="39">
-        <f t="shared" si="135"/>
+        <f t="shared" si="145"/>
         <v>0.80691178791226137</v>
       </c>
     </row>
@@ -17816,27 +17819,27 @@
         <v>75</v>
       </c>
       <c r="F95" s="39">
-        <f t="shared" ref="F95:K95" si="136">F67/SUM(F82:F85)</f>
+        <f t="shared" ref="F95:K95" si="146">F67/SUM(F82:F85)</f>
         <v>5.2924315839759775E-2</v>
       </c>
       <c r="G95" s="39">
-        <f t="shared" si="136"/>
+        <f t="shared" si="146"/>
         <v>0.11027917061932511</v>
       </c>
       <c r="H95" s="39">
-        <f t="shared" si="136"/>
+        <f t="shared" si="146"/>
         <v>0.19883020815413727</v>
       </c>
       <c r="I95" s="39">
-        <f t="shared" si="136"/>
+        <f t="shared" si="146"/>
         <v>0.23677638319672131</v>
       </c>
       <c r="J95" s="39">
-        <f t="shared" si="136"/>
+        <f t="shared" si="146"/>
         <v>0.25895534164431117</v>
       </c>
       <c r="K95" s="39">
-        <f t="shared" si="136"/>
+        <f t="shared" si="146"/>
         <v>0.24810258293548781</v>
       </c>
       <c r="L95" s="39">
@@ -17848,11 +17851,11 @@
         <v>0.22524310379043461</v>
       </c>
       <c r="Z95" s="39">
-        <f t="shared" ref="Z95:AA95" si="137">Z67/SUM(Z82:Z85)</f>
+        <f t="shared" ref="Z95:AA95" si="147">Z67/SUM(Z82:Z85)</f>
         <v>5.2924315839759775E-2</v>
       </c>
       <c r="AA95" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="147"/>
         <v>0.25895534164431117</v>
       </c>
     </row>
@@ -17861,27 +17864,27 @@
         <v>76</v>
       </c>
       <c r="F96" s="39">
-        <f t="shared" ref="F96:K96" si="138">F41/F91</f>
+        <f t="shared" ref="F96:K96" si="148">F41/F91</f>
         <v>0.21781834739055961</v>
       </c>
       <c r="G96" s="39">
-        <f t="shared" si="138"/>
+        <f t="shared" si="148"/>
         <v>0.15163352272727273</v>
       </c>
       <c r="H96" s="39">
-        <f t="shared" si="138"/>
+        <f t="shared" si="148"/>
         <v>0.17073170731707318</v>
       </c>
       <c r="I96" s="39">
-        <f t="shared" si="138"/>
+        <f t="shared" si="148"/>
         <v>0.17526989558138162</v>
       </c>
       <c r="J96" s="39">
-        <f t="shared" si="138"/>
+        <f t="shared" si="148"/>
         <v>0.2050888608332524</v>
       </c>
       <c r="K96" s="39">
-        <f t="shared" si="138"/>
+        <f t="shared" si="148"/>
         <v>0.15578269555266783</v>
       </c>
       <c r="L96" s="39">
@@ -17893,11 +17896,11 @@
         <v>0.18325704516627145</v>
       </c>
       <c r="Z96" s="39">
-        <f t="shared" ref="Z96:AA96" si="139">Z41/Z91</f>
+        <f t="shared" ref="Z96:AA96" si="149">Z41/Z91</f>
         <v>0.72069122525530671</v>
       </c>
       <c r="AA96" s="39">
-        <f t="shared" si="139"/>
+        <f t="shared" si="149"/>
         <v>0.67854714965523943</v>
       </c>
     </row>
@@ -17906,27 +17909,27 @@
         <v>77</v>
       </c>
       <c r="F97" s="39">
-        <f t="shared" ref="F97:K97" si="140">F69/AVERAGE(SUM(C44:F44))</f>
+        <f t="shared" ref="F97:K97" si="150">F69/AVERAGE(SUM(C44:F44))</f>
         <v>0.29038387108124275</v>
       </c>
       <c r="G97" s="39">
-        <f t="shared" si="140"/>
+        <f t="shared" si="150"/>
         <v>0.30946309428162222</v>
       </c>
       <c r="H97" s="39">
-        <f t="shared" si="140"/>
+        <f t="shared" si="150"/>
         <v>0.33192456582732538</v>
       </c>
       <c r="I97" s="39">
-        <f t="shared" si="140"/>
+        <f t="shared" si="150"/>
         <v>0.32604311543810849</v>
       </c>
       <c r="J97" s="39">
-        <f t="shared" si="140"/>
+        <f t="shared" si="150"/>
         <v>0.29764298093587521</v>
       </c>
       <c r="K97" s="39">
-        <f t="shared" si="140"/>
+        <f t="shared" si="150"/>
         <v>0.31245947513906425</v>
       </c>
       <c r="L97" s="39">
@@ -17938,11 +17941,11 @@
         <v>0.3307289091088913</v>
       </c>
       <c r="Z97" s="39">
-        <f t="shared" ref="Z97:AA97" si="141">Z69/AVERAGE(SUM(W42:Z43))</f>
+        <f t="shared" ref="Z97:AA97" si="151">Z69/AVERAGE(SUM(W42:Z43))</f>
         <v>0.15110679824962925</v>
       </c>
       <c r="AA97" s="39">
-        <f t="shared" si="141"/>
+        <f t="shared" si="151"/>
         <v>0.10287898211269124</v>
       </c>
     </row>
@@ -17951,27 +17954,27 @@
         <v>78</v>
       </c>
       <c r="F98" s="63">
-        <f t="shared" ref="F98:K98" si="142">F54/F91</f>
+        <f t="shared" ref="F98:K98" si="152">F54/F91</f>
         <v>4.2713731272088634E-3</v>
       </c>
       <c r="G98" s="63">
-        <f t="shared" si="142"/>
+        <f t="shared" si="152"/>
         <v>-2.7155748663101604E-3</v>
       </c>
       <c r="H98" s="63">
-        <f t="shared" si="142"/>
+        <f t="shared" si="152"/>
         <v>2.6929160076583702E-2</v>
       </c>
       <c r="I98" s="63">
-        <f t="shared" si="142"/>
+        <f t="shared" si="152"/>
         <v>-1.8877942304288832E-3</v>
       </c>
       <c r="J98" s="63">
-        <f t="shared" si="142"/>
+        <f t="shared" si="152"/>
         <v>9.4202194814023508E-3</v>
       </c>
       <c r="K98" s="63">
-        <f t="shared" si="142"/>
+        <f t="shared" si="152"/>
         <v>4.9263950037820746E-3</v>
       </c>
       <c r="L98" s="63">
@@ -17983,11 +17986,11 @@
         <v>8.32735895880439E-3</v>
       </c>
       <c r="Z98" s="63">
-        <f t="shared" ref="Z98:AA98" si="143">Z54/Z91</f>
+        <f t="shared" ref="Z98:AA98" si="153">Z54/Z91</f>
         <v>-9.4967585264846815E-3</v>
       </c>
       <c r="AA98" s="63">
-        <f t="shared" si="143"/>
+        <f t="shared" si="153"/>
         <v>3.0164125473438864E-2</v>
       </c>
     </row>
@@ -17996,27 +17999,27 @@
         <v>79</v>
       </c>
       <c r="F99" s="63">
-        <f t="shared" ref="F99:K99" si="144">F54/F90</f>
+        <f t="shared" ref="F99:K99" si="154">F54/F90</f>
         <v>2.3508353221957042E-2</v>
       </c>
       <c r="G99" s="63">
-        <f t="shared" si="144"/>
+        <f t="shared" si="154"/>
         <v>-1.3026052104208416E-2</v>
       </c>
       <c r="H99" s="63">
-        <f t="shared" si="144"/>
+        <f t="shared" si="154"/>
         <v>0.12876903174445217</v>
       </c>
       <c r="I99" s="63">
-        <f t="shared" si="144"/>
+        <f t="shared" si="154"/>
         <v>-9.1280783493391648E-3</v>
       </c>
       <c r="J99" s="63">
-        <f t="shared" si="144"/>
+        <f t="shared" si="154"/>
         <v>4.5784952327008403E-2</v>
       </c>
       <c r="K99" s="63">
-        <f t="shared" si="144"/>
+        <f t="shared" si="154"/>
         <v>2.6261373035566585E-2</v>
       </c>
       <c r="L99" s="63">
@@ -18028,11 +18031,11 @@
         <v>4.6561825470243602E-2</v>
       </c>
       <c r="Z99" s="63">
-        <f t="shared" ref="Z99:AA99" si="145">Z54/Z90</f>
+        <f t="shared" ref="Z99:AA99" si="155">Z54/Z90</f>
         <v>-5.2267303102625298E-2</v>
       </c>
       <c r="AA99" s="63">
-        <f t="shared" si="145"/>
+        <f t="shared" si="155"/>
         <v>0.14660624940998773</v>
       </c>
     </row>
@@ -18042,39 +18045,39 @@
         <v>80</v>
       </c>
       <c r="C101" s="1">
-        <f t="shared" ref="C101:K101" si="146">C54</f>
+        <f t="shared" ref="C101:K101" si="156">C54</f>
         <v>-315</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>-150</v>
       </c>
       <c r="E101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>-170</v>
       </c>
       <c r="F101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>197</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>-130</v>
       </c>
       <c r="H101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>1294</v>
       </c>
       <c r="I101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>-96</v>
       </c>
       <c r="J101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>485</v>
       </c>
       <c r="K101" s="1">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>254</v>
       </c>
       <c r="L101" s="1">
@@ -18086,11 +18089,11 @@
         <v>453</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" ref="Z101:Z104" si="147">SUM(C101:F101)</f>
+        <f t="shared" ref="Z101:Z104" si="157">SUM(C101:F101)</f>
         <v>-438</v>
       </c>
       <c r="AA101" s="1">
-        <f t="shared" ref="AA101:AA104" si="148">SUM(G101:J101)</f>
+        <f t="shared" ref="AA101:AA104" si="158">SUM(G101:J101)</f>
         <v>1553</v>
       </c>
     </row>
@@ -18138,11 +18141,11 @@
       <c r="Q102" s="34"/>
       <c r="R102" s="34"/>
       <c r="Z102" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="157"/>
         <v>1188</v>
       </c>
       <c r="AA102" s="2">
-        <f t="shared" si="148"/>
+        <f t="shared" si="158"/>
         <v>2583</v>
       </c>
       <c r="AB102" s="34"/>
@@ -18247,11 +18250,11 @@
         <v>-247</v>
       </c>
       <c r="Z103" s="1">
-        <f t="shared" si="147"/>
+        <f t="shared" si="157"/>
         <v>-744</v>
       </c>
       <c r="AA103" s="1">
-        <f t="shared" si="148"/>
+        <f t="shared" si="158"/>
         <v>-883</v>
       </c>
     </row>
@@ -18264,43 +18267,43 @@
         <v>-814</v>
       </c>
       <c r="D104" s="2">
-        <f t="shared" ref="D104:L104" si="149">D102+D103</f>
+        <f t="shared" ref="D104:L104" si="159">D102+D103</f>
         <v>-447</v>
       </c>
       <c r="E104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>51</v>
       </c>
       <c r="F104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>1654</v>
       </c>
       <c r="G104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>-661</v>
       </c>
       <c r="H104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>825</v>
       </c>
       <c r="I104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>964</v>
       </c>
       <c r="J104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>572</v>
       </c>
       <c r="K104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>974</v>
       </c>
       <c r="L104" s="2">
-        <f t="shared" si="149"/>
+        <f t="shared" si="159"/>
         <v>194</v>
       </c>
       <c r="M104" s="2">
-        <f t="shared" ref="M104" si="150">M102+M103</f>
+        <f t="shared" ref="M104" si="160">M102+M103</f>
         <v>734</v>
       </c>
       <c r="N104" s="34"/>
@@ -18309,11 +18312,11 @@
       <c r="Q104" s="34"/>
       <c r="R104" s="34"/>
       <c r="Z104" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="157"/>
         <v>444</v>
       </c>
       <c r="AA104" s="2">
-        <f t="shared" si="148"/>
+        <f t="shared" si="158"/>
         <v>1700</v>
       </c>
       <c r="AB104" s="34"/>
@@ -18385,39 +18388,39 @@
         <v>84</v>
       </c>
       <c r="C105" s="1">
-        <f t="shared" ref="C105:K105" si="151">C55</f>
+        <f t="shared" ref="C105:K105" si="161">C55</f>
         <v>274</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>274</v>
       </c>
       <c r="E105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>274</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>274</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>274</v>
       </c>
       <c r="H105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>274</v>
       </c>
       <c r="I105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>275</v>
       </c>
       <c r="J105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>275</v>
       </c>
       <c r="K105" s="1">
-        <f t="shared" si="151"/>
+        <f t="shared" si="161"/>
         <v>275</v>
       </c>
       <c r="L105" s="1">
@@ -18446,43 +18449,43 @@
         <v>-2.9708029197080292</v>
       </c>
       <c r="D106" s="39">
-        <f t="shared" ref="D106:L106" si="152">D104/D105</f>
+        <f t="shared" ref="D106:L106" si="162">D104/D105</f>
         <v>-1.6313868613138687</v>
       </c>
       <c r="E106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>0.18613138686131386</v>
       </c>
       <c r="F106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>6.0364963503649633</v>
       </c>
       <c r="G106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>-2.4124087591240877</v>
       </c>
       <c r="H106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>3.0109489051094891</v>
       </c>
       <c r="I106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>3.5054545454545454</v>
       </c>
       <c r="J106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>2.08</v>
       </c>
       <c r="K106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>3.541818181818182</v>
       </c>
       <c r="L106" s="39">
-        <f t="shared" si="152"/>
+        <f t="shared" si="162"/>
         <v>0.71323529411764708</v>
       </c>
       <c r="M106" s="39">
-        <f t="shared" ref="M106" si="153">M104/M105</f>
+        <f t="shared" ref="M106" si="163">M104/M105</f>
         <v>2.6985294117647061</v>
       </c>
       <c r="Z106" s="39">

--- a/GEV_Model.xlsx
+++ b/GEV_Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Industrial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Industrials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA5DFA4-8F72-4870-BF93-28C796BF0998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C56978-8308-4E34-A25F-46AA1D03A8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1953,7 +1953,7 @@
     <t>Electrification Software</t>
   </si>
   <si>
-    <t>12/29/25</t>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -7596,7 +7596,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$Z$54:$AA$54</c:f>
+              <c:f>Model!$X$54:$Y$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -7708,7 +7708,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$Z$104:$AA$104</c:f>
+              <c:f>Model!$X$104:$Y$104</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -7756,7 +7756,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Model!$Z$3:$AA$3</c:f>
+              <c:f>Model!$X$3:$Y$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -7771,7 +7771,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$Z$41:$AA$41</c:f>
+              <c:f>Model!$X$41:$Y$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -9216,13 +9216,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>110</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -10439,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="73">
-        <v>663.16</v>
+        <v>622.65</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>609</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="C5" s="72">
         <f>C3*C4</f>
-        <v>179928.57119999998</v>
+        <v>168937.39799999999</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C8" s="72">
         <f>C5-C6+C7</f>
-        <v>171983.57119999998</v>
+        <v>160992.39799999999</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15">
@@ -10728,28 +10728,25 @@
     <hyperlink ref="Q13" r:id="rId3" xr:uid="{F5D8B61A-D6AC-4492-A18C-0BC09C1A4F05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B27957-A42B-4AB7-A411-12A70E029F5D}">
-  <dimension ref="B1:CM115"/>
+  <dimension ref="B1:CK115"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.42578125" style="1" customWidth="1"/>
     <col min="3" max="13" width="9.140625" style="1"/>
     <col min="14" max="18" width="9.140625" style="35"/>
-    <col min="19" max="27" width="9.140625" style="1"/>
-    <col min="28" max="90" width="9.140625" style="35"/>
-    <col min="91" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="25" width="9.140625" style="1"/>
+    <col min="26" max="88" width="9.140625" style="35"/>
+    <col min="89" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:91" ht="15">
+    <row r="1" spans="2:89" ht="15">
       <c r="B1" s="1" t="s">
         <v>60</v>
       </c>
@@ -10763,12 +10760,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="2:91">
+    <row r="2" spans="2:89">
       <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="2:91" ht="15">
+    <row r="3" spans="2:89" ht="15">
       <c r="B3" s="2" t="s">
         <v>62</v>
       </c>
@@ -10820,265 +10817,265 @@
       <c r="R3" s="34" t="s">
         <v>59</v>
       </c>
+      <c r="W3" s="2">
+        <v>2022</v>
+      </c>
+      <c r="X3" s="2">
+        <v>2023</v>
+      </c>
       <c r="Y3" s="2">
-        <v>2022</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>2023</v>
-      </c>
-      <c r="AA3" s="2">
         <f>2023+1</f>
         <v>2024</v>
       </c>
+      <c r="Z3" s="34">
+        <f t="shared" ref="Z3:BW3" si="0">Y3+1</f>
+        <v>2025</v>
+      </c>
+      <c r="AA3" s="34">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
       <c r="AB3" s="34">
-        <f t="shared" ref="AB3:BY3" si="0">AA3+1</f>
-        <v>2025</v>
+        <f t="shared" si="0"/>
+        <v>2027</v>
       </c>
       <c r="AC3" s="34">
         <f t="shared" si="0"/>
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="AD3" s="34">
         <f t="shared" si="0"/>
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="AE3" s="34">
         <f t="shared" si="0"/>
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="AF3" s="34">
         <f t="shared" si="0"/>
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="AG3" s="34">
         <f t="shared" si="0"/>
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="AH3" s="34">
         <f t="shared" si="0"/>
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="AI3" s="34">
         <f t="shared" si="0"/>
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="AJ3" s="34">
         <f t="shared" si="0"/>
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="AK3" s="34">
         <f t="shared" si="0"/>
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="AL3" s="34">
         <f t="shared" si="0"/>
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="AM3" s="34">
         <f t="shared" si="0"/>
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="AN3" s="34">
         <f t="shared" si="0"/>
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="AO3" s="34">
         <f t="shared" si="0"/>
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="AP3" s="34">
         <f t="shared" si="0"/>
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="AQ3" s="34">
         <f t="shared" si="0"/>
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="AR3" s="34">
         <f t="shared" si="0"/>
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="AS3" s="34">
         <f t="shared" si="0"/>
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="AT3" s="34">
         <f t="shared" si="0"/>
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="AU3" s="34">
         <f t="shared" si="0"/>
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="AV3" s="34">
         <f t="shared" si="0"/>
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="AW3" s="34">
         <f t="shared" si="0"/>
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="AX3" s="34">
         <f t="shared" si="0"/>
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="AY3" s="34">
         <f t="shared" si="0"/>
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="AZ3" s="34">
         <f t="shared" si="0"/>
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="BA3" s="34">
         <f t="shared" si="0"/>
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="BB3" s="34">
         <f t="shared" si="0"/>
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="BC3" s="34">
         <f t="shared" si="0"/>
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="BD3" s="34">
         <f t="shared" si="0"/>
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="BE3" s="34">
         <f t="shared" si="0"/>
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="BF3" s="34">
         <f t="shared" si="0"/>
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="BG3" s="34">
         <f t="shared" si="0"/>
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="BH3" s="34">
         <f t="shared" si="0"/>
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="BI3" s="34">
         <f t="shared" si="0"/>
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="BJ3" s="34">
         <f t="shared" si="0"/>
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="BK3" s="34">
         <f t="shared" si="0"/>
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="BL3" s="34">
         <f t="shared" si="0"/>
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="BM3" s="34">
         <f t="shared" si="0"/>
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="BN3" s="34">
         <f t="shared" si="0"/>
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="BO3" s="34">
         <f t="shared" si="0"/>
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="BP3" s="34">
         <f t="shared" si="0"/>
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="BQ3" s="34">
         <f t="shared" si="0"/>
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="BR3" s="34">
         <f t="shared" si="0"/>
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="BS3" s="34">
         <f t="shared" si="0"/>
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="BT3" s="34">
         <f t="shared" si="0"/>
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="BU3" s="34">
         <f t="shared" si="0"/>
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="BV3" s="34">
         <f t="shared" si="0"/>
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="BW3" s="34">
         <f t="shared" si="0"/>
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="BX3" s="34">
-        <f t="shared" si="0"/>
-        <v>2073</v>
+        <f t="shared" ref="BX3:CH3" si="1">BW3+1</f>
+        <v>2075</v>
       </c>
       <c r="BY3" s="34">
-        <f t="shared" si="0"/>
-        <v>2074</v>
+        <f t="shared" si="1"/>
+        <v>2076</v>
       </c>
       <c r="BZ3" s="34">
-        <f t="shared" ref="BZ3:CJ3" si="1">BY3+1</f>
-        <v>2075</v>
+        <f t="shared" si="1"/>
+        <v>2077</v>
       </c>
       <c r="CA3" s="34">
         <f t="shared" si="1"/>
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="CB3" s="34">
         <f t="shared" si="1"/>
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="CC3" s="34">
         <f t="shared" si="1"/>
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="CD3" s="34">
         <f t="shared" si="1"/>
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="CE3" s="34">
         <f t="shared" si="1"/>
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="CF3" s="34">
         <f t="shared" si="1"/>
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="CG3" s="34">
         <f t="shared" si="1"/>
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="CH3" s="34">
         <f t="shared" si="1"/>
-        <v>2083</v>
-      </c>
-      <c r="CI3" s="34">
-        <f t="shared" si="1"/>
-        <v>2084</v>
-      </c>
-      <c r="CJ3" s="34">
-        <f t="shared" si="1"/>
         <v>2085</v>
       </c>
-      <c r="CK3" s="34"/>
-      <c r="CL3" s="34"/>
-      <c r="CM3" s="2"/>
-    </row>
-    <row r="4" spans="2:91">
+      <c r="CI3" s="34"/>
+      <c r="CJ3" s="34"/>
+      <c r="CK3" s="2"/>
+    </row>
+    <row r="4" spans="2:89">
       <c r="B4" s="36" t="s">
         <v>542</v>
       </c>
@@ -11117,63 +11114,63 @@
       <c r="M4" s="1">
         <v>5880</v>
       </c>
-      <c r="Y4" s="1">
+      <c r="W4" s="1">
         <v>15819</v>
       </c>
-      <c r="Z4" s="1">
+      <c r="X4" s="1">
         <f>SUM(C4:F4)</f>
         <v>18258</v>
       </c>
-      <c r="AA4" s="1">
+      <c r="Y4" s="1">
         <f>SUM(G4:J4)</f>
         <v>18952</v>
       </c>
+      <c r="Z4" s="70">
+        <f t="shared" ref="Z4:AJ4" si="2">Y4*(1+Z8)</f>
+        <v>21557.899999999998</v>
+      </c>
+      <c r="AA4" s="70">
+        <f t="shared" si="2"/>
+        <v>25718.574699999997</v>
+      </c>
       <c r="AB4" s="70">
-        <f t="shared" ref="AB4:AL4" si="2">AA4*(1+AB8)</f>
-        <v>21557.899999999998</v>
+        <f t="shared" si="2"/>
+        <v>30733.696766499997</v>
       </c>
       <c r="AC4" s="70">
         <f t="shared" si="2"/>
-        <v>25718.574699999997</v>
+        <v>36680.667090817748</v>
       </c>
       <c r="AD4" s="70">
         <f t="shared" si="2"/>
-        <v>30733.696766499997</v>
+        <v>42402.851156985314</v>
       </c>
       <c r="AE4" s="70">
         <f t="shared" si="2"/>
-        <v>36680.667090817748</v>
+        <v>47872.81895623642</v>
       </c>
       <c r="AF4" s="70">
         <f t="shared" si="2"/>
-        <v>42402.851156985314</v>
+        <v>51702.644472735337</v>
       </c>
       <c r="AG4" s="70">
         <f t="shared" si="2"/>
-        <v>47872.81895623642</v>
+        <v>54804.803141099459</v>
       </c>
       <c r="AH4" s="70">
         <f t="shared" si="2"/>
-        <v>51702.644472735337</v>
+        <v>56996.995266743441</v>
       </c>
       <c r="AI4" s="70">
         <f t="shared" si="2"/>
-        <v>54804.803141099459</v>
+        <v>58706.905124745746</v>
       </c>
       <c r="AJ4" s="70">
         <f t="shared" si="2"/>
-        <v>56996.995266743441</v>
-      </c>
-      <c r="AK4" s="70">
-        <f t="shared" si="2"/>
-        <v>58706.905124745746</v>
-      </c>
-      <c r="AL4" s="70">
-        <f t="shared" si="2"/>
         <v>59881.043227240662</v>
       </c>
     </row>
-    <row r="5" spans="2:91">
+    <row r="5" spans="2:89">
       <c r="B5" s="36" t="s">
         <v>543</v>
       </c>
@@ -11212,63 +11209,63 @@
       <c r="M5" s="1">
         <v>4089</v>
       </c>
-      <c r="Y5" s="1">
+      <c r="W5" s="1">
         <v>13835</v>
       </c>
-      <c r="Z5" s="1">
+      <c r="X5" s="1">
         <f>SUM(C5:F5)</f>
         <v>14981</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="Y5" s="1">
         <f>SUM(G5:J5)</f>
         <v>15983</v>
       </c>
+      <c r="Z5" s="70">
+        <f t="shared" ref="Z5:AJ5" si="3">Y5*(1+Z9)</f>
+        <v>16814.116000000002</v>
+      </c>
+      <c r="AA5" s="70">
+        <f t="shared" si="3"/>
+        <v>18293.758208000003</v>
+      </c>
       <c r="AB5" s="70">
-        <f t="shared" ref="AB5:AL5" si="3">AA5*(1+AB9)</f>
-        <v>16814.116000000002</v>
+        <f t="shared" si="3"/>
+        <v>20287.777852672003</v>
       </c>
       <c r="AC5" s="70">
         <f t="shared" si="3"/>
-        <v>18293.758208000003</v>
+        <v>22499.145638613252</v>
       </c>
       <c r="AD5" s="70">
         <f t="shared" si="3"/>
-        <v>20287.777852672003</v>
+        <v>25829.019193128013</v>
       </c>
       <c r="AE5" s="70">
         <f t="shared" si="3"/>
-        <v>22499.145638613252</v>
+        <v>29845.431677659417</v>
       </c>
       <c r="AF5" s="70">
         <f t="shared" si="3"/>
-        <v>25829.019193128013</v>
+        <v>34322.246429308325</v>
       </c>
       <c r="AG5" s="70">
         <f t="shared" si="3"/>
-        <v>29845.431677659417</v>
+        <v>39127.360929411494</v>
       </c>
       <c r="AH5" s="70">
         <f t="shared" si="3"/>
-        <v>34322.246429308325</v>
+        <v>42257.549803764414</v>
       </c>
       <c r="AI5" s="70">
         <f t="shared" si="3"/>
-        <v>39127.360929411494</v>
+        <v>45215.578290027923</v>
       </c>
       <c r="AJ5" s="70">
         <f t="shared" si="3"/>
-        <v>42257.549803764414</v>
-      </c>
-      <c r="AK5" s="70">
-        <f t="shared" si="3"/>
-        <v>45215.578290027923</v>
-      </c>
-      <c r="AL5" s="70">
-        <f t="shared" si="3"/>
         <v>47476.357204529319</v>
       </c>
     </row>
-    <row r="6" spans="2:91" s="2" customFormat="1" ht="15">
+    <row r="6" spans="2:89" s="2" customFormat="1" ht="15">
       <c r="B6" s="33" t="s">
         <v>63</v>
       </c>
@@ -11321,62 +11318,64 @@
       <c r="P6" s="34"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
-      <c r="Y6" s="2">
-        <f>SUM(Y4:Y5)</f>
+      <c r="W6" s="2">
+        <f>SUM(W4:W5)</f>
         <v>29654</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="X6" s="2">
         <f>SUM(C6:F6)</f>
         <v>33239</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="Y6" s="2">
         <f>SUM(G6:J6)</f>
         <v>34935</v>
       </c>
+      <c r="Z6" s="71">
+        <f t="shared" ref="Z6:AJ6" si="9">SUM(Z4:Z5)</f>
+        <v>38372.016000000003</v>
+      </c>
+      <c r="AA6" s="71">
+        <f t="shared" si="9"/>
+        <v>44012.332907999997</v>
+      </c>
       <c r="AB6" s="71">
-        <f t="shared" ref="AB6:AL6" si="9">SUM(AB4:AB5)</f>
-        <v>38372.016000000003</v>
+        <f t="shared" si="9"/>
+        <v>51021.474619172004</v>
       </c>
       <c r="AC6" s="71">
         <f t="shared" si="9"/>
-        <v>44012.332907999997</v>
+        <v>59179.812729430996</v>
       </c>
       <c r="AD6" s="71">
         <f t="shared" si="9"/>
-        <v>51021.474619172004</v>
+        <v>68231.870350113328</v>
       </c>
       <c r="AE6" s="71">
         <f t="shared" si="9"/>
-        <v>59179.812729430996</v>
+        <v>77718.250633895834</v>
       </c>
       <c r="AF6" s="71">
         <f t="shared" si="9"/>
-        <v>68231.870350113328</v>
+        <v>86024.890902043669</v>
       </c>
       <c r="AG6" s="71">
         <f t="shared" si="9"/>
-        <v>77718.250633895834</v>
+        <v>93932.164070510946</v>
       </c>
       <c r="AH6" s="71">
         <f t="shared" si="9"/>
-        <v>86024.890902043669</v>
+        <v>99254.545070507855</v>
       </c>
       <c r="AI6" s="71">
         <f t="shared" si="9"/>
-        <v>93932.164070510946</v>
+        <v>103922.48341477367</v>
       </c>
       <c r="AJ6" s="71">
         <f t="shared" si="9"/>
-        <v>99254.545070507855</v>
-      </c>
-      <c r="AK6" s="71">
-        <f t="shared" si="9"/>
-        <v>103922.48341477367</v>
-      </c>
-      <c r="AL6" s="71">
-        <f t="shared" si="9"/>
         <v>107357.40043176999</v>
       </c>
+      <c r="AK6" s="34"/>
+      <c r="AL6" s="34"/>
       <c r="AM6" s="34"/>
       <c r="AN6" s="34"/>
       <c r="AO6" s="34"/>
@@ -11427,13 +11426,11 @@
       <c r="CH6" s="34"/>
       <c r="CI6" s="34"/>
       <c r="CJ6" s="34"/>
-      <c r="CK6" s="34"/>
-      <c r="CL6" s="34"/>
-    </row>
-    <row r="7" spans="2:91">
+    </row>
+    <row r="7" spans="2:89">
       <c r="B7" s="36"/>
     </row>
-    <row r="8" spans="2:91">
+    <row r="8" spans="2:89">
       <c r="B8" s="36" t="s">
         <v>582</v>
       </c>
@@ -11465,49 +11462,49 @@
         <f t="shared" si="11"/>
         <v>0.11153119092627595</v>
       </c>
-      <c r="Z8" s="63">
-        <f t="shared" ref="Z8:AA10" si="12">Z4/Y4-1</f>
+      <c r="X8" s="63">
+        <f t="shared" ref="X8:Y10" si="12">X4/W4-1</f>
         <v>0.15418168025791767</v>
       </c>
-      <c r="AA8" s="63">
+      <c r="Y8" s="63">
         <f t="shared" si="12"/>
         <v>3.8010735020265196E-2</v>
       </c>
+      <c r="Z8" s="65">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="AA8" s="65">
+        <v>0.193</v>
+      </c>
       <c r="AB8" s="65">
-        <v>0.13750000000000001</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="AC8" s="65">
-        <v>0.193</v>
+        <v>0.19350000000000001</v>
       </c>
       <c r="AD8" s="65">
-        <v>0.19500000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="AE8" s="65">
-        <v>0.19350000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="AF8" s="65">
-        <v>0.156</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" s="65">
-        <v>0.129</v>
+        <v>0.06</v>
       </c>
       <c r="AH8" s="65">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AI8" s="65">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AJ8" s="65">
-        <v>0.04</v>
-      </c>
-      <c r="AK8" s="65">
-        <v>0.03</v>
-      </c>
-      <c r="AL8" s="65">
         <v>0.02</v>
       </c>
     </row>
-    <row r="9" spans="2:91">
+    <row r="9" spans="2:89">
       <c r="B9" s="36" t="s">
         <v>583</v>
       </c>
@@ -11539,49 +11536,49 @@
         <f t="shared" si="11"/>
         <v>0.12862268837979585</v>
       </c>
-      <c r="Z9" s="63">
+      <c r="X9" s="63">
         <f t="shared" si="12"/>
         <v>8.2833393567040225E-2</v>
       </c>
-      <c r="AA9" s="63">
+      <c r="Y9" s="63">
         <f t="shared" si="12"/>
         <v>6.6884720646151807E-2</v>
       </c>
+      <c r="Z9" s="65">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AA9" s="65">
+        <v>8.7999999999999995E-2</v>
+      </c>
       <c r="AB9" s="65">
-        <v>5.1999999999999998E-2</v>
+        <v>0.109</v>
       </c>
       <c r="AC9" s="65">
-        <v>8.7999999999999995E-2</v>
+        <v>0.109</v>
       </c>
       <c r="AD9" s="65">
-        <v>0.109</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="AE9" s="65">
-        <v>0.109</v>
+        <v>0.1555</v>
       </c>
       <c r="AF9" s="65">
-        <v>0.14799999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="AG9" s="65">
-        <v>0.1555</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AH9" s="65">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="AI9" s="65">
-        <v>0.14000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AJ9" s="65">
-        <v>0.08</v>
-      </c>
-      <c r="AK9" s="65">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AL9" s="65">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="2:91" s="2" customFormat="1" ht="15">
+    <row r="10" spans="2:89" s="2" customFormat="1" ht="15">
       <c r="B10" s="33" t="s">
         <v>116</v>
       </c>
@@ -11618,58 +11615,60 @@
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="34"/>
-      <c r="Z10" s="64">
+      <c r="X10" s="64">
         <f t="shared" si="12"/>
         <v>0.12089431442638432</v>
       </c>
-      <c r="AA10" s="64">
+      <c r="Y10" s="64">
         <f t="shared" si="12"/>
         <v>5.1024399049309554E-2</v>
       </c>
+      <c r="Z10" s="66">
+        <f t="shared" ref="Z10:AJ10" si="15">Z6/Y6-1</f>
+        <v>9.8383168741949412E-2</v>
+      </c>
+      <c r="AA10" s="66">
+        <f t="shared" si="15"/>
+        <v>0.14699037204612853</v>
+      </c>
       <c r="AB10" s="66">
-        <f t="shared" ref="AB10:AL10" si="15">AB6/AA6-1</f>
-        <v>9.8383168741949412E-2</v>
+        <f t="shared" si="15"/>
+        <v>0.15925403740409272</v>
       </c>
       <c r="AC10" s="66">
         <f t="shared" si="15"/>
-        <v>0.14699037204612853</v>
+        <v>0.1599000846438372</v>
       </c>
       <c r="AD10" s="66">
         <f t="shared" si="15"/>
-        <v>0.15925403740409272</v>
+        <v>0.15295853777145552</v>
       </c>
       <c r="AE10" s="66">
         <f t="shared" si="15"/>
-        <v>0.1599000846438372</v>
+        <v>0.1390315146735055</v>
       </c>
       <c r="AF10" s="66">
         <f t="shared" si="15"/>
-        <v>0.15295853777145552</v>
+        <v>0.10688146220992012</v>
       </c>
       <c r="AG10" s="66">
         <f t="shared" si="15"/>
-        <v>0.1390315146735055</v>
+        <v>9.1918432973908226E-2</v>
       </c>
       <c r="AH10" s="66">
         <f t="shared" si="15"/>
-        <v>0.10688146220992012</v>
+        <v>5.6661965075153864E-2</v>
       </c>
       <c r="AI10" s="66">
         <f t="shared" si="15"/>
-        <v>9.1918432973908226E-2</v>
+        <v>4.7029970677411548E-2</v>
       </c>
       <c r="AJ10" s="66">
         <f t="shared" si="15"/>
-        <v>5.6661965075153864E-2</v>
-      </c>
-      <c r="AK10" s="66">
-        <f t="shared" si="15"/>
-        <v>4.7029970677411548E-2</v>
-      </c>
-      <c r="AL10" s="66">
-        <f t="shared" si="15"/>
         <v>3.3052684117323539E-2</v>
       </c>
+      <c r="AK10" s="34"/>
+      <c r="AL10" s="34"/>
       <c r="AM10" s="34"/>
       <c r="AN10" s="34"/>
       <c r="AO10" s="34"/>
@@ -11720,10 +11719,8 @@
       <c r="CH10" s="34"/>
       <c r="CI10" s="34"/>
       <c r="CJ10" s="34"/>
-      <c r="CK10" s="34"/>
-      <c r="CL10" s="34"/>
-    </row>
-    <row r="11" spans="2:91">
+    </row>
+    <row r="11" spans="2:89">
       <c r="G11" s="63"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -11731,7 +11728,9 @@
       <c r="K11" s="63"/>
       <c r="L11" s="63"/>
       <c r="M11" s="63"/>
-      <c r="AA11" s="63"/>
+      <c r="Y11" s="63"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
       <c r="AB11" s="65"/>
       <c r="AC11" s="65"/>
       <c r="AD11" s="65"/>
@@ -11741,10 +11740,8 @@
       <c r="AH11" s="65"/>
       <c r="AI11" s="65"/>
       <c r="AJ11" s="65"/>
-      <c r="AK11" s="65"/>
-      <c r="AL11" s="65"/>
-    </row>
-    <row r="12" spans="2:91" ht="15">
+    </row>
+    <row r="12" spans="2:89" ht="15">
       <c r="B12" s="33" t="s">
         <v>584</v>
       </c>
@@ -11792,64 +11789,64 @@
         <f>M4/M6</f>
         <v>0.58982846825157986</v>
       </c>
+      <c r="W12" s="63">
+        <f>W4/W6</f>
+        <v>0.53345248533081535</v>
+      </c>
+      <c r="X12" s="63">
+        <f>X4/X6</f>
+        <v>0.54929450344474862</v>
+      </c>
       <c r="Y12" s="63">
         <f>Y4/Y6</f>
-        <v>0.53345248533081535</v>
-      </c>
-      <c r="Z12" s="63">
+        <v>0.54249320166022619</v>
+      </c>
+      <c r="Z12" s="65">
         <f>Z4/Z6</f>
-        <v>0.54929450344474862</v>
-      </c>
-      <c r="AA12" s="63">
-        <f>AA4/AA6</f>
-        <v>0.54249320166022619</v>
+        <v>0.56181306710598666</v>
+      </c>
+      <c r="AA12" s="65">
+        <f t="shared" ref="AA12:AJ12" si="18">AA4/AA6</f>
+        <v>0.58434927214060961</v>
       </c>
       <c r="AB12" s="65">
-        <f>AB4/AB6</f>
-        <v>0.56181306710598666</v>
+        <f t="shared" si="18"/>
+        <v>0.60236786560754163</v>
       </c>
       <c r="AC12" s="65">
-        <f t="shared" ref="AC12:AL12" si="18">AC4/AC6</f>
-        <v>0.58434927214060961</v>
+        <f t="shared" si="18"/>
+        <v>0.61981722143192775</v>
       </c>
       <c r="AD12" s="65">
         <f t="shared" si="18"/>
-        <v>0.60236786560754163</v>
+        <v>0.62145227647148749</v>
       </c>
       <c r="AE12" s="65">
         <f t="shared" si="18"/>
-        <v>0.61981722143192775</v>
+        <v>0.61597911128685767</v>
       </c>
       <c r="AF12" s="65">
         <f t="shared" si="18"/>
-        <v>0.62145227647148749</v>
+        <v>0.60101958782614451</v>
       </c>
       <c r="AG12" s="65">
         <f t="shared" si="18"/>
-        <v>0.61597911128685767</v>
+        <v>0.58345087312115784</v>
       </c>
       <c r="AH12" s="65">
         <f t="shared" si="18"/>
-        <v>0.60101958782614451</v>
+        <v>0.57425073306471008</v>
       </c>
       <c r="AI12" s="65">
         <f t="shared" si="18"/>
-        <v>0.58345087312115784</v>
+        <v>0.56491052942254794</v>
       </c>
       <c r="AJ12" s="65">
         <f t="shared" si="18"/>
-        <v>0.57425073306471008</v>
-      </c>
-      <c r="AK12" s="65">
-        <f t="shared" si="18"/>
-        <v>0.56491052942254794</v>
-      </c>
-      <c r="AL12" s="65">
-        <f t="shared" si="18"/>
         <v>0.55777285018462708</v>
       </c>
     </row>
-    <row r="13" spans="2:91" ht="15">
+    <row r="13" spans="2:89" ht="15">
       <c r="B13" s="33" t="s">
         <v>585</v>
       </c>
@@ -11897,64 +11894,64 @@
         <f>M5/M6</f>
         <v>0.41017153174842008</v>
       </c>
+      <c r="W13" s="63">
+        <f>W5/W6</f>
+        <v>0.46654751466918459</v>
+      </c>
+      <c r="X13" s="63">
+        <f>X5/X6</f>
+        <v>0.45070549655525138</v>
+      </c>
       <c r="Y13" s="63">
         <f>Y5/Y6</f>
-        <v>0.46654751466918459</v>
-      </c>
-      <c r="Z13" s="63">
+        <v>0.45750679833977387</v>
+      </c>
+      <c r="Z13" s="65">
         <f>Z5/Z6</f>
-        <v>0.45070549655525138</v>
-      </c>
-      <c r="AA13" s="63">
-        <f>AA5/AA6</f>
-        <v>0.45750679833977387</v>
+        <v>0.43818693289401317</v>
+      </c>
+      <c r="AA13" s="65">
+        <f t="shared" ref="AA13:AJ13" si="21">AA5/AA6</f>
+        <v>0.4156507278593905</v>
       </c>
       <c r="AB13" s="65">
-        <f>AB5/AB6</f>
-        <v>0.43818693289401317</v>
+        <f t="shared" si="21"/>
+        <v>0.39763213439245831</v>
       </c>
       <c r="AC13" s="65">
-        <f t="shared" ref="AC13:AL13" si="21">AC5/AC6</f>
-        <v>0.4156507278593905</v>
+        <f t="shared" si="21"/>
+        <v>0.38018277856807231</v>
       </c>
       <c r="AD13" s="65">
         <f t="shared" si="21"/>
-        <v>0.39763213439245831</v>
+        <v>0.37854772352851257</v>
       </c>
       <c r="AE13" s="65">
         <f t="shared" si="21"/>
-        <v>0.38018277856807231</v>
+        <v>0.38402088871314233</v>
       </c>
       <c r="AF13" s="65">
         <f t="shared" si="21"/>
-        <v>0.37854772352851257</v>
+        <v>0.39898041217385538</v>
       </c>
       <c r="AG13" s="65">
         <f t="shared" si="21"/>
-        <v>0.38402088871314233</v>
+        <v>0.41654912687884227</v>
       </c>
       <c r="AH13" s="65">
         <f t="shared" si="21"/>
-        <v>0.39898041217385538</v>
+        <v>0.42574926693528992</v>
       </c>
       <c r="AI13" s="65">
         <f t="shared" si="21"/>
-        <v>0.41654912687884227</v>
+        <v>0.43508947057745212</v>
       </c>
       <c r="AJ13" s="65">
         <f t="shared" si="21"/>
-        <v>0.42574926693528992</v>
-      </c>
-      <c r="AK13" s="65">
-        <f t="shared" si="21"/>
-        <v>0.43508947057745212</v>
-      </c>
-      <c r="AL13" s="65">
-        <f t="shared" si="21"/>
         <v>0.44222714981537281</v>
       </c>
     </row>
-    <row r="15" spans="2:91">
+    <row r="15" spans="2:89">
       <c r="B15" s="62" t="s">
         <v>599</v>
       </c>
@@ -11993,19 +11990,19 @@
       <c r="M15" s="1">
         <v>3923</v>
       </c>
+      <c r="W15" s="1">
+        <v>12079</v>
+      </c>
+      <c r="X15" s="1">
+        <f>SUM(C15:F15)</f>
+        <v>13220</v>
+      </c>
       <c r="Y15" s="1">
-        <v>12079</v>
-      </c>
-      <c r="Z15" s="1">
-        <f t="shared" ref="Z15:Z18" si="22">SUM(C15:F15)</f>
-        <v>13220</v>
-      </c>
-      <c r="AA15" s="1">
-        <f t="shared" ref="AA15:AA18" si="23">SUM(G15:J15)</f>
+        <f>SUM(G15:J15)</f>
         <v>14465</v>
       </c>
     </row>
-    <row r="16" spans="2:91">
+    <row r="16" spans="2:89">
       <c r="B16" s="62" t="s">
         <v>600</v>
       </c>
@@ -12044,19 +12041,19 @@
       <c r="M16" s="1">
         <v>251</v>
       </c>
+      <c r="W16" s="1">
+        <v>699</v>
+      </c>
+      <c r="X16" s="1">
+        <f>SUM(C16:F16)</f>
+        <v>827</v>
+      </c>
       <c r="Y16" s="1">
-        <v>699</v>
-      </c>
-      <c r="Z16" s="1">
-        <f t="shared" si="22"/>
-        <v>827</v>
-      </c>
-      <c r="AA16" s="1">
-        <f t="shared" si="23"/>
+        <f>SUM(G16:J16)</f>
         <v>819</v>
       </c>
     </row>
-    <row r="17" spans="2:90">
+    <row r="17" spans="2:88">
       <c r="B17" s="62" t="s">
         <v>601</v>
       </c>
@@ -12095,19 +12092,19 @@
       <c r="M17" s="1">
         <v>223</v>
       </c>
+      <c r="W17" s="1">
+        <v>703</v>
+      </c>
+      <c r="X17" s="1">
+        <f>SUM(C17:F17)</f>
+        <v>887</v>
+      </c>
       <c r="Y17" s="1">
-        <v>703</v>
-      </c>
-      <c r="Z17" s="1">
-        <f t="shared" si="22"/>
-        <v>887</v>
-      </c>
-      <c r="AA17" s="1">
-        <f t="shared" si="23"/>
+        <f>SUM(G17:J17)</f>
         <v>781</v>
       </c>
     </row>
-    <row r="18" spans="2:90">
+    <row r="18" spans="2:88">
       <c r="B18" s="62" t="s">
         <v>602</v>
       </c>
@@ -12146,124 +12143,124 @@
       <c r="M18" s="1">
         <v>442</v>
       </c>
+      <c r="W18" s="1">
+        <v>2643</v>
+      </c>
+      <c r="X18" s="1">
+        <f>SUM(C18:F18)</f>
+        <v>2502</v>
+      </c>
       <c r="Y18" s="1">
-        <v>2643</v>
-      </c>
-      <c r="Z18" s="1">
-        <f t="shared" si="22"/>
-        <v>2502</v>
-      </c>
-      <c r="AA18" s="1">
-        <f t="shared" si="23"/>
+        <f>SUM(G18:J18)</f>
         <v>2063</v>
       </c>
     </row>
-    <row r="19" spans="2:90" ht="15">
+    <row r="19" spans="2:88" ht="15">
       <c r="B19" s="74" t="s">
         <v>590</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" ref="C19:L19" si="24">SUM(C15:C18)</f>
+        <f t="shared" ref="C19:L19" si="22">SUM(C15:C18)</f>
         <v>3821</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4131</v>
       </c>
       <c r="E19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>3893</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>5591</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4035</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4455</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4207</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>5431</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4423</v>
       </c>
       <c r="L19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>4758</v>
       </c>
       <c r="M19" s="2">
         <f>SUM(M15:M18)</f>
         <v>4839</v>
       </c>
-      <c r="Y19" s="2">
-        <f>SUM(Y15:Y18)</f>
+      <c r="W19" s="2">
+        <f>SUM(W15:W18)</f>
         <v>16124</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="X19" s="2">
         <f>SUM(C19:F19)</f>
         <v>17436</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="Y19" s="2">
         <f>SUM(G19:J19)</f>
         <v>18128</v>
       </c>
+      <c r="Z19" s="70">
+        <f>Y19*(1+Z30)</f>
+        <v>19487.599999999999</v>
+      </c>
+      <c r="AA19" s="70">
+        <f t="shared" ref="AA19:AJ19" si="23">Z19*(1+AA30)</f>
+        <v>22313.302</v>
+      </c>
       <c r="AB19" s="70">
-        <f>AA19*(1+AB30)</f>
-        <v>19487.599999999999</v>
+        <f t="shared" si="23"/>
+        <v>26218.129850000001</v>
       </c>
       <c r="AC19" s="70">
-        <f t="shared" ref="AC19:AL19" si="25">AB19*(1+AC30)</f>
-        <v>22703.054</v>
+        <f t="shared" si="23"/>
+        <v>31396.210495375002</v>
       </c>
       <c r="AD19" s="70">
-        <f t="shared" si="25"/>
-        <v>27470.695339999998</v>
+        <f t="shared" si="23"/>
+        <v>36419.604174635002</v>
       </c>
       <c r="AE19" s="70">
-        <f t="shared" si="25"/>
-        <v>32896.157669649998</v>
+        <f t="shared" si="23"/>
+        <v>41336.250738210729</v>
       </c>
       <c r="AF19" s="70">
-        <f t="shared" si="25"/>
-        <v>38159.542896793995</v>
+        <f t="shared" si="23"/>
+        <v>45738.56144183017</v>
       </c>
       <c r="AG19" s="70">
-        <f t="shared" si="25"/>
-        <v>43311.081187861186</v>
+        <f t="shared" si="23"/>
+        <v>49545.610603440902</v>
       </c>
       <c r="AH19" s="70">
-        <f t="shared" si="25"/>
-        <v>47923.711334368403</v>
+        <f t="shared" si="23"/>
+        <v>52468.801629043912</v>
       </c>
       <c r="AI19" s="70">
-        <f t="shared" si="25"/>
-        <v>51912.641447284557</v>
+        <f t="shared" si="23"/>
+        <v>54829.897702350885</v>
       </c>
       <c r="AJ19" s="70">
-        <f t="shared" si="25"/>
-        <v>54975.487292674341</v>
-      </c>
-      <c r="AK19" s="70">
-        <f t="shared" si="25"/>
-        <v>57449.38422084468</v>
-      </c>
-      <c r="AL19" s="70">
-        <f t="shared" si="25"/>
-        <v>59575.011437015928</v>
-      </c>
-    </row>
-    <row r="20" spans="2:90">
+        <f t="shared" si="23"/>
+        <v>56858.603917337867</v>
+      </c>
+    </row>
+    <row r="20" spans="2:88">
       <c r="B20" s="62" t="s">
         <v>603</v>
       </c>
@@ -12302,17 +12299,19 @@
       <c r="M20" s="1">
         <v>2402</v>
       </c>
+      <c r="W20" s="1">
+        <v>7941</v>
+      </c>
+      <c r="X20" s="1">
+        <f>SUM(C20:F20)</f>
+        <v>7761</v>
+      </c>
       <c r="Y20" s="1">
-        <v>7941</v>
-      </c>
-      <c r="Z20" s="1">
-        <f t="shared" ref="Z20:Z22" si="26">SUM(C20:F20)</f>
-        <v>7761</v>
-      </c>
-      <c r="AA20" s="1">
-        <f t="shared" ref="AA20:AA22" si="27">SUM(G20:J20)</f>
+        <f>SUM(G20:J20)</f>
         <v>7781</v>
       </c>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="70"/>
       <c r="AB20" s="70"/>
       <c r="AC20" s="70"/>
       <c r="AD20" s="70"/>
@@ -12322,10 +12321,8 @@
       <c r="AH20" s="70"/>
       <c r="AI20" s="70"/>
       <c r="AJ20" s="70"/>
-      <c r="AK20" s="70"/>
-      <c r="AL20" s="70"/>
-    </row>
-    <row r="21" spans="2:90">
+    </row>
+    <row r="21" spans="2:88">
       <c r="B21" s="62" t="s">
         <v>604</v>
       </c>
@@ -12364,17 +12361,19 @@
       <c r="M21" s="1">
         <v>195</v>
       </c>
+      <c r="W21" s="1">
+        <v>531</v>
+      </c>
+      <c r="X21" s="1">
+        <f>SUM(C21:F21)</f>
+        <v>1455</v>
+      </c>
       <c r="Y21" s="1">
-        <v>531</v>
-      </c>
-      <c r="Z21" s="1">
-        <f t="shared" si="26"/>
-        <v>1455</v>
-      </c>
-      <c r="AA21" s="1">
-        <f t="shared" si="27"/>
+        <f>SUM(G21:J21)</f>
         <v>1377</v>
       </c>
+      <c r="Z21" s="70"/>
+      <c r="AA21" s="70"/>
       <c r="AB21" s="70"/>
       <c r="AC21" s="70"/>
       <c r="AD21" s="70"/>
@@ -12384,10 +12383,8 @@
       <c r="AH21" s="70"/>
       <c r="AI21" s="70"/>
       <c r="AJ21" s="70"/>
-      <c r="AK21" s="70"/>
-      <c r="AL21" s="70"/>
-    </row>
-    <row r="22" spans="2:90">
+    </row>
+    <row r="22" spans="2:88">
       <c r="B22" s="62" t="s">
         <v>605</v>
       </c>
@@ -12426,17 +12423,19 @@
       <c r="M22" s="1">
         <v>51</v>
       </c>
+      <c r="W22" s="1">
+        <v>433</v>
+      </c>
+      <c r="X22" s="1">
+        <f>SUM(C22:F22)</f>
+        <v>610</v>
+      </c>
       <c r="Y22" s="1">
-        <v>433</v>
-      </c>
-      <c r="Z22" s="1">
-        <f t="shared" si="26"/>
-        <v>610</v>
-      </c>
-      <c r="AA22" s="1">
-        <f t="shared" si="27"/>
+        <f>SUM(G22:J22)</f>
         <v>542</v>
       </c>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="70"/>
       <c r="AB22" s="70"/>
       <c r="AC22" s="70"/>
       <c r="AD22" s="70"/>
@@ -12446,115 +12445,113 @@
       <c r="AH22" s="70"/>
       <c r="AI22" s="70"/>
       <c r="AJ22" s="70"/>
-      <c r="AK22" s="70"/>
-      <c r="AL22" s="70"/>
-    </row>
-    <row r="23" spans="2:90" ht="15">
+    </row>
+    <row r="23" spans="2:88" ht="15">
       <c r="B23" s="74" t="s">
         <v>591</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" ref="C23:L23" si="28">SUM(C20:C22)</f>
+        <f t="shared" ref="C23:L23" si="24">SUM(C20:C22)</f>
         <v>1751</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2601</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2887</v>
       </c>
       <c r="F23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2587</v>
       </c>
       <c r="G23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>1639</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2062</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2891</v>
       </c>
       <c r="J23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>3108</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>1850</v>
       </c>
       <c r="L23" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>2245</v>
       </c>
       <c r="M23" s="2">
         <f>SUM(M20:M22)</f>
         <v>2648</v>
       </c>
-      <c r="Y23" s="2">
-        <f>SUM(Y20:Y22)</f>
+      <c r="W23" s="2">
+        <f>SUM(W20:W22)</f>
         <v>8905</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="X23" s="2">
         <f>SUM(C23:F23)</f>
         <v>9826</v>
       </c>
-      <c r="AA23" s="2">
+      <c r="Y23" s="2">
         <f>SUM(G23:J23)</f>
         <v>9700</v>
       </c>
+      <c r="Z23" s="70">
+        <f>Y23*(1+Z31)</f>
+        <v>9215</v>
+      </c>
+      <c r="AA23" s="70">
+        <f t="shared" ref="AA23:AJ23" si="25">Z23*(1+AA31)</f>
+        <v>8477.8000000000011</v>
+      </c>
       <c r="AB23" s="70">
-        <f>AA23*(1+AB31)</f>
-        <v>9991</v>
+        <f t="shared" si="25"/>
+        <v>6612.6840000000011</v>
       </c>
       <c r="AC23" s="70">
-        <f t="shared" ref="AC23:AL23" si="29">AB23*(1+AC31)</f>
-        <v>9491.4499999999989</v>
+        <f t="shared" si="25"/>
+        <v>5323.2106200000007</v>
       </c>
       <c r="AD23" s="70">
-        <f t="shared" si="29"/>
-        <v>7403.3309999999992</v>
+        <f t="shared" si="25"/>
+        <v>5562.7550979000007</v>
       </c>
       <c r="AE23" s="70">
-        <f t="shared" si="29"/>
-        <v>5959.681454999999</v>
+        <f t="shared" si="25"/>
+        <v>6174.6581586690018</v>
       </c>
       <c r="AF23" s="70">
-        <f t="shared" si="29"/>
-        <v>6227.867120474999</v>
+        <f t="shared" si="25"/>
+        <v>6736.5520511078803</v>
       </c>
       <c r="AG23" s="70">
-        <f t="shared" si="29"/>
-        <v>6912.9325037272492</v>
+        <f t="shared" si="25"/>
+        <v>7208.1106946854325</v>
       </c>
       <c r="AH23" s="70">
-        <f t="shared" si="29"/>
-        <v>7542.0093615664291</v>
+        <f t="shared" si="25"/>
+        <v>7514.4553992095634</v>
       </c>
       <c r="AI23" s="70">
-        <f t="shared" si="29"/>
-        <v>8069.9500168760796</v>
+        <f t="shared" si="25"/>
+        <v>7800.0047043795275</v>
       </c>
       <c r="AJ23" s="70">
-        <f t="shared" si="29"/>
-        <v>8412.922892593313</v>
-      </c>
-      <c r="AK23" s="70">
-        <f t="shared" si="29"/>
-        <v>8732.6139625118594</v>
-      </c>
-      <c r="AL23" s="70">
-        <f t="shared" si="29"/>
-        <v>8929.0977766683754</v>
-      </c>
-    </row>
-    <row r="24" spans="2:90">
+        <f t="shared" si="25"/>
+        <v>7975.5048102280671</v>
+      </c>
+    </row>
+    <row r="24" spans="2:88">
       <c r="B24" s="62" t="s">
         <v>606</v>
       </c>
@@ -12593,17 +12590,19 @@
       <c r="M24" s="1">
         <v>1747</v>
       </c>
+      <c r="W24" s="1">
+        <v>3133</v>
+      </c>
+      <c r="X24" s="1">
+        <f>SUM(C24:F24)</f>
+        <v>3955</v>
+      </c>
       <c r="Y24" s="1">
-        <v>3133</v>
-      </c>
-      <c r="Z24" s="1">
-        <f t="shared" ref="Z24:Z26" si="30">SUM(C24:F24)</f>
-        <v>3955</v>
-      </c>
-      <c r="AA24" s="1">
-        <f t="shared" ref="AA24:AA26" si="31">SUM(G24:J24)</f>
+        <f>SUM(G24:J24)</f>
         <v>4957</v>
       </c>
+      <c r="Z24" s="70"/>
+      <c r="AA24" s="70"/>
       <c r="AB24" s="70"/>
       <c r="AC24" s="70"/>
       <c r="AD24" s="70"/>
@@ -12613,10 +12612,8 @@
       <c r="AH24" s="70"/>
       <c r="AI24" s="70"/>
       <c r="AJ24" s="70"/>
-      <c r="AK24" s="70"/>
-      <c r="AL24" s="70"/>
-    </row>
-    <row r="25" spans="2:90">
+    </row>
+    <row r="25" spans="2:88">
       <c r="B25" s="62" t="s">
         <v>607</v>
       </c>
@@ -12658,18 +12655,20 @@
       <c r="M25" s="1">
         <v>621</v>
       </c>
-      <c r="Y25" s="1">
+      <c r="W25" s="1">
         <f>843+296</f>
         <v>1139</v>
       </c>
-      <c r="Z25" s="1">
-        <f t="shared" si="30"/>
+      <c r="X25" s="1">
+        <f>SUM(C25:F25)</f>
         <v>1509</v>
       </c>
-      <c r="AA25" s="1">
-        <f t="shared" si="31"/>
+      <c r="Y25" s="1">
+        <f>SUM(G25:J25)</f>
         <v>1676</v>
       </c>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="70"/>
       <c r="AB25" s="70"/>
       <c r="AC25" s="70"/>
       <c r="AD25" s="70"/>
@@ -12679,10 +12678,8 @@
       <c r="AH25" s="70"/>
       <c r="AI25" s="70"/>
       <c r="AJ25" s="70"/>
-      <c r="AK25" s="70"/>
-      <c r="AL25" s="70"/>
-    </row>
-    <row r="26" spans="2:90">
+    </row>
+    <row r="26" spans="2:88">
       <c r="B26" s="62" t="s">
         <v>608</v>
       </c>
@@ -12721,17 +12718,19 @@
       <c r="M26" s="1">
         <v>234</v>
       </c>
+      <c r="W26" s="1">
+        <v>804</v>
+      </c>
+      <c r="X26" s="1">
+        <f>SUM(C26:F26)</f>
+        <v>874</v>
+      </c>
       <c r="Y26" s="1">
-        <v>804</v>
-      </c>
-      <c r="Z26" s="1">
-        <f t="shared" si="30"/>
-        <v>874</v>
-      </c>
-      <c r="AA26" s="1">
-        <f t="shared" si="31"/>
+        <f>SUM(G26:J26)</f>
         <v>917</v>
       </c>
+      <c r="Z26" s="70"/>
+      <c r="AA26" s="70"/>
       <c r="AB26" s="70"/>
       <c r="AC26" s="70"/>
       <c r="AD26" s="70"/>
@@ -12741,115 +12740,113 @@
       <c r="AH26" s="70"/>
       <c r="AI26" s="70"/>
       <c r="AJ26" s="70"/>
-      <c r="AK26" s="70"/>
-      <c r="AL26" s="70"/>
-    </row>
-    <row r="27" spans="2:90" ht="15">
+    </row>
+    <row r="27" spans="2:88" ht="15">
       <c r="B27" s="74" t="s">
         <v>592</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" ref="C27:L27" si="32">SUM(C24:C26)</f>
+        <f t="shared" ref="C27:L27" si="26">SUM(C24:C26)</f>
         <v>1331</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1505</v>
       </c>
       <c r="E27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1577</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1925</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1651</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1791</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1928</v>
       </c>
       <c r="J27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>2180</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>1880</v>
       </c>
       <c r="L27" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="26"/>
         <v>2201</v>
       </c>
       <c r="M27" s="2">
         <f>SUM(M24:M26)</f>
         <v>2602</v>
       </c>
-      <c r="Y27" s="2">
-        <f>SUM(Y24:Y26)</f>
+      <c r="W27" s="2">
+        <f>SUM(W24:W26)</f>
         <v>5076</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="X27" s="2">
         <f>SUM(C27:F27)</f>
         <v>6338</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="Y27" s="2">
         <f>SUM(G27:J27)</f>
         <v>7550</v>
       </c>
+      <c r="Z27" s="70">
+        <f>Y27*(1+Z32)</f>
+        <v>9248.75</v>
+      </c>
+      <c r="AA27" s="70">
+        <f t="shared" ref="AA27:AJ27" si="27">Z27*(1+AA32)</f>
+        <v>12300.837500000001</v>
+      </c>
       <c r="AB27" s="70">
-        <f>AA27*(1+AB32)</f>
-        <v>8886.35</v>
+        <f t="shared" si="27"/>
+        <v>16667.6348125</v>
       </c>
       <c r="AC27" s="70">
-        <f t="shared" ref="AC27:AL27" si="33">AB27*(1+AC32)</f>
-        <v>11818.845500000001</v>
+        <f t="shared" si="27"/>
+        <v>21001.219863750001</v>
       </c>
       <c r="AD27" s="70">
-        <f t="shared" si="33"/>
-        <v>16132.724107500002</v>
+        <f t="shared" si="27"/>
+        <v>24634.430900178751</v>
       </c>
       <c r="AE27" s="70">
-        <f t="shared" si="33"/>
-        <v>20327.232375450003</v>
+        <f t="shared" si="27"/>
+        <v>28428.133258806276</v>
       </c>
       <c r="AF27" s="70">
-        <f t="shared" si="33"/>
-        <v>23843.843576402855</v>
+        <f t="shared" si="27"/>
+        <v>31583.656050533773</v>
       </c>
       <c r="AG27" s="70">
-        <f t="shared" si="33"/>
-        <v>27515.795487168893</v>
+        <f t="shared" si="27"/>
+        <v>33510.259069616332</v>
       </c>
       <c r="AH27" s="70">
-        <f t="shared" si="33"/>
-        <v>30570.048786244639</v>
+        <f t="shared" si="27"/>
+        <v>35286.302800305995</v>
       </c>
       <c r="AI27" s="70">
-        <f t="shared" si="33"/>
-        <v>32434.82176220556</v>
+        <f t="shared" si="27"/>
+        <v>36450.750792716091</v>
       </c>
       <c r="AJ27" s="70">
-        <f t="shared" si="33"/>
-        <v>34153.867315602452</v>
-      </c>
-      <c r="AK27" s="70">
-        <f t="shared" si="33"/>
-        <v>35280.944937017332</v>
-      </c>
-      <c r="AL27" s="70">
-        <f t="shared" si="33"/>
-        <v>35986.563835757675</v>
-      </c>
-    </row>
-    <row r="28" spans="2:90" s="2" customFormat="1" ht="15">
+        <f t="shared" si="27"/>
+        <v>37179.765808570417</v>
+      </c>
+    </row>
+    <row r="28" spans="2:88" s="2" customFormat="1" ht="15">
       <c r="B28" s="33" t="s">
         <v>63</v>
       </c>
@@ -12866,7 +12863,7 @@
         <v>8252</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" ref="F28" si="34">F27+F23+F19</f>
+        <f t="shared" ref="F28" si="28">F27+F23+F19</f>
         <v>10103</v>
       </c>
       <c r="G28" s="2">
@@ -12902,62 +12899,64 @@
       <c r="P28" s="34"/>
       <c r="Q28" s="34"/>
       <c r="R28" s="34"/>
-      <c r="Y28" s="2">
-        <f>Y27+Y23+Y19-451</f>
+      <c r="W28" s="2">
+        <f>W27+W23+W19-451</f>
         <v>29654</v>
       </c>
-      <c r="Z28" s="2">
+      <c r="X28" s="2">
         <f>SUM(C28:F28)</f>
         <v>33296</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="Y28" s="2">
         <f>SUM(G28:J28)</f>
         <v>34935</v>
       </c>
+      <c r="Z28" s="71">
+        <f>Z19+Z23+Z27</f>
+        <v>37951.35</v>
+      </c>
+      <c r="AA28" s="71">
+        <f t="shared" ref="AA28:AJ28" si="29">AA19+AA23+AA27</f>
+        <v>43091.9395</v>
+      </c>
       <c r="AB28" s="71">
-        <f>AB19+AB23+AB27</f>
-        <v>38364.949999999997</v>
+        <f t="shared" si="29"/>
+        <v>49498.448662500006</v>
       </c>
       <c r="AC28" s="71">
-        <f t="shared" ref="AC28:AL28" si="35">AC19+AC23+AC27</f>
-        <v>44013.349500000004</v>
+        <f t="shared" si="29"/>
+        <v>57720.640979125004</v>
       </c>
       <c r="AD28" s="71">
-        <f t="shared" si="35"/>
-        <v>51006.750447500002</v>
+        <f t="shared" si="29"/>
+        <v>66616.790172713751</v>
       </c>
       <c r="AE28" s="71">
-        <f t="shared" si="35"/>
-        <v>59183.071500099999</v>
+        <f t="shared" si="29"/>
+        <v>75939.042155686009</v>
       </c>
       <c r="AF28" s="71">
-        <f t="shared" si="35"/>
-        <v>68231.253593671849</v>
+        <f t="shared" si="29"/>
+        <v>84058.769543471819</v>
       </c>
       <c r="AG28" s="71">
-        <f t="shared" si="35"/>
-        <v>77739.809178757336</v>
+        <f t="shared" si="29"/>
+        <v>90263.980367742668</v>
       </c>
       <c r="AH28" s="71">
-        <f t="shared" si="35"/>
-        <v>86035.769482179472</v>
+        <f t="shared" si="29"/>
+        <v>95269.559828559461</v>
       </c>
       <c r="AI28" s="71">
-        <f t="shared" si="35"/>
-        <v>92417.413226366189</v>
+        <f t="shared" si="29"/>
+        <v>99080.653199446504</v>
       </c>
       <c r="AJ28" s="71">
-        <f t="shared" si="35"/>
-        <v>97542.277500870114</v>
-      </c>
-      <c r="AK28" s="71">
-        <f t="shared" si="35"/>
-        <v>101462.94312037388</v>
-      </c>
-      <c r="AL28" s="71">
-        <f t="shared" si="35"/>
-        <v>104490.67304944198</v>
-      </c>
+        <f t="shared" si="29"/>
+        <v>102013.87453613635</v>
+      </c>
+      <c r="AK28" s="34"/>
+      <c r="AL28" s="34"/>
       <c r="AM28" s="34"/>
       <c r="AN28" s="34"/>
       <c r="AO28" s="34"/>
@@ -13008,10 +13007,8 @@
       <c r="CH28" s="34"/>
       <c r="CI28" s="34"/>
       <c r="CJ28" s="34"/>
-      <c r="CK28" s="34"/>
-      <c r="CL28" s="34"/>
-    </row>
-    <row r="30" spans="2:90">
+    </row>
+    <row r="30" spans="2:88">
       <c r="B30" s="62" t="s">
         <v>593</v>
       </c>
@@ -13020,77 +13017,77 @@
       <c r="E30" s="63"/>
       <c r="F30" s="63"/>
       <c r="G30" s="63">
-        <f t="shared" ref="G30:M30" si="36">G19/C19-1</f>
+        <f t="shared" ref="G30:M30" si="30">G19/C19-1</f>
         <v>5.6006281078251785E-2</v>
       </c>
       <c r="H30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>7.8431372549019551E-2</v>
       </c>
       <c r="I30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>8.0657590547135838E-2</v>
       </c>
       <c r="J30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>-2.8617420854945452E-2</v>
       </c>
       <c r="K30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>9.6158612143742328E-2</v>
       </c>
       <c r="L30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>6.8013468013468081E-2</v>
       </c>
       <c r="M30" s="63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="30"/>
         <v>0.1502258141193249</v>
       </c>
-      <c r="Y30" s="63"/>
-      <c r="Z30" s="63">
-        <f>Z19/Y19-1</f>
+      <c r="W30" s="63"/>
+      <c r="X30" s="63">
+        <f>X19/W19-1</f>
         <v>8.1369387248821701E-2</v>
       </c>
-      <c r="AA30" s="63">
-        <f>AA19/Z19-1</f>
+      <c r="Y30" s="63">
+        <f>Y19/X19-1</f>
         <v>3.9688001835283426E-2</v>
       </c>
+      <c r="Z30" s="65">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="AA30" s="65">
+        <v>0.14499999999999999</v>
+      </c>
       <c r="AB30" s="65">
-        <v>7.4999999999999997E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="AC30" s="65">
-        <v>0.16500000000000001</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="AD30" s="65">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="AE30" s="65">
-        <v>0.19750000000000001</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="AF30" s="65">
-        <v>0.16</v>
+        <v>0.1065</v>
       </c>
       <c r="AG30" s="65">
-        <v>0.13500000000000001</v>
+        <v>8.3235000000000003E-2</v>
       </c>
       <c r="AH30" s="65">
-        <v>0.1065</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="AI30" s="65">
-        <v>8.3235000000000003E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AJ30" s="65">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="AK30" s="65">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="AL30" s="65">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:90">
+    <row r="31" spans="2:88">
       <c r="B31" s="62" t="s">
         <v>594</v>
       </c>
@@ -13099,77 +13096,77 @@
       <c r="E31" s="63"/>
       <c r="F31" s="63"/>
       <c r="G31" s="63">
-        <f t="shared" ref="G31:M31" si="37">G23/C23-1</f>
+        <f t="shared" ref="G31:M31" si="31">G23/C23-1</f>
         <v>-6.3963449457452914E-2</v>
       </c>
       <c r="H31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>-0.2072279892349097</v>
       </c>
       <c r="I31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>1.3855213023901136E-3</v>
       </c>
       <c r="J31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>0.20139157325086976</v>
       </c>
       <c r="K31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>0.12873703477730314</v>
       </c>
       <c r="L31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>8.8748787584869149E-2</v>
       </c>
       <c r="M31" s="63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="31"/>
         <v>-8.4053960567277763E-2</v>
       </c>
-      <c r="Y31" s="63"/>
-      <c r="Z31" s="63">
-        <f>Z23/Y23-1</f>
+      <c r="W31" s="63"/>
+      <c r="X31" s="63">
+        <f>X23/W23-1</f>
         <v>0.10342504211117354</v>
       </c>
-      <c r="AA31" s="63">
-        <f>AA23/Z23-1</f>
+      <c r="Y31" s="63">
+        <f>Y23/X23-1</f>
         <v>-1.2823122328516234E-2</v>
       </c>
+      <c r="Z31" s="65">
+        <v>-0.05</v>
+      </c>
+      <c r="AA31" s="65">
+        <v>-0.08</v>
+      </c>
       <c r="AB31" s="65">
-        <v>0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="AC31" s="65">
-        <v>-0.05</v>
+        <v>-0.19500000000000001</v>
       </c>
       <c r="AD31" s="65">
-        <v>-0.22</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="AE31" s="65">
-        <v>-0.19500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AF31" s="65">
-        <v>4.4999999999999998E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="AG31" s="65">
-        <v>0.11</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AH31" s="65">
-        <v>9.0999999999999998E-2</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="AI31" s="65">
-        <v>7.0000000000000007E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="AJ31" s="65">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="AK31" s="65">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="AL31" s="65">
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:90">
+    <row r="32" spans="2:88">
       <c r="B32" s="62" t="s">
         <v>595</v>
       </c>
@@ -13178,77 +13175,77 @@
       <c r="E32" s="63"/>
       <c r="F32" s="63"/>
       <c r="G32" s="63">
-        <f t="shared" ref="G32:G33" si="38">G27/C27-1</f>
+        <f t="shared" ref="G32:G33" si="32">G27/C27-1</f>
         <v>0.24042073628850491</v>
       </c>
       <c r="H32" s="63">
-        <f t="shared" ref="H32:H33" si="39">H27/D27-1</f>
+        <f t="shared" ref="H32:H33" si="33">H27/D27-1</f>
         <v>0.19003322259136213</v>
       </c>
       <c r="I32" s="63">
-        <f t="shared" ref="I32:I33" si="40">I27/E27-1</f>
+        <f t="shared" ref="I32:I33" si="34">I27/E27-1</f>
         <v>0.22257450856055794</v>
       </c>
       <c r="J32" s="63">
-        <f t="shared" ref="J32:J33" si="41">J27/F27-1</f>
+        <f t="shared" ref="J32:J33" si="35">J27/F27-1</f>
         <v>0.1324675324675324</v>
       </c>
       <c r="K32" s="63">
-        <f t="shared" ref="K32:K33" si="42">K27/G27-1</f>
+        <f t="shared" ref="K32:K33" si="36">K27/G27-1</f>
         <v>0.13870381586917024</v>
       </c>
       <c r="L32" s="63">
-        <f t="shared" ref="L32:L33" si="43">L27/H27-1</f>
+        <f t="shared" ref="L32:L33" si="37">L27/H27-1</f>
         <v>0.22892238972640988</v>
       </c>
       <c r="M32" s="63">
-        <f t="shared" ref="M32" si="44">M27/I27-1</f>
+        <f t="shared" ref="M32" si="38">M27/I27-1</f>
         <v>0.34958506224066399</v>
       </c>
-      <c r="Y32" s="63"/>
-      <c r="Z32" s="63">
-        <f t="shared" ref="Z32:AA33" si="45">Z27/Y27-1</f>
+      <c r="W32" s="63"/>
+      <c r="X32" s="63">
+        <f t="shared" ref="X32:Y33" si="39">X27/W27-1</f>
         <v>0.2486209613869188</v>
       </c>
-      <c r="AA32" s="63">
-        <f t="shared" si="45"/>
+      <c r="Y32" s="63">
+        <f t="shared" si="39"/>
         <v>0.19122751656674031</v>
       </c>
+      <c r="Z32" s="65">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="AA32" s="65">
+        <v>0.33</v>
+      </c>
       <c r="AB32" s="65">
-        <v>0.17699999999999999</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="AC32" s="65">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="AD32" s="65">
-        <v>0.36499999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="AE32" s="65">
-        <v>0.26</v>
+        <v>0.154</v>
       </c>
       <c r="AF32" s="65">
-        <v>0.17299999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="AG32" s="65">
-        <v>0.154</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="AH32" s="65">
-        <v>0.111</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="AI32" s="65">
-        <v>6.0999999999999999E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="AJ32" s="65">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="AK32" s="65">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="AL32" s="65">
         <v>0.02</v>
       </c>
     </row>
-    <row r="33" spans="2:90" s="2" customFormat="1" ht="15">
+    <row r="33" spans="2:88" s="2" customFormat="1" ht="15">
       <c r="B33" s="33" t="s">
         <v>116</v>
       </c>
@@ -13257,27 +13254,27 @@
       <c r="E33" s="64"/>
       <c r="F33" s="64"/>
       <c r="G33" s="64">
-        <f t="shared" si="38"/>
+        <f t="shared" si="32"/>
         <v>6.4057461155086592E-2</v>
       </c>
       <c r="H33" s="64">
-        <f t="shared" si="39"/>
+        <f t="shared" si="33"/>
         <v>1.0469269614484578E-2</v>
       </c>
       <c r="I33" s="64">
-        <f t="shared" si="40"/>
+        <f t="shared" si="34"/>
         <v>8.010179350460489E-2</v>
       </c>
       <c r="J33" s="64">
-        <f t="shared" si="41"/>
+        <f t="shared" si="35"/>
         <v>4.5135108383648426E-2</v>
       </c>
       <c r="K33" s="64">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.10648849703815944</v>
       </c>
       <c r="L33" s="64">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>0.11055582642613349</v>
       </c>
       <c r="M33" s="64">
@@ -13289,59 +13286,61 @@
       <c r="P33" s="34"/>
       <c r="Q33" s="34"/>
       <c r="R33" s="34"/>
-      <c r="Y33" s="64"/>
-      <c r="Z33" s="64">
-        <f t="shared" si="45"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64">
+        <f t="shared" si="39"/>
         <v>0.12281648344236862</v>
       </c>
-      <c r="AA33" s="64">
-        <f t="shared" si="45"/>
+      <c r="Y33" s="64">
+        <f t="shared" si="39"/>
         <v>4.9225132148005724E-2</v>
       </c>
+      <c r="Z33" s="66">
+        <f>Z28/Y28-1</f>
+        <v>8.6341777586947055E-2</v>
+      </c>
+      <c r="AA33" s="66">
+        <f t="shared" ref="AA33:AJ33" si="40">AA28/Z28-1</f>
+        <v>0.13545208536718722</v>
+      </c>
       <c r="AB33" s="66">
-        <f>AB28/AA28-1</f>
-        <v>9.8180907399455952E-2</v>
+        <f t="shared" si="40"/>
+        <v>0.14867070818429995</v>
       </c>
       <c r="AC33" s="66">
-        <f t="shared" ref="AC33:AL33" si="46">AC28/AB28-1</f>
-        <v>0.14722812098021776</v>
+        <f t="shared" si="40"/>
+        <v>0.16611010120109326</v>
       </c>
       <c r="AD33" s="66">
-        <f t="shared" si="46"/>
-        <v>0.1588927229339816</v>
+        <f t="shared" si="40"/>
+        <v>0.15412422735925757</v>
       </c>
       <c r="AE33" s="66">
-        <f t="shared" si="46"/>
-        <v>0.16029880321459977</v>
+        <f t="shared" si="40"/>
+        <v>0.13993847435163054</v>
       </c>
       <c r="AF33" s="66">
-        <f t="shared" si="46"/>
-        <v>0.15288463177441813</v>
+        <f t="shared" si="40"/>
+        <v>0.10692427975505936</v>
       </c>
       <c r="AG33" s="66">
-        <f t="shared" si="46"/>
-        <v>0.13935777351696443</v>
+        <f t="shared" si="40"/>
+        <v>7.3819910260068289E-2</v>
       </c>
       <c r="AH33" s="66">
-        <f t="shared" si="46"/>
-        <v>0.10671444130183216</v>
+        <f t="shared" si="40"/>
+        <v>5.5454893972364916E-2</v>
       </c>
       <c r="AI33" s="66">
-        <f t="shared" si="46"/>
-        <v>7.4174308925179622E-2</v>
+        <f t="shared" si="40"/>
+        <v>4.0003264187902454E-2</v>
       </c>
       <c r="AJ33" s="66">
-        <f t="shared" si="46"/>
-        <v>5.5453448604443567E-2</v>
-      </c>
-      <c r="AK33" s="66">
-        <f t="shared" si="46"/>
-        <v>4.0194526106577699E-2</v>
-      </c>
-      <c r="AL33" s="66">
-        <f t="shared" si="46"/>
-        <v>2.9840746147842934E-2</v>
-      </c>
+        <f t="shared" si="40"/>
+        <v>2.960438028991752E-2</v>
+      </c>
+      <c r="AK33" s="34"/>
+      <c r="AL33" s="34"/>
       <c r="AM33" s="34"/>
       <c r="AN33" s="34"/>
       <c r="AO33" s="34"/>
@@ -13392,10 +13391,8 @@
       <c r="CH33" s="34"/>
       <c r="CI33" s="34"/>
       <c r="CJ33" s="34"/>
-      <c r="CK33" s="34"/>
-      <c r="CL33" s="34"/>
-    </row>
-    <row r="34" spans="2:90">
+    </row>
+    <row r="34" spans="2:88">
       <c r="C34" s="63"/>
       <c r="D34" s="63"/>
       <c r="E34" s="63"/>
@@ -13407,441 +13404,441 @@
       <c r="K34" s="63"/>
       <c r="L34" s="63"/>
       <c r="M34" s="63"/>
+      <c r="W34" s="63"/>
+      <c r="X34" s="63"/>
       <c r="Y34" s="63"/>
-      <c r="Z34" s="63"/>
-      <c r="AA34" s="63"/>
-    </row>
-    <row r="35" spans="2:90">
+    </row>
+    <row r="35" spans="2:88">
       <c r="B35" s="62" t="s">
         <v>596</v>
       </c>
       <c r="C35" s="63">
-        <f t="shared" ref="C35:L35" si="47">C19/C28</f>
+        <f t="shared" ref="C35:L35" si="41">C19/C28</f>
         <v>0.56009967751392553</v>
       </c>
       <c r="D35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.50880650326394872</v>
       </c>
       <c r="E35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.47176442074648572</v>
       </c>
       <c r="F35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.5533999802038998</v>
       </c>
       <c r="G35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.55586168893787025</v>
       </c>
       <c r="H35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.54302779132130663</v>
       </c>
       <c r="I35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.4720071805228318</v>
       </c>
       <c r="J35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.51434794961644092</v>
       </c>
       <c r="K35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.55067231075697209</v>
       </c>
       <c r="L35" s="63">
-        <f t="shared" si="47"/>
+        <f t="shared" si="41"/>
         <v>0.52222588080342447</v>
       </c>
       <c r="M35" s="63">
         <f>M19/M28</f>
         <v>0.48540475473969302</v>
       </c>
+      <c r="W35" s="63">
+        <f t="shared" ref="W35:X35" si="42">W19/W28</f>
+        <v>0.54373777567950365</v>
+      </c>
+      <c r="X35" s="63">
+        <f t="shared" si="42"/>
+        <v>0.52366650648726576</v>
+      </c>
       <c r="Y35" s="63">
-        <f t="shared" ref="Y35:Z35" si="48">Y19/Y28</f>
-        <v>0.54373777567950365</v>
-      </c>
-      <c r="Z35" s="63">
-        <f t="shared" si="48"/>
-        <v>0.52366650648726576</v>
-      </c>
-      <c r="AA35" s="63">
-        <f>AA19/AA28</f>
+        <f>Y19/Y28</f>
         <v>0.51890654071847719</v>
       </c>
     </row>
-    <row r="36" spans="2:90">
+    <row r="36" spans="2:88">
       <c r="B36" s="62" t="s">
         <v>597</v>
       </c>
       <c r="C36" s="63">
-        <f t="shared" ref="C36:L36" si="49">C23/C28</f>
+        <f t="shared" ref="C36:L36" si="43">C23/C28</f>
         <v>0.2566695983582527</v>
       </c>
       <c r="D36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.32035965020322699</v>
       </c>
       <c r="E36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.3498545807077072</v>
       </c>
       <c r="F36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.25606255567653174</v>
       </c>
       <c r="G36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.22578867612618819</v>
       </c>
       <c r="H36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.25134080936128717</v>
       </c>
       <c r="I36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.32435767979355995</v>
       </c>
       <c r="J36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.29434605549767973</v>
       </c>
       <c r="K36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.23032868525896413</v>
       </c>
       <c r="L36" s="63">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>0.24640544396882888</v>
       </c>
       <c r="M36" s="63">
         <f>M23/M28</f>
         <v>0.26562343264118771</v>
       </c>
+      <c r="W36" s="63">
+        <f t="shared" ref="W36:X36" si="44">W23/W28</f>
+        <v>0.30029675591825722</v>
+      </c>
+      <c r="X36" s="63">
+        <f t="shared" si="44"/>
+        <v>0.29511052378664104</v>
+      </c>
       <c r="Y36" s="63">
-        <f t="shared" ref="Y36:Z36" si="50">Y23/Y28</f>
-        <v>0.30029675591825722</v>
-      </c>
-      <c r="Z36" s="63">
-        <f t="shared" si="50"/>
-        <v>0.29511052378664104</v>
-      </c>
-      <c r="AA36" s="63">
-        <f>AA23/AA28</f>
+        <f>Y23/Y28</f>
         <v>0.27765850865893804</v>
       </c>
     </row>
-    <row r="37" spans="2:90">
+    <row r="37" spans="2:88">
       <c r="B37" s="62" t="s">
         <v>598</v>
       </c>
       <c r="C37" s="63">
-        <f t="shared" ref="C37:L37" si="51">C27/C28</f>
+        <f t="shared" ref="C37:L37" si="45">C27/C28</f>
         <v>0.19510407505130462</v>
       </c>
       <c r="D37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.18536765611528513</v>
       </c>
       <c r="E37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.19110518662142512</v>
       </c>
       <c r="F37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.19053746411956846</v>
       </c>
       <c r="G37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.22744179639068743</v>
       </c>
       <c r="H37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.21830814236957582</v>
       </c>
       <c r="I37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.2163132503085381</v>
       </c>
       <c r="J37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.20645894497584999</v>
       </c>
       <c r="K37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.23406374501992031</v>
       </c>
       <c r="L37" s="63">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.24157611678191199</v>
       </c>
       <c r="M37" s="63">
         <f>M27/M28</f>
         <v>0.26100912829772294</v>
       </c>
+      <c r="W37" s="63">
+        <f t="shared" ref="W37:X37" si="46">W27/W28</f>
+        <v>0.17117420921292237</v>
+      </c>
+      <c r="X37" s="63">
+        <f t="shared" si="46"/>
+        <v>0.19035319557904853</v>
+      </c>
       <c r="Y37" s="63">
-        <f t="shared" ref="Y37:Z37" si="52">Y27/Y28</f>
-        <v>0.17117420921292237</v>
-      </c>
-      <c r="Z37" s="63">
-        <f t="shared" si="52"/>
-        <v>0.19035319557904853</v>
-      </c>
-      <c r="AA37" s="63">
-        <f>AA27/AA28</f>
+        <f>Y27/Y28</f>
         <v>0.21611564333762703</v>
       </c>
     </row>
-    <row r="39" spans="2:90">
+    <row r="39" spans="2:88">
       <c r="B39" s="62" t="s">
         <v>545</v>
       </c>
       <c r="C39" s="1">
-        <f t="shared" ref="C39:M39" si="53">C4</f>
+        <f t="shared" ref="C39:M39" si="47">C4</f>
         <v>3489</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>4388</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>4869</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>5512</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>3617</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>4194</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>5290</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>5851</v>
       </c>
       <c r="K39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>4197</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>4894</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>5880</v>
       </c>
+      <c r="W39" s="1">
+        <f>W4</f>
+        <v>15819</v>
+      </c>
+      <c r="X39" s="1">
+        <f>SUM(C39:F39)</f>
+        <v>18258</v>
+      </c>
       <c r="Y39" s="1">
-        <f>Y4</f>
-        <v>15819</v>
-      </c>
-      <c r="Z39" s="1">
-        <f t="shared" ref="Z39:Z56" si="54">SUM(C39:F39)</f>
-        <v>18258</v>
-      </c>
-      <c r="AA39" s="1">
-        <f t="shared" ref="AA39:AA45" si="55">SUM(G39:J39)</f>
+        <f>SUM(G39:J39)</f>
         <v>18952</v>
       </c>
+      <c r="Z39" s="70">
+        <f t="shared" ref="Z39:AJ39" si="48">Z4</f>
+        <v>21557.899999999998</v>
+      </c>
+      <c r="AA39" s="70">
+        <f t="shared" si="48"/>
+        <v>25718.574699999997</v>
+      </c>
       <c r="AB39" s="70">
-        <f t="shared" ref="AB39:AL39" si="56">AB4</f>
-        <v>21557.899999999998</v>
+        <f t="shared" si="48"/>
+        <v>30733.696766499997</v>
       </c>
       <c r="AC39" s="70">
-        <f t="shared" si="56"/>
-        <v>25718.574699999997</v>
+        <f t="shared" si="48"/>
+        <v>36680.667090817748</v>
       </c>
       <c r="AD39" s="70">
-        <f t="shared" si="56"/>
-        <v>30733.696766499997</v>
+        <f t="shared" si="48"/>
+        <v>42402.851156985314</v>
       </c>
       <c r="AE39" s="70">
-        <f t="shared" si="56"/>
-        <v>36680.667090817748</v>
+        <f t="shared" si="48"/>
+        <v>47872.81895623642</v>
       </c>
       <c r="AF39" s="70">
-        <f t="shared" si="56"/>
-        <v>42402.851156985314</v>
+        <f t="shared" si="48"/>
+        <v>51702.644472735337</v>
       </c>
       <c r="AG39" s="70">
-        <f t="shared" si="56"/>
-        <v>47872.81895623642</v>
+        <f t="shared" si="48"/>
+        <v>54804.803141099459</v>
       </c>
       <c r="AH39" s="70">
-        <f t="shared" si="56"/>
-        <v>51702.644472735337</v>
+        <f t="shared" si="48"/>
+        <v>56996.995266743441</v>
       </c>
       <c r="AI39" s="70">
-        <f t="shared" si="56"/>
-        <v>54804.803141099459</v>
+        <f t="shared" si="48"/>
+        <v>58706.905124745746</v>
       </c>
       <c r="AJ39" s="70">
-        <f t="shared" si="56"/>
-        <v>56996.995266743441</v>
-      </c>
-      <c r="AK39" s="70">
-        <f t="shared" si="56"/>
-        <v>58706.905124745746</v>
-      </c>
-      <c r="AL39" s="70">
-        <f t="shared" si="56"/>
+        <f t="shared" si="48"/>
         <v>59881.043227240662</v>
       </c>
     </row>
-    <row r="40" spans="2:90">
+    <row r="40" spans="2:88">
       <c r="B40" s="62" t="s">
         <v>546</v>
       </c>
       <c r="C40" s="1">
-        <f t="shared" ref="C40:M40" si="57">C5</f>
+        <f t="shared" ref="C40:M40" si="49">C5</f>
         <v>3333</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>3731</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>3383</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>4534</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>3642</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>4010</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>3623</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>4708</v>
       </c>
       <c r="K40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>3835</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>4217</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="49"/>
         <v>4089</v>
       </c>
+      <c r="W40" s="1">
+        <f>W5</f>
+        <v>13835</v>
+      </c>
+      <c r="X40" s="1">
+        <f>SUM(C40:F40)</f>
+        <v>14981</v>
+      </c>
       <c r="Y40" s="1">
-        <f>Y5</f>
-        <v>13835</v>
-      </c>
-      <c r="Z40" s="1">
-        <f t="shared" si="54"/>
-        <v>14981</v>
-      </c>
-      <c r="AA40" s="1">
-        <f t="shared" si="55"/>
+        <f>SUM(G40:J40)</f>
         <v>15983</v>
       </c>
+      <c r="Z40" s="70">
+        <f t="shared" ref="Z40:AJ40" si="50">Z5</f>
+        <v>16814.116000000002</v>
+      </c>
+      <c r="AA40" s="70">
+        <f t="shared" si="50"/>
+        <v>18293.758208000003</v>
+      </c>
       <c r="AB40" s="70">
-        <f t="shared" ref="AB40:AL40" si="58">AB5</f>
-        <v>16814.116000000002</v>
+        <f t="shared" si="50"/>
+        <v>20287.777852672003</v>
       </c>
       <c r="AC40" s="70">
-        <f t="shared" si="58"/>
-        <v>18293.758208000003</v>
+        <f t="shared" si="50"/>
+        <v>22499.145638613252</v>
       </c>
       <c r="AD40" s="70">
-        <f t="shared" si="58"/>
-        <v>20287.777852672003</v>
+        <f t="shared" si="50"/>
+        <v>25829.019193128013</v>
       </c>
       <c r="AE40" s="70">
-        <f t="shared" si="58"/>
-        <v>22499.145638613252</v>
+        <f t="shared" si="50"/>
+        <v>29845.431677659417</v>
       </c>
       <c r="AF40" s="70">
-        <f t="shared" si="58"/>
-        <v>25829.019193128013</v>
+        <f t="shared" si="50"/>
+        <v>34322.246429308325</v>
       </c>
       <c r="AG40" s="70">
-        <f t="shared" si="58"/>
-        <v>29845.431677659417</v>
+        <f t="shared" si="50"/>
+        <v>39127.360929411494</v>
       </c>
       <c r="AH40" s="70">
-        <f t="shared" si="58"/>
-        <v>34322.246429308325</v>
+        <f t="shared" si="50"/>
+        <v>42257.549803764414</v>
       </c>
       <c r="AI40" s="70">
-        <f t="shared" si="58"/>
-        <v>39127.360929411494</v>
+        <f t="shared" si="50"/>
+        <v>45215.578290027923</v>
       </c>
       <c r="AJ40" s="70">
-        <f t="shared" si="58"/>
-        <v>42257.549803764414</v>
-      </c>
-      <c r="AK40" s="70">
-        <f t="shared" si="58"/>
-        <v>45215.578290027923</v>
-      </c>
-      <c r="AL40" s="70">
-        <f t="shared" si="58"/>
+        <f t="shared" si="50"/>
         <v>47476.357204529319</v>
       </c>
     </row>
-    <row r="41" spans="2:90" s="2" customFormat="1" ht="15">
+    <row r="41" spans="2:88" s="2" customFormat="1" ht="15">
       <c r="B41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" ref="C41" si="59">SUM(C39:C40)</f>
+        <f t="shared" ref="C41" si="51">SUM(C39:C40)</f>
         <v>6822</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41" si="60">SUM(D39:D40)</f>
+        <f t="shared" ref="D41" si="52">SUM(D39:D40)</f>
         <v>8119</v>
       </c>
       <c r="E41" s="2">
-        <f t="shared" ref="E41" si="61">SUM(E39:E40)</f>
+        <f t="shared" ref="E41" si="53">SUM(E39:E40)</f>
         <v>8252</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" ref="F41" si="62">SUM(F39:F40)</f>
+        <f t="shared" ref="F41" si="54">SUM(F39:F40)</f>
         <v>10046</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" ref="G41:K41" si="63">SUM(G39:G40)</f>
+        <f t="shared" ref="G41:K41" si="55">SUM(G39:G40)</f>
         <v>7259</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="55"/>
         <v>8204</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="55"/>
         <v>8913</v>
       </c>
       <c r="J41" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="55"/>
         <v>10559</v>
       </c>
       <c r="K41" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="55"/>
         <v>8032</v>
       </c>
       <c r="L41" s="2">
@@ -13857,62 +13854,64 @@
       <c r="P41" s="34"/>
       <c r="Q41" s="34"/>
       <c r="R41" s="34"/>
+      <c r="W41" s="2">
+        <f>W6</f>
+        <v>29654</v>
+      </c>
+      <c r="X41" s="2">
+        <f>SUM(C41:F41)</f>
+        <v>33239</v>
+      </c>
       <c r="Y41" s="2">
-        <f>Y6</f>
-        <v>29654</v>
-      </c>
-      <c r="Z41" s="2">
-        <f t="shared" si="54"/>
-        <v>33239</v>
-      </c>
-      <c r="AA41" s="2">
-        <f t="shared" si="55"/>
+        <f>SUM(G41:J41)</f>
         <v>34935</v>
       </c>
+      <c r="Z41" s="71">
+        <f t="shared" ref="Z41:AJ41" si="56">Z6</f>
+        <v>38372.016000000003</v>
+      </c>
+      <c r="AA41" s="71">
+        <f t="shared" si="56"/>
+        <v>44012.332907999997</v>
+      </c>
       <c r="AB41" s="71">
-        <f t="shared" ref="AB41:AL41" si="64">AB6</f>
-        <v>38372.016000000003</v>
+        <f t="shared" si="56"/>
+        <v>51021.474619172004</v>
       </c>
       <c r="AC41" s="71">
-        <f t="shared" si="64"/>
-        <v>44012.332907999997</v>
+        <f t="shared" si="56"/>
+        <v>59179.812729430996</v>
       </c>
       <c r="AD41" s="71">
-        <f t="shared" si="64"/>
-        <v>51021.474619172004</v>
+        <f t="shared" si="56"/>
+        <v>68231.870350113328</v>
       </c>
       <c r="AE41" s="71">
-        <f t="shared" si="64"/>
-        <v>59179.812729430996</v>
+        <f t="shared" si="56"/>
+        <v>77718.250633895834</v>
       </c>
       <c r="AF41" s="71">
-        <f t="shared" si="64"/>
-        <v>68231.870350113328</v>
+        <f t="shared" si="56"/>
+        <v>86024.890902043669</v>
       </c>
       <c r="AG41" s="71">
-        <f t="shared" si="64"/>
-        <v>77718.250633895834</v>
+        <f t="shared" si="56"/>
+        <v>93932.164070510946</v>
       </c>
       <c r="AH41" s="71">
-        <f t="shared" si="64"/>
-        <v>86024.890902043669</v>
+        <f t="shared" si="56"/>
+        <v>99254.545070507855</v>
       </c>
       <c r="AI41" s="71">
-        <f t="shared" si="64"/>
-        <v>93932.164070510946</v>
+        <f t="shared" si="56"/>
+        <v>103922.48341477367</v>
       </c>
       <c r="AJ41" s="71">
-        <f t="shared" si="64"/>
-        <v>99254.545070507855</v>
-      </c>
-      <c r="AK41" s="71">
-        <f t="shared" si="64"/>
-        <v>103922.48341477367</v>
-      </c>
-      <c r="AL41" s="71">
-        <f t="shared" si="64"/>
+        <f t="shared" si="56"/>
         <v>107357.40043176999</v>
       </c>
+      <c r="AK41" s="34"/>
+      <c r="AL41" s="34"/>
       <c r="AM41" s="34"/>
       <c r="AN41" s="34"/>
       <c r="AO41" s="34"/>
@@ -13963,10 +13962,8 @@
       <c r="CH41" s="34"/>
       <c r="CI41" s="34"/>
       <c r="CJ41" s="34"/>
-      <c r="CK41" s="34"/>
-      <c r="CL41" s="34"/>
-    </row>
-    <row r="42" spans="2:90">
+    </row>
+    <row r="42" spans="2:88">
       <c r="B42" s="62" t="s">
         <v>547</v>
       </c>
@@ -14005,63 +14002,63 @@
       <c r="M42" s="1">
         <v>5165</v>
       </c>
+      <c r="W42" s="1">
+        <v>16972</v>
+      </c>
+      <c r="X42" s="1">
+        <f>SUM(C42:F42)</f>
+        <v>18705</v>
+      </c>
       <c r="Y42" s="1">
-        <v>16972</v>
-      </c>
-      <c r="Z42" s="1">
-        <f t="shared" si="54"/>
-        <v>18705</v>
-      </c>
-      <c r="AA42" s="1">
-        <f t="shared" si="55"/>
+        <f>SUM(G42:J42)</f>
         <v>17989</v>
       </c>
+      <c r="Z42" s="70">
+        <f>Z39*(1-Z58)</f>
+        <v>19294.320499999998</v>
+      </c>
+      <c r="AA42" s="70">
+        <f t="shared" ref="AA42:AJ42" si="57">AA39*(1-AA58)</f>
+        <v>22760.938609499997</v>
+      </c>
       <c r="AB42" s="70">
-        <f>AB39*(1-AB58)</f>
-        <v>19240.425749999999</v>
+        <f t="shared" si="57"/>
+        <v>26738.316186854998</v>
       </c>
       <c r="AC42" s="70">
-        <f t="shared" ref="AC42:AL42" si="65">AC39*(1-AC58)</f>
-        <v>22632.345735999999</v>
+        <f t="shared" si="57"/>
+        <v>31361.970362649172</v>
       </c>
       <c r="AD42" s="70">
-        <f t="shared" si="65"/>
-        <v>26430.979219189998</v>
+        <f t="shared" si="57"/>
+        <v>36042.423483437517</v>
       </c>
       <c r="AE42" s="70">
-        <f t="shared" si="65"/>
-        <v>31361.970362649172</v>
+        <f t="shared" si="57"/>
+        <v>40452.532018019774</v>
       </c>
       <c r="AF42" s="70">
-        <f t="shared" si="65"/>
-        <v>36042.423483437517</v>
+        <f t="shared" si="57"/>
+        <v>43430.221357097682</v>
       </c>
       <c r="AG42" s="70">
-        <f t="shared" si="65"/>
-        <v>40452.532018019774</v>
+        <f t="shared" si="57"/>
+        <v>46036.034638523546</v>
       </c>
       <c r="AH42" s="70">
-        <f t="shared" si="65"/>
-        <v>43430.221357097682</v>
+        <f t="shared" si="57"/>
+        <v>47877.47602406449</v>
       </c>
       <c r="AI42" s="70">
-        <f t="shared" si="65"/>
-        <v>46036.034638523546</v>
+        <f t="shared" si="57"/>
+        <v>49313.800304786426</v>
       </c>
       <c r="AJ42" s="70">
-        <f t="shared" si="65"/>
-        <v>47877.47602406449</v>
-      </c>
-      <c r="AK42" s="70">
-        <f t="shared" si="65"/>
-        <v>49313.800304786426</v>
-      </c>
-      <c r="AL42" s="70">
-        <f t="shared" si="65"/>
+        <f t="shared" si="57"/>
         <v>50300.076310882156</v>
       </c>
     </row>
-    <row r="43" spans="2:90">
+    <row r="43" spans="2:88">
       <c r="B43" s="62" t="s">
         <v>548</v>
       </c>
@@ -14100,100 +14097,100 @@
       <c r="M43" s="1">
         <v>2906</v>
       </c>
+      <c r="W43" s="1">
+        <v>9224</v>
+      </c>
+      <c r="X43" s="1">
+        <f>SUM(C43:F43)</f>
+        <v>9716</v>
+      </c>
       <c r="Y43" s="1">
-        <v>9224</v>
-      </c>
-      <c r="Z43" s="1">
-        <f t="shared" si="54"/>
-        <v>9716</v>
-      </c>
-      <c r="AA43" s="1">
-        <f t="shared" si="55"/>
+        <f>SUM(G43:J43)</f>
         <v>10861</v>
       </c>
+      <c r="Z43" s="70">
+        <f>Z40*(1-Z59)</f>
+        <v>11853.951780000003</v>
+      </c>
+      <c r="AA43" s="70">
+        <f t="shared" ref="AA43:AJ43" si="58">AA40*(1-AA59)</f>
+        <v>12439.75558144</v>
+      </c>
       <c r="AB43" s="70">
-        <f>AB40*(1-AB59)</f>
-        <v>11685.810620000002</v>
+        <f t="shared" si="58"/>
+        <v>13187.055604236803</v>
       </c>
       <c r="AC43" s="70">
-        <f t="shared" ref="AC43:AL43" si="66">AC40*(1-AC59)</f>
-        <v>12439.75558144</v>
+        <f t="shared" si="58"/>
+        <v>14399.453208712483</v>
       </c>
       <c r="AD43" s="70">
-        <f t="shared" si="66"/>
-        <v>13187.055604236803</v>
+        <f t="shared" si="58"/>
+        <v>16401.427187636287</v>
       </c>
       <c r="AE43" s="70">
-        <f t="shared" si="66"/>
-        <v>14399.453208712483</v>
+        <f t="shared" si="58"/>
+        <v>18802.621956925432</v>
       </c>
       <c r="AF43" s="70">
-        <f t="shared" si="66"/>
-        <v>16401.427187636287</v>
+        <f t="shared" si="58"/>
+        <v>21623.015250464246</v>
       </c>
       <c r="AG43" s="70">
-        <f t="shared" si="66"/>
-        <v>18802.621956925432</v>
+        <f t="shared" si="58"/>
+        <v>24650.237385529243</v>
       </c>
       <c r="AH43" s="70">
-        <f t="shared" si="66"/>
-        <v>21623.015250464246</v>
+        <f t="shared" si="58"/>
+        <v>26622.256376371581</v>
       </c>
       <c r="AI43" s="70">
-        <f t="shared" si="66"/>
-        <v>24650.237385529243</v>
+        <f t="shared" si="58"/>
+        <v>28485.814322717593</v>
       </c>
       <c r="AJ43" s="70">
-        <f t="shared" si="66"/>
-        <v>26622.256376371581</v>
-      </c>
-      <c r="AK43" s="70">
-        <f t="shared" si="66"/>
-        <v>28485.814322717593</v>
-      </c>
-      <c r="AL43" s="70">
-        <f t="shared" si="66"/>
+        <f t="shared" si="58"/>
         <v>29910.105038853471</v>
       </c>
     </row>
-    <row r="44" spans="2:90">
+    <row r="44" spans="2:88">
       <c r="B44" s="69" t="s">
         <v>64</v>
       </c>
       <c r="C44" s="1">
-        <f t="shared" ref="C44:K44" si="67">SUM(C42:C43)</f>
+        <f t="shared" ref="C44:K44" si="59">SUM(C42:C43)</f>
         <v>5903</v>
       </c>
       <c r="D44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>6972</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>7201</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>8345</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>6109</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>6502</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>7804</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>8435</v>
       </c>
       <c r="K44" s="1">
-        <f t="shared" si="67"/>
+        <f t="shared" si="59"/>
         <v>6562</v>
       </c>
       <c r="L44" s="1">
@@ -14204,169 +14201,169 @@
         <f>SUM(M42:M43)</f>
         <v>8071</v>
       </c>
+      <c r="W44" s="1">
+        <f>W42+W43</f>
+        <v>26196</v>
+      </c>
+      <c r="X44" s="1">
+        <f>SUM(C44:F44)</f>
+        <v>28421</v>
+      </c>
       <c r="Y44" s="1">
-        <f>Y42+Y43</f>
-        <v>26196</v>
-      </c>
-      <c r="Z44" s="1">
-        <f t="shared" ref="Z44" si="68">SUM(C44:F44)</f>
-        <v>28421</v>
-      </c>
-      <c r="AA44" s="1">
-        <f t="shared" si="55"/>
+        <f>SUM(G44:J44)</f>
         <v>28850</v>
       </c>
+      <c r="Z44" s="70">
+        <f>Z43+Z42</f>
+        <v>31148.272280000001</v>
+      </c>
+      <c r="AA44" s="70">
+        <f t="shared" ref="AA44:AJ44" si="60">AA43+AA42</f>
+        <v>35200.694190939997</v>
+      </c>
       <c r="AB44" s="70">
-        <f>AB43+AB42</f>
-        <v>30926.236369999999</v>
+        <f t="shared" si="60"/>
+        <v>39925.371791091799</v>
       </c>
       <c r="AC44" s="70">
-        <f t="shared" ref="AC44:AL44" si="69">AC43+AC42</f>
-        <v>35072.10131744</v>
+        <f t="shared" si="60"/>
+        <v>45761.423571361651</v>
       </c>
       <c r="AD44" s="70">
-        <f t="shared" si="69"/>
-        <v>39618.034823426802</v>
+        <f t="shared" si="60"/>
+        <v>52443.8506710738</v>
       </c>
       <c r="AE44" s="70">
-        <f t="shared" si="69"/>
-        <v>45761.423571361651</v>
+        <f t="shared" si="60"/>
+        <v>59255.153974945206</v>
       </c>
       <c r="AF44" s="70">
-        <f t="shared" si="69"/>
-        <v>52443.8506710738</v>
+        <f t="shared" si="60"/>
+        <v>65053.236607561928</v>
       </c>
       <c r="AG44" s="70">
-        <f t="shared" si="69"/>
-        <v>59255.153974945206</v>
+        <f t="shared" si="60"/>
+        <v>70686.272024052785</v>
       </c>
       <c r="AH44" s="70">
-        <f t="shared" si="69"/>
-        <v>65053.236607561928</v>
+        <f t="shared" si="60"/>
+        <v>74499.732400436071</v>
       </c>
       <c r="AI44" s="70">
-        <f t="shared" si="69"/>
-        <v>70686.272024052785</v>
+        <f t="shared" si="60"/>
+        <v>77799.614627504023</v>
       </c>
       <c r="AJ44" s="70">
-        <f t="shared" si="69"/>
-        <v>74499.732400436071</v>
-      </c>
-      <c r="AK44" s="70">
-        <f t="shared" si="69"/>
-        <v>77799.614627504023</v>
-      </c>
-      <c r="AL44" s="70">
-        <f t="shared" si="69"/>
+        <f t="shared" si="60"/>
         <v>80210.18134973562</v>
       </c>
     </row>
-    <row r="45" spans="2:90">
+    <row r="45" spans="2:88">
       <c r="B45" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C45" s="1">
-        <f t="shared" ref="C45" si="70">C41-SUM(C42:C43)</f>
+        <f t="shared" ref="C45" si="61">C41-SUM(C42:C43)</f>
         <v>919</v>
       </c>
       <c r="D45" s="1">
-        <f t="shared" ref="D45" si="71">D41-SUM(D42:D43)</f>
+        <f t="shared" ref="D45" si="62">D41-SUM(D42:D43)</f>
         <v>1147</v>
       </c>
       <c r="E45" s="1">
-        <f t="shared" ref="E45" si="72">E41-SUM(E42:E43)</f>
+        <f t="shared" ref="E45" si="63">E41-SUM(E42:E43)</f>
         <v>1051</v>
       </c>
       <c r="F45" s="1">
-        <f t="shared" ref="F45" si="73">F41-SUM(F42:F43)</f>
+        <f t="shared" ref="F45" si="64">F41-SUM(F42:F43)</f>
         <v>1701</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" ref="G45:L45" si="74">G41-SUM(G42:G43)</f>
+        <f t="shared" ref="G45:L45" si="65">G41-SUM(G42:G43)</f>
         <v>1150</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="65"/>
         <v>1702</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="65"/>
         <v>1109</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="65"/>
         <v>2124</v>
       </c>
       <c r="K45" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="65"/>
         <v>1470</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="74"/>
+        <f t="shared" si="65"/>
         <v>1846</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" ref="M45" si="75">M41-SUM(M42:M43)</f>
+        <f t="shared" ref="M45" si="66">M41-SUM(M42:M43)</f>
         <v>1898</v>
       </c>
+      <c r="W45" s="1">
+        <f t="shared" ref="W45" si="67">W41-SUM(W42:W43)</f>
+        <v>3458</v>
+      </c>
+      <c r="X45" s="1">
+        <f>SUM(C45:F45)</f>
+        <v>4818</v>
+      </c>
       <c r="Y45" s="1">
-        <f t="shared" ref="Y45" si="76">Y41-SUM(Y42:Y43)</f>
-        <v>3458</v>
-      </c>
-      <c r="Z45" s="1">
-        <f t="shared" si="54"/>
-        <v>4818</v>
-      </c>
-      <c r="AA45" s="1">
-        <f t="shared" si="55"/>
+        <f>SUM(G45:J45)</f>
         <v>6085</v>
       </c>
+      <c r="Z45" s="70">
+        <f>Z41-SUM(Z42:Z43)</f>
+        <v>7223.7437200000022</v>
+      </c>
+      <c r="AA45" s="70">
+        <f t="shared" ref="AA45:AJ45" si="68">AA41-SUM(AA42:AA43)</f>
+        <v>8811.6387170599992</v>
+      </c>
       <c r="AB45" s="70">
-        <f>AB41-SUM(AB42:AB43)</f>
-        <v>7445.7796300000045</v>
+        <f t="shared" si="68"/>
+        <v>11096.102828080206</v>
       </c>
       <c r="AC45" s="70">
-        <f t="shared" ref="AC45:AL45" si="77">AC41-SUM(AC42:AC43)</f>
-        <v>8940.2315905599971</v>
+        <f t="shared" si="68"/>
+        <v>13418.389158069345</v>
       </c>
       <c r="AD45" s="70">
-        <f t="shared" si="77"/>
-        <v>11403.439795745202</v>
+        <f t="shared" si="68"/>
+        <v>15788.019679039528</v>
       </c>
       <c r="AE45" s="70">
-        <f t="shared" si="77"/>
-        <v>13418.389158069345</v>
+        <f t="shared" si="68"/>
+        <v>18463.096658950628</v>
       </c>
       <c r="AF45" s="70">
-        <f t="shared" si="77"/>
-        <v>15788.019679039528</v>
+        <f t="shared" si="68"/>
+        <v>20971.654294481741</v>
       </c>
       <c r="AG45" s="70">
-        <f t="shared" si="77"/>
-        <v>18463.096658950628</v>
+        <f t="shared" si="68"/>
+        <v>23245.892046458161</v>
       </c>
       <c r="AH45" s="70">
-        <f t="shared" si="77"/>
-        <v>20971.654294481741</v>
+        <f t="shared" si="68"/>
+        <v>24754.812670071784</v>
       </c>
       <c r="AI45" s="70">
-        <f t="shared" si="77"/>
-        <v>23245.892046458161</v>
+        <f t="shared" si="68"/>
+        <v>26122.868787269646</v>
       </c>
       <c r="AJ45" s="70">
-        <f t="shared" si="77"/>
-        <v>24754.812670071784</v>
-      </c>
-      <c r="AK45" s="70">
-        <f t="shared" si="77"/>
-        <v>26122.868787269646</v>
-      </c>
-      <c r="AL45" s="70">
-        <f t="shared" si="77"/>
+        <f t="shared" si="68"/>
         <v>27147.219082034368</v>
       </c>
     </row>
-    <row r="46" spans="2:90">
+    <row r="46" spans="2:88">
       <c r="B46" s="1" t="s">
         <v>549</v>
       </c>
@@ -14405,63 +14402,63 @@
       <c r="M46" s="1">
         <v>1221</v>
       </c>
+      <c r="W46" s="1">
+        <v>5360</v>
+      </c>
+      <c r="X46" s="1">
+        <f>SUM(C46:F46)</f>
+        <v>4845</v>
+      </c>
       <c r="Y46" s="1">
-        <v>5360</v>
-      </c>
-      <c r="Z46" s="1">
-        <f t="shared" si="54"/>
-        <v>4845</v>
-      </c>
-      <c r="AA46" s="1">
-        <f t="shared" ref="AA46:AA56" si="78">SUM(G46:J46)</f>
+        <f>SUM(G46:J46)</f>
         <v>4632</v>
       </c>
+      <c r="Z46" s="70">
+        <f>Z41*Z61</f>
+        <v>5087.7108376127098</v>
+      </c>
+      <c r="AA46" s="70">
+        <f t="shared" ref="AA46:AJ46" si="69">AA41*AA61</f>
+        <v>5721.6032780400001</v>
+      </c>
       <c r="AB46" s="70">
-        <f>AB41*AB61</f>
-        <v>5087.7108376127098</v>
+        <f t="shared" si="69"/>
+        <v>6581.7702258731888</v>
       </c>
       <c r="AC46" s="70">
-        <f t="shared" ref="AC46:AL46" si="79">AC41*AC61</f>
-        <v>5835.5553464965215</v>
+        <f t="shared" si="69"/>
+        <v>7575.0160293671679</v>
       </c>
       <c r="AD46" s="70">
-        <f t="shared" si="79"/>
-        <v>6764.8910959211316</v>
+        <f t="shared" si="69"/>
+        <v>8665.4475344643924</v>
       </c>
       <c r="AE46" s="70">
-        <f t="shared" si="79"/>
-        <v>7846.597754765261</v>
+        <f t="shared" si="69"/>
+        <v>9792.4995798708751</v>
       </c>
       <c r="AF46" s="70">
-        <f t="shared" si="79"/>
-        <v>9046.8018738149403</v>
+        <f t="shared" si="69"/>
+        <v>10753.111362755459</v>
       </c>
       <c r="AG46" s="70">
-        <f t="shared" si="79"/>
-        <v>10304.592441282539</v>
+        <f t="shared" si="69"/>
+        <v>11741.520508813868</v>
       </c>
       <c r="AH46" s="70">
-        <f t="shared" si="79"/>
-        <v>11405.962348884108</v>
+        <f t="shared" si="69"/>
+        <v>12406.818133813482</v>
       </c>
       <c r="AI46" s="70">
-        <f t="shared" si="79"/>
-        <v>12454.380534552933</v>
+        <f t="shared" si="69"/>
+        <v>12990.310426846709</v>
       </c>
       <c r="AJ46" s="70">
-        <f t="shared" si="79"/>
-        <v>13160.070209434447</v>
-      </c>
-      <c r="AK46" s="70">
-        <f t="shared" si="79"/>
-        <v>13778.987925496827</v>
-      </c>
-      <c r="AL46" s="70">
-        <f t="shared" si="79"/>
-        <v>14234.42046085469</v>
-      </c>
-    </row>
-    <row r="47" spans="2:90">
+        <f t="shared" si="69"/>
+        <v>13419.675053971248</v>
+      </c>
+    </row>
+    <row r="47" spans="2:88">
       <c r="B47" s="1" t="s">
         <v>550</v>
       </c>
@@ -14500,100 +14497,100 @@
       <c r="M47" s="1">
         <v>310</v>
       </c>
+      <c r="W47" s="1">
+        <v>979</v>
+      </c>
+      <c r="X47" s="1">
+        <f>SUM(C47:F47)</f>
+        <v>896</v>
+      </c>
       <c r="Y47" s="1">
-        <v>979</v>
-      </c>
-      <c r="Z47" s="1">
-        <f t="shared" si="54"/>
-        <v>896</v>
-      </c>
-      <c r="AA47" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G47:J47)</f>
         <v>982</v>
       </c>
+      <c r="Z47" s="70">
+        <f>Z41*Z62</f>
+        <v>1078.6122717045944</v>
+      </c>
+      <c r="AA47" s="70">
+        <f t="shared" ref="AA47:AJ47" si="70">AA41*AA62</f>
+        <v>1320.3699872399998</v>
+      </c>
       <c r="AB47" s="70">
-        <f>AB41*AB62</f>
-        <v>1078.6122717045944</v>
+        <f t="shared" si="70"/>
+        <v>1581.6657131943321</v>
       </c>
       <c r="AC47" s="70">
-        <f t="shared" ref="AC47:AL47" si="80">AC41*AC62</f>
-        <v>1237.1578908159725</v>
+        <f t="shared" si="70"/>
+        <v>1893.754007341792</v>
       </c>
       <c r="AD47" s="70">
-        <f t="shared" si="80"/>
-        <v>1434.1802798347476</v>
+        <f t="shared" si="70"/>
+        <v>2251.6517215537401</v>
       </c>
       <c r="AE47" s="70">
-        <f t="shared" si="80"/>
-        <v>1663.5058279748457</v>
+        <f t="shared" si="70"/>
+        <v>2642.4205215524585</v>
       </c>
       <c r="AF47" s="70">
-        <f t="shared" si="80"/>
-        <v>1917.9532469961725</v>
+        <f t="shared" si="70"/>
+        <v>3010.8711815715287</v>
       </c>
       <c r="AG47" s="70">
-        <f t="shared" si="80"/>
-        <v>2184.6091919990185</v>
+        <f t="shared" si="70"/>
+        <v>3099.7614143268615</v>
       </c>
       <c r="AH47" s="70">
-        <f t="shared" si="80"/>
-        <v>2418.1034167971056</v>
+        <f t="shared" si="70"/>
+        <v>3176.1454422562515</v>
       </c>
       <c r="AI47" s="70">
-        <f t="shared" si="80"/>
-        <v>2640.3716936379487</v>
+        <f t="shared" si="70"/>
+        <v>3221.5969858579838</v>
       </c>
       <c r="AJ47" s="70">
-        <f t="shared" si="80"/>
-        <v>2789.980342328287</v>
-      </c>
-      <c r="AK47" s="70">
-        <f t="shared" si="80"/>
-        <v>2921.1930360185411</v>
-      </c>
-      <c r="AL47" s="70">
-        <f t="shared" si="80"/>
-        <v>3017.7463066837877</v>
-      </c>
-    </row>
-    <row r="48" spans="2:90">
+        <f t="shared" si="70"/>
+        <v>3220.7220129530997</v>
+      </c>
+    </row>
+    <row r="48" spans="2:88">
       <c r="B48" s="1" t="s">
         <v>551</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" ref="C48" si="81">C45-SUM(C46:C47)</f>
+        <f t="shared" ref="C48" si="71">C45-SUM(C46:C47)</f>
         <v>-469</v>
       </c>
       <c r="D48" s="1">
-        <f t="shared" ref="D48" si="82">D45-SUM(D46:D47)</f>
+        <f t="shared" ref="D48" si="72">D45-SUM(D46:D47)</f>
         <v>-341</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" ref="E48" si="83">E45-SUM(E46:E47)</f>
+        <f t="shared" ref="E48" si="73">E45-SUM(E46:E47)</f>
         <v>-307</v>
       </c>
       <c r="F48" s="1">
-        <f t="shared" ref="F48" si="84">F45-SUM(F46:F47)</f>
+        <f t="shared" ref="F48" si="74">F45-SUM(F46:F47)</f>
         <v>194</v>
       </c>
       <c r="G48" s="1">
-        <f t="shared" ref="G48:K48" si="85">G45-SUM(G46:G47)</f>
+        <f t="shared" ref="G48:K48" si="75">G45-SUM(G46:G47)</f>
         <v>-289</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="75"/>
         <v>527</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="75"/>
         <v>-359</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="75"/>
         <v>592</v>
       </c>
       <c r="K48" s="1">
-        <f t="shared" si="85"/>
+        <f t="shared" si="75"/>
         <v>43</v>
       </c>
       <c r="L48" s="1">
@@ -14604,64 +14601,64 @@
         <f>M45-SUM(M46:M47)</f>
         <v>367</v>
       </c>
+      <c r="W48" s="1">
+        <f t="shared" ref="W48" si="76">W45-SUM(W46:W47)</f>
+        <v>-2881</v>
+      </c>
+      <c r="X48" s="1">
+        <f>SUM(C48:F48)</f>
+        <v>-923</v>
+      </c>
       <c r="Y48" s="1">
-        <f t="shared" ref="Y48" si="86">Y45-SUM(Y46:Y47)</f>
-        <v>-2881</v>
-      </c>
-      <c r="Z48" s="1">
-        <f t="shared" si="54"/>
-        <v>-923</v>
-      </c>
-      <c r="AA48" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G48:J48)</f>
         <v>471</v>
       </c>
+      <c r="Z48" s="70">
+        <f>Z45-SUM(Z46:Z47)</f>
+        <v>1057.4206106826978</v>
+      </c>
+      <c r="AA48" s="70">
+        <f t="shared" ref="AA48:AJ48" si="77">AA45-SUM(AA46:AA47)</f>
+        <v>1769.6654517799998</v>
+      </c>
       <c r="AB48" s="70">
-        <f>AB45-SUM(AB46:AB47)</f>
-        <v>1279.4565206827001</v>
+        <f t="shared" si="77"/>
+        <v>2932.6668890126848</v>
       </c>
       <c r="AC48" s="70">
-        <f t="shared" ref="AC48:AL48" si="87">AC45-SUM(AC46:AC47)</f>
-        <v>1867.518353247503</v>
+        <f t="shared" si="77"/>
+        <v>3949.6191213603852</v>
       </c>
       <c r="AD48" s="70">
-        <f t="shared" si="87"/>
-        <v>3204.3684199893232</v>
+        <f t="shared" si="77"/>
+        <v>4870.9204230213945</v>
       </c>
       <c r="AE48" s="70">
-        <f t="shared" si="87"/>
-        <v>3908.2855753292388</v>
+        <f t="shared" si="77"/>
+        <v>6028.1765575272948</v>
       </c>
       <c r="AF48" s="70">
-        <f t="shared" si="87"/>
-        <v>4823.2645582284149</v>
+        <f t="shared" si="77"/>
+        <v>7207.6717501547537</v>
       </c>
       <c r="AG48" s="70">
-        <f t="shared" si="87"/>
-        <v>5973.8950256690696</v>
+        <f t="shared" si="77"/>
+        <v>8404.6101233174304</v>
       </c>
       <c r="AH48" s="70">
-        <f t="shared" si="87"/>
-        <v>7147.5885288005265</v>
+        <f t="shared" si="77"/>
+        <v>9171.8490940020511</v>
       </c>
       <c r="AI48" s="70">
-        <f t="shared" si="87"/>
-        <v>8151.1398182672783</v>
+        <f t="shared" si="77"/>
+        <v>9910.9613745649549</v>
       </c>
       <c r="AJ48" s="70">
-        <f t="shared" si="87"/>
-        <v>8804.7621183090505</v>
-      </c>
-      <c r="AK48" s="70">
-        <f t="shared" si="87"/>
-        <v>9422.6878257542776</v>
-      </c>
-      <c r="AL48" s="70">
-        <f t="shared" si="87"/>
-        <v>9895.0523144958897</v>
-      </c>
-    </row>
-    <row r="49" spans="2:90">
+        <f t="shared" si="77"/>
+        <v>10506.822015110018</v>
+      </c>
+    </row>
+    <row r="49" spans="2:88">
       <c r="B49" s="1" t="s">
         <v>552</v>
       </c>
@@ -14700,63 +14697,63 @@
       <c r="M49" s="1">
         <v>44</v>
       </c>
+      <c r="W49" s="1">
+        <v>-151</v>
+      </c>
+      <c r="X49" s="1">
+        <f>SUM(C49:F49)</f>
+        <v>-98</v>
+      </c>
       <c r="Y49" s="1">
-        <v>-151</v>
-      </c>
-      <c r="Z49" s="1">
-        <f t="shared" si="54"/>
-        <v>-98</v>
-      </c>
-      <c r="AA49" s="1">
+        <f>SUM(G49:J49)</f>
+        <v>120</v>
+      </c>
+      <c r="Z49" s="70">
+        <f t="shared" ref="Z49:AJ49" si="78">Y67*$AI$69</f>
+        <v>943.57500000000005</v>
+      </c>
+      <c r="AA49" s="70">
         <f t="shared" si="78"/>
-        <v>120</v>
+        <v>1276.4772973975255</v>
       </c>
       <c r="AB49" s="70">
-        <f t="shared" ref="AB49:AL49" si="88">AA67*$AK$69</f>
-        <v>943.57500000000005</v>
+        <f t="shared" si="78"/>
+        <v>1718.8115301187495</v>
       </c>
       <c r="AC49" s="70">
-        <f t="shared" si="88"/>
-        <v>1300.4202085320605</v>
+        <f t="shared" si="78"/>
+        <v>2322.4264164432402</v>
       </c>
       <c r="AD49" s="70">
-        <f t="shared" si="88"/>
-        <v>1753.6795256436876</v>
+        <f t="shared" si="78"/>
+        <v>3086.268759699884</v>
       </c>
       <c r="AE49" s="70">
-        <f t="shared" si="88"/>
-        <v>2385.1462534508469</v>
+        <f t="shared" si="78"/>
+        <v>4017.198998338527</v>
       </c>
       <c r="AF49" s="70">
-        <f t="shared" si="88"/>
-        <v>3150.9315412427018</v>
+        <f t="shared" si="78"/>
+        <v>5152.9082174202968</v>
       </c>
       <c r="AG49" s="70">
-        <f t="shared" si="88"/>
-        <v>4083.4068582680679</v>
+        <f t="shared" si="78"/>
+        <v>6515.1836478913347</v>
       </c>
       <c r="AH49" s="70">
-        <f t="shared" si="88"/>
-        <v>5220.1995842551169</v>
+        <f t="shared" si="78"/>
+        <v>8127.4518044026718</v>
       </c>
       <c r="AI49" s="70">
-        <f t="shared" si="88"/>
-        <v>6583.1298747430683</v>
+        <f t="shared" si="78"/>
+        <v>9974.7485392742637</v>
       </c>
       <c r="AJ49" s="70">
-        <f t="shared" si="88"/>
-        <v>8178.5431687500804</v>
-      </c>
-      <c r="AK49" s="70">
-        <f t="shared" si="88"/>
-        <v>9997.1317023309257</v>
-      </c>
-      <c r="AL49" s="70">
-        <f t="shared" si="88"/>
-        <v>12057.403138145832</v>
-      </c>
-    </row>
-    <row r="50" spans="2:90">
+        <f t="shared" si="78"/>
+        <v>12077.346116634921</v>
+      </c>
+    </row>
+    <row r="50" spans="2:88">
       <c r="B50" s="1" t="s">
         <v>553</v>
       </c>
@@ -14795,63 +14792,63 @@
       <c r="M50" s="1">
         <v>115</v>
       </c>
+      <c r="W50" s="1">
+        <v>188</v>
+      </c>
+      <c r="X50" s="1">
+        <f>SUM(C50:F50)</f>
+        <v>567</v>
+      </c>
       <c r="Y50" s="1">
-        <v>188</v>
-      </c>
-      <c r="Z50" s="1">
-        <f t="shared" si="54"/>
-        <v>567</v>
-      </c>
-      <c r="AA50" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G50:J50)</f>
         <v>536</v>
       </c>
+      <c r="Z50" s="70">
+        <f>Y50*0.95</f>
+        <v>509.2</v>
+      </c>
+      <c r="AA50" s="70">
+        <f>Z50*1.05</f>
+        <v>534.66</v>
+      </c>
       <c r="AB50" s="70">
-        <f>AA50*0.95</f>
-        <v>509.2</v>
+        <f>AA50*1.1</f>
+        <v>588.12599999999998</v>
       </c>
       <c r="AC50" s="70">
-        <f>AB50*1.05</f>
-        <v>534.66</v>
+        <f t="shared" ref="AC50:AJ50" si="79">AB50*1.1</f>
+        <v>646.93860000000006</v>
       </c>
       <c r="AD50" s="70">
-        <f>AC50*1.1</f>
-        <v>588.12599999999998</v>
+        <f t="shared" si="79"/>
+        <v>711.63246000000015</v>
       </c>
       <c r="AE50" s="70">
-        <f t="shared" ref="AE50:AL50" si="89">AD50*1.1</f>
-        <v>646.93860000000006</v>
+        <f t="shared" si="79"/>
+        <v>782.79570600000022</v>
       </c>
       <c r="AF50" s="70">
-        <f t="shared" si="89"/>
-        <v>711.63246000000015</v>
+        <f t="shared" si="79"/>
+        <v>861.07527660000028</v>
       </c>
       <c r="AG50" s="70">
-        <f t="shared" si="89"/>
-        <v>782.79570600000022</v>
+        <f t="shared" si="79"/>
+        <v>947.18280426000035</v>
       </c>
       <c r="AH50" s="70">
-        <f t="shared" si="89"/>
-        <v>861.07527660000028</v>
+        <f t="shared" si="79"/>
+        <v>1041.9010846860006</v>
       </c>
       <c r="AI50" s="70">
-        <f t="shared" si="89"/>
-        <v>947.18280426000035</v>
+        <f t="shared" si="79"/>
+        <v>1146.0911931546007</v>
       </c>
       <c r="AJ50" s="70">
-        <f t="shared" si="89"/>
-        <v>1041.9010846860006</v>
-      </c>
-      <c r="AK50" s="70">
-        <f t="shared" si="89"/>
-        <v>1146.0911931546007</v>
-      </c>
-      <c r="AL50" s="70">
-        <f t="shared" si="89"/>
+        <f t="shared" si="79"/>
         <v>1260.7003124700609</v>
       </c>
     </row>
-    <row r="51" spans="2:90">
+    <row r="51" spans="2:88">
       <c r="B51" s="1" t="s">
         <v>554</v>
       </c>
@@ -14890,100 +14887,100 @@
       <c r="M51" s="1">
         <v>221</v>
       </c>
+      <c r="W51" s="1">
+        <v>370</v>
+      </c>
+      <c r="X51" s="1">
+        <f>SUM(C51:F51)</f>
+        <v>324</v>
+      </c>
       <c r="Y51" s="1">
-        <v>370</v>
-      </c>
-      <c r="Z51" s="1">
-        <f t="shared" si="54"/>
-        <v>324</v>
-      </c>
-      <c r="AA51" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G51:J51)</f>
         <v>1372</v>
       </c>
+      <c r="Z51" s="70">
+        <f>Y51*0.965</f>
+        <v>1323.98</v>
+      </c>
+      <c r="AA51" s="70">
+        <f>Z51*1.02</f>
+        <v>1350.4596000000001</v>
+      </c>
       <c r="AB51" s="70">
-        <f>AA51*0.965</f>
-        <v>1323.98</v>
+        <f>AA51*1.04</f>
+        <v>1404.4779840000001</v>
       </c>
       <c r="AC51" s="70">
-        <f>AB51*1.02</f>
-        <v>1350.4596000000001</v>
+        <f>AB51*1.06</f>
+        <v>1488.7466630400002</v>
       </c>
       <c r="AD51" s="70">
-        <f>AC51*1.04</f>
-        <v>1404.4779840000001</v>
+        <f t="shared" ref="AD51:AJ51" si="80">AC51*1.06</f>
+        <v>1578.0714628224002</v>
       </c>
       <c r="AE51" s="70">
-        <f>AD51*1.06</f>
-        <v>1488.7466630400002</v>
+        <f t="shared" si="80"/>
+        <v>1672.7557505917443</v>
       </c>
       <c r="AF51" s="70">
-        <f t="shared" ref="AF51:AL51" si="90">AE51*1.06</f>
-        <v>1578.0714628224002</v>
+        <f t="shared" si="80"/>
+        <v>1773.1210956272491</v>
       </c>
       <c r="AG51" s="70">
-        <f t="shared" si="90"/>
-        <v>1672.7557505917443</v>
+        <f t="shared" si="80"/>
+        <v>1879.5083613648842</v>
       </c>
       <c r="AH51" s="70">
-        <f t="shared" si="90"/>
-        <v>1773.1210956272491</v>
+        <f t="shared" si="80"/>
+        <v>1992.2788630467774</v>
       </c>
       <c r="AI51" s="70">
-        <f t="shared" si="90"/>
-        <v>1879.5083613648842</v>
+        <f t="shared" si="80"/>
+        <v>2111.8155948295839</v>
       </c>
       <c r="AJ51" s="70">
-        <f t="shared" si="90"/>
-        <v>1992.2788630467774</v>
-      </c>
-      <c r="AK51" s="70">
-        <f t="shared" si="90"/>
-        <v>2111.8155948295839</v>
-      </c>
-      <c r="AL51" s="70">
-        <f t="shared" si="90"/>
+        <f t="shared" si="80"/>
         <v>2238.5245305193589</v>
       </c>
     </row>
-    <row r="52" spans="2:90">
+    <row r="52" spans="2:88">
       <c r="B52" s="1" t="s">
         <v>555</v>
       </c>
       <c r="C52" s="1">
-        <f t="shared" ref="C52" si="91">C48+SUM(C49:C51)</f>
+        <f t="shared" ref="C52" si="81">C48+SUM(C49:C51)</f>
         <v>-415</v>
       </c>
       <c r="D52" s="1">
-        <f t="shared" ref="D52" si="92">D48+SUM(D49:D51)</f>
+        <f t="shared" ref="D52" si="82">D48+SUM(D49:D51)</f>
         <v>-27</v>
       </c>
       <c r="E52" s="1">
-        <f t="shared" ref="E52" si="93">E48+SUM(E49:E51)</f>
+        <f t="shared" ref="E52" si="83">E48+SUM(E49:E51)</f>
         <v>-16</v>
       </c>
       <c r="F52" s="1">
-        <f t="shared" ref="F52" si="94">F48+SUM(F49:F51)</f>
+        <f t="shared" ref="F52" si="84">F48+SUM(F49:F51)</f>
         <v>328</v>
       </c>
       <c r="G52" s="1">
-        <f t="shared" ref="G52:K52" si="95">G48+SUM(G49:G51)</f>
+        <f t="shared" ref="G52:K52" si="85">G48+SUM(G49:G51)</f>
         <v>-96</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="85"/>
         <v>1602</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="85"/>
         <v>-122</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="85"/>
         <v>1115</v>
       </c>
       <c r="K52" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="85"/>
         <v>332</v>
       </c>
       <c r="L52" s="1">
@@ -14994,64 +14991,64 @@
         <f>M48+SUM(M49:M51)</f>
         <v>747</v>
       </c>
+      <c r="W52" s="1">
+        <f t="shared" ref="W52" si="86">W48+SUM(W49:W51)</f>
+        <v>-2474</v>
+      </c>
+      <c r="X52" s="1">
+        <f>SUM(C52:F52)</f>
+        <v>-130</v>
+      </c>
       <c r="Y52" s="1">
-        <f t="shared" ref="Y52" si="96">Y48+SUM(Y49:Y51)</f>
-        <v>-2474</v>
-      </c>
-      <c r="Z52" s="1">
-        <f t="shared" si="54"/>
-        <v>-130</v>
-      </c>
-      <c r="AA52" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G52:J52)</f>
         <v>2499</v>
       </c>
+      <c r="Z52" s="70">
+        <f>Z48+SUM(Z49:Z51)</f>
+        <v>3834.1756106826979</v>
+      </c>
+      <c r="AA52" s="70">
+        <f t="shared" ref="AA52:AJ52" si="87">AA48+SUM(AA49:AA51)</f>
+        <v>4931.2623491775248</v>
+      </c>
       <c r="AB52" s="70">
-        <f>AB48+SUM(AB49:AB51)</f>
-        <v>4056.2115206827002</v>
+        <f t="shared" si="87"/>
+        <v>6644.0824031314341</v>
       </c>
       <c r="AC52" s="70">
-        <f t="shared" ref="AC52:AL52" si="97">AC48+SUM(AC49:AC51)</f>
-        <v>5053.0581617795633</v>
+        <f t="shared" si="87"/>
+        <v>8407.7308008436266</v>
       </c>
       <c r="AD52" s="70">
-        <f t="shared" si="97"/>
-        <v>6950.6519296330107</v>
+        <f t="shared" si="87"/>
+        <v>10246.893105543679</v>
       </c>
       <c r="AE52" s="70">
-        <f t="shared" si="97"/>
-        <v>8429.117091820086</v>
+        <f t="shared" si="87"/>
+        <v>12500.927012457567</v>
       </c>
       <c r="AF52" s="70">
-        <f t="shared" si="97"/>
-        <v>10263.900022293517</v>
+        <f t="shared" si="87"/>
+        <v>14994.7763398023</v>
       </c>
       <c r="AG52" s="70">
-        <f t="shared" si="97"/>
-        <v>12512.853340528882</v>
+        <f t="shared" si="87"/>
+        <v>17746.484936833651</v>
       </c>
       <c r="AH52" s="70">
-        <f t="shared" si="97"/>
-        <v>15001.984485282894</v>
+        <f t="shared" si="87"/>
+        <v>20333.4808461375</v>
       </c>
       <c r="AI52" s="70">
-        <f t="shared" si="97"/>
-        <v>17560.960858635233</v>
+        <f t="shared" si="87"/>
+        <v>23143.616701823405</v>
       </c>
       <c r="AJ52" s="70">
-        <f t="shared" si="97"/>
-        <v>20017.485234791908</v>
-      </c>
-      <c r="AK52" s="70">
-        <f t="shared" si="97"/>
-        <v>22677.726316069391</v>
-      </c>
-      <c r="AL52" s="70">
-        <f t="shared" si="97"/>
-        <v>25451.68029563114</v>
-      </c>
-    </row>
-    <row r="53" spans="2:90">
+        <f t="shared" si="87"/>
+        <v>26083.392974734357</v>
+      </c>
+    </row>
+    <row r="53" spans="2:88">
       <c r="B53" s="1" t="s">
         <v>556</v>
       </c>
@@ -15090,63 +15087,63 @@
       <c r="M53" s="1">
         <v>293</v>
       </c>
+      <c r="W53" s="1">
+        <v>248</v>
+      </c>
+      <c r="X53" s="1">
+        <f>SUM(C53:F53)</f>
+        <v>344</v>
+      </c>
       <c r="Y53" s="1">
-        <v>248</v>
-      </c>
-      <c r="Z53" s="1">
-        <f t="shared" si="54"/>
-        <v>344</v>
-      </c>
-      <c r="AA53" s="1">
-        <f t="shared" si="78"/>
+        <f>SUM(G53:J53)</f>
         <v>939</v>
       </c>
+      <c r="Z53" s="70">
+        <f>Z52*Z64</f>
+        <v>939.37302461726097</v>
+      </c>
+      <c r="AA53" s="70">
+        <f t="shared" ref="AA53:AJ53" si="88">AA52*AA64</f>
+        <v>1084.8777168190554</v>
+      </c>
       <c r="AB53" s="70">
-        <f>AB52*AB64</f>
-        <v>953.20970736043455</v>
+        <f t="shared" si="88"/>
+        <v>1395.257304657601</v>
       </c>
       <c r="AC53" s="70">
-        <f t="shared" ref="AC53:AL53" si="98">AC52*AC64</f>
-        <v>1111.6727955915039</v>
+        <f t="shared" si="88"/>
+        <v>1765.6234681771616</v>
       </c>
       <c r="AD53" s="70">
-        <f t="shared" si="98"/>
-        <v>1459.6369052229322</v>
+        <f t="shared" si="88"/>
+        <v>2151.8475521641726</v>
       </c>
       <c r="AE53" s="70">
-        <f t="shared" si="98"/>
-        <v>1770.114589282218</v>
+        <f t="shared" si="88"/>
+        <v>2625.1946726160891</v>
       </c>
       <c r="AF53" s="70">
-        <f t="shared" si="98"/>
-        <v>2155.4190046816384</v>
+        <f t="shared" si="88"/>
+        <v>3148.9030313584831</v>
       </c>
       <c r="AG53" s="70">
-        <f t="shared" si="98"/>
-        <v>2627.699201511065</v>
+        <f t="shared" si="88"/>
+        <v>3726.7618367350665</v>
       </c>
       <c r="AH53" s="70">
-        <f t="shared" si="98"/>
-        <v>3150.4167419094074</v>
+        <f t="shared" si="88"/>
+        <v>4270.0309776888744</v>
       </c>
       <c r="AI53" s="70">
-        <f t="shared" si="98"/>
-        <v>3687.8017803133989</v>
+        <f t="shared" si="88"/>
+        <v>4860.1595073829149</v>
       </c>
       <c r="AJ53" s="70">
-        <f t="shared" si="98"/>
-        <v>4203.6718993063005</v>
-      </c>
-      <c r="AK53" s="70">
-        <f t="shared" si="98"/>
-        <v>4762.3225263745717</v>
-      </c>
-      <c r="AL53" s="70">
-        <f t="shared" si="98"/>
-        <v>5344.8528620825391</v>
-      </c>
-    </row>
-    <row r="54" spans="2:90" s="2" customFormat="1" ht="15">
+        <f t="shared" si="88"/>
+        <v>5477.5125246942152</v>
+      </c>
+    </row>
+    <row r="54" spans="2:88" s="2" customFormat="1" ht="15">
       <c r="B54" s="2" t="s">
         <v>80</v>
       </c>
@@ -15179,7 +15176,7 @@
         <v>-96</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" ref="J54" si="99">J52-J53</f>
+        <f t="shared" ref="J54" si="89">J52-J53</f>
         <v>485</v>
       </c>
       <c r="K54" s="2">
@@ -15199,266 +15196,266 @@
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
       <c r="R54" s="34"/>
+      <c r="W54" s="2">
+        <f>W52-W53-14</f>
+        <v>-2736</v>
+      </c>
+      <c r="X54" s="2">
+        <f>SUM(C54:F54)</f>
+        <v>-438</v>
+      </c>
       <c r="Y54" s="2">
-        <f>Y52-Y53-14</f>
-        <v>-2736</v>
-      </c>
-      <c r="Z54" s="2">
-        <f t="shared" si="54"/>
-        <v>-438</v>
-      </c>
-      <c r="AA54" s="2">
-        <f t="shared" si="78"/>
+        <f>SUM(G54:J54)</f>
         <v>1553</v>
       </c>
+      <c r="Z54" s="71">
+        <f>Z52-Z53</f>
+        <v>2894.802586065437</v>
+      </c>
+      <c r="AA54" s="71">
+        <f t="shared" ref="AA54:AJ54" si="90">AA52-AA53</f>
+        <v>3846.3846323584694</v>
+      </c>
       <c r="AB54" s="71">
-        <f>AB52-AB53</f>
-        <v>3103.0018133222657</v>
+        <f t="shared" si="90"/>
+        <v>5248.8250984738333</v>
       </c>
       <c r="AC54" s="71">
-        <f t="shared" ref="AC54:AL54" si="100">AC52-AC53</f>
-        <v>3941.3853661880594</v>
+        <f t="shared" si="90"/>
+        <v>6642.1073326664646</v>
       </c>
       <c r="AD54" s="71">
-        <f t="shared" si="100"/>
-        <v>5491.0150244100787</v>
+        <f t="shared" si="90"/>
+        <v>8095.0455533795066</v>
       </c>
       <c r="AE54" s="71">
-        <f t="shared" si="100"/>
-        <v>6659.0025025378682</v>
+        <f t="shared" si="90"/>
+        <v>9875.7323398414774</v>
       </c>
       <c r="AF54" s="71">
-        <f t="shared" si="100"/>
-        <v>8108.481017611879</v>
+        <f t="shared" si="90"/>
+        <v>11845.873308443817</v>
       </c>
       <c r="AG54" s="71">
-        <f t="shared" si="100"/>
-        <v>9885.1541390178172</v>
+        <f t="shared" si="90"/>
+        <v>14019.723100098585</v>
       </c>
       <c r="AH54" s="71">
-        <f t="shared" si="100"/>
-        <v>11851.567743373485</v>
+        <f t="shared" si="90"/>
+        <v>16063.449868448624</v>
       </c>
       <c r="AI54" s="71">
-        <f t="shared" si="100"/>
-        <v>13873.159078321834</v>
+        <f t="shared" si="90"/>
+        <v>18283.457194440489</v>
       </c>
       <c r="AJ54" s="71">
-        <f t="shared" si="100"/>
-        <v>15813.813335485607</v>
+        <f t="shared" si="90"/>
+        <v>20605.880450040142</v>
       </c>
       <c r="AK54" s="71">
-        <f t="shared" si="100"/>
-        <v>17915.403789694821</v>
+        <f t="shared" ref="AK54:BP54" si="91">AJ54*(1+$AI$70)</f>
+        <v>20966.483357915848</v>
       </c>
       <c r="AL54" s="71">
-        <f t="shared" si="100"/>
-        <v>20106.827433548602</v>
+        <f t="shared" si="91"/>
+        <v>21333.396816679375</v>
       </c>
       <c r="AM54" s="71">
-        <f t="shared" ref="AM54:BR54" si="101">AL54*(1+$AK$70)</f>
-        <v>20458.696913635704</v>
+        <f t="shared" si="91"/>
+        <v>21706.731260971264</v>
       </c>
       <c r="AN54" s="71">
-        <f t="shared" si="101"/>
-        <v>20816.724109624331</v>
+        <f t="shared" si="91"/>
+        <v>22086.599058038264</v>
       </c>
       <c r="AO54" s="71">
-        <f t="shared" si="101"/>
-        <v>21181.016781542759</v>
+        <f t="shared" si="91"/>
+        <v>22473.114541553936</v>
       </c>
       <c r="AP54" s="71">
-        <f t="shared" si="101"/>
-        <v>21551.684575219759</v>
+        <f t="shared" si="91"/>
+        <v>22866.394046031131</v>
       </c>
       <c r="AQ54" s="71">
-        <f t="shared" si="101"/>
-        <v>21928.839055286106</v>
+        <f t="shared" si="91"/>
+        <v>23266.555941836679</v>
       </c>
       <c r="AR54" s="71">
-        <f t="shared" si="101"/>
-        <v>22312.593738753614</v>
+        <f t="shared" si="91"/>
+        <v>23673.720670818824</v>
       </c>
       <c r="AS54" s="71">
-        <f t="shared" si="101"/>
-        <v>22703.064129181803</v>
+        <f t="shared" si="91"/>
+        <v>24088.010782558154</v>
       </c>
       <c r="AT54" s="71">
-        <f t="shared" si="101"/>
-        <v>23100.367751442485</v>
+        <f t="shared" si="91"/>
+        <v>24509.550971252924</v>
       </c>
       <c r="AU54" s="71">
-        <f t="shared" si="101"/>
-        <v>23504.62418709273</v>
+        <f t="shared" si="91"/>
+        <v>24938.468113249852</v>
       </c>
       <c r="AV54" s="71">
-        <f t="shared" si="101"/>
-        <v>23915.955110366853</v>
+        <f t="shared" si="91"/>
+        <v>25374.891305231726</v>
       </c>
       <c r="AW54" s="71">
-        <f t="shared" si="101"/>
-        <v>24334.484324798275</v>
+        <f t="shared" si="91"/>
+        <v>25818.951903073284</v>
       </c>
       <c r="AX54" s="71">
-        <f t="shared" si="101"/>
-        <v>24760.337800482248</v>
+        <f t="shared" si="91"/>
+        <v>26270.783561377069</v>
       </c>
       <c r="AY54" s="71">
-        <f t="shared" si="101"/>
-        <v>25193.643711990688</v>
+        <f t="shared" si="91"/>
+        <v>26730.522273701172</v>
       </c>
       <c r="AZ54" s="71">
-        <f t="shared" si="101"/>
-        <v>25634.532476950528</v>
+        <f t="shared" si="91"/>
+        <v>27198.306413490944</v>
       </c>
       <c r="BA54" s="71">
-        <f t="shared" si="101"/>
-        <v>26083.136795297163</v>
+        <f t="shared" si="91"/>
+        <v>27674.276775727038</v>
       </c>
       <c r="BB54" s="71">
-        <f t="shared" si="101"/>
-        <v>26539.591689214867</v>
+        <f t="shared" si="91"/>
+        <v>28158.576619302261</v>
       </c>
       <c r="BC54" s="71">
-        <f t="shared" si="101"/>
-        <v>27004.034543776128</v>
+        <f t="shared" si="91"/>
+        <v>28651.351710140054</v>
       </c>
       <c r="BD54" s="71">
-        <f t="shared" si="101"/>
-        <v>27476.605148292212</v>
+        <f t="shared" si="91"/>
+        <v>29152.750365067506</v>
       </c>
       <c r="BE54" s="71">
-        <f t="shared" si="101"/>
-        <v>27957.445738387327</v>
+        <f t="shared" si="91"/>
+        <v>29662.923496456191</v>
       </c>
       <c r="BF54" s="71">
-        <f t="shared" si="101"/>
-        <v>28446.701038809108</v>
+        <f t="shared" si="91"/>
+        <v>30182.024657644175</v>
       </c>
       <c r="BG54" s="71">
-        <f t="shared" si="101"/>
-        <v>28944.51830698827</v>
+        <f t="shared" si="91"/>
+        <v>30710.210089152952</v>
       </c>
       <c r="BH54" s="71">
-        <f t="shared" si="101"/>
-        <v>29451.047377360566</v>
+        <f t="shared" si="91"/>
+        <v>31247.638765713131</v>
       </c>
       <c r="BI54" s="71">
-        <f t="shared" si="101"/>
-        <v>29966.440706464378</v>
+        <f t="shared" si="91"/>
+        <v>31794.472444113111</v>
       </c>
       <c r="BJ54" s="71">
-        <f t="shared" si="101"/>
-        <v>30490.853418827508</v>
+        <f t="shared" si="91"/>
+        <v>32350.875711885092</v>
       </c>
       <c r="BK54" s="71">
-        <f t="shared" si="101"/>
-        <v>31024.443353656992</v>
+        <f t="shared" si="91"/>
+        <v>32917.016036843081</v>
       </c>
       <c r="BL54" s="71">
-        <f t="shared" si="101"/>
-        <v>31567.371112345991</v>
+        <f t="shared" si="91"/>
+        <v>33493.06381748784</v>
       </c>
       <c r="BM54" s="71">
-        <f t="shared" si="101"/>
-        <v>32119.800106812047</v>
+        <f t="shared" si="91"/>
+        <v>34079.19243429388</v>
       </c>
       <c r="BN54" s="71">
-        <f t="shared" si="101"/>
-        <v>32681.896608681258</v>
+        <f t="shared" si="91"/>
+        <v>34675.578301894027</v>
       </c>
       <c r="BO54" s="71">
-        <f t="shared" si="101"/>
-        <v>33253.82979933318</v>
+        <f t="shared" si="91"/>
+        <v>35282.400922177178</v>
       </c>
       <c r="BP54" s="71">
-        <f t="shared" si="101"/>
-        <v>33835.771820821516</v>
+        <f t="shared" si="91"/>
+        <v>35899.842938315283</v>
       </c>
       <c r="BQ54" s="71">
-        <f t="shared" si="101"/>
-        <v>34427.897827685898</v>
+        <f t="shared" ref="BQ54:CH54" si="92">BP54*(1+$AI$70)</f>
+        <v>36528.090189735805</v>
       </c>
       <c r="BR54" s="71">
-        <f t="shared" si="101"/>
-        <v>35030.386039670404</v>
+        <f t="shared" si="92"/>
+        <v>37167.331768056181</v>
       </c>
       <c r="BS54" s="71">
-        <f t="shared" ref="BS54:CJ54" si="102">BR54*(1+$AK$70)</f>
-        <v>35643.417795364636</v>
+        <f t="shared" si="92"/>
+        <v>37817.760073997168</v>
       </c>
       <c r="BT54" s="71">
-        <f t="shared" si="102"/>
-        <v>36267.177606783516</v>
+        <f t="shared" si="92"/>
+        <v>38479.57087529212</v>
       </c>
       <c r="BU54" s="71">
-        <f t="shared" si="102"/>
-        <v>36901.853214902229</v>
+        <f t="shared" si="92"/>
+        <v>39152.963365609736</v>
       </c>
       <c r="BV54" s="71">
-        <f t="shared" si="102"/>
-        <v>37547.63564616302</v>
+        <f t="shared" si="92"/>
+        <v>39838.140224507908</v>
       </c>
       <c r="BW54" s="71">
-        <f t="shared" si="102"/>
-        <v>38204.719269970876</v>
+        <f t="shared" si="92"/>
+        <v>40535.307678436802</v>
       </c>
       <c r="BX54" s="71">
-        <f t="shared" si="102"/>
-        <v>38873.301857195365</v>
+        <f t="shared" si="92"/>
+        <v>41244.675562809447</v>
       </c>
       <c r="BY54" s="71">
-        <f t="shared" si="102"/>
-        <v>39553.584639696288</v>
+        <f t="shared" si="92"/>
+        <v>41966.457385158617</v>
       </c>
       <c r="BZ54" s="71">
-        <f t="shared" si="102"/>
-        <v>40245.772370890976</v>
+        <f t="shared" si="92"/>
+        <v>42700.870389398893</v>
       </c>
       <c r="CA54" s="71">
-        <f t="shared" si="102"/>
-        <v>40950.07338738157</v>
+        <f t="shared" si="92"/>
+        <v>43448.135621213376</v>
       </c>
       <c r="CB54" s="71">
-        <f t="shared" si="102"/>
-        <v>41666.699671660754</v>
+        <f t="shared" si="92"/>
+        <v>44208.477994584617</v>
       </c>
       <c r="CC54" s="71">
-        <f t="shared" si="102"/>
-        <v>42395.866915914819</v>
+        <f t="shared" si="92"/>
+        <v>44982.126359489848</v>
       </c>
       <c r="CD54" s="71">
-        <f t="shared" si="102"/>
-        <v>43137.794586943332</v>
+        <f t="shared" si="92"/>
+        <v>45769.313570780927</v>
       </c>
       <c r="CE54" s="71">
-        <f t="shared" si="102"/>
-        <v>43892.70599221484</v>
+        <f t="shared" si="92"/>
+        <v>46570.276558269594</v>
       </c>
       <c r="CF54" s="71">
-        <f t="shared" si="102"/>
-        <v>44660.828347078605</v>
+        <f t="shared" si="92"/>
+        <v>47385.256398039317</v>
       </c>
       <c r="CG54" s="71">
-        <f t="shared" si="102"/>
-        <v>45442.392843152484</v>
+        <f t="shared" si="92"/>
+        <v>48214.498385005005</v>
       </c>
       <c r="CH54" s="71">
-        <f t="shared" si="102"/>
-        <v>46237.634717907655</v>
-      </c>
-      <c r="CI54" s="71">
-        <f t="shared" si="102"/>
-        <v>47046.793325471044</v>
-      </c>
-      <c r="CJ54" s="71">
-        <f t="shared" si="102"/>
-        <v>47870.112208666789</v>
-      </c>
-      <c r="CK54" s="34"/>
-      <c r="CL54" s="34"/>
-    </row>
-    <row r="55" spans="2:90">
+        <f t="shared" si="92"/>
+        <v>49058.252106742599</v>
+      </c>
+      <c r="CI54" s="34"/>
+      <c r="CJ54" s="34"/>
+    </row>
+    <row r="55" spans="2:88">
       <c r="B55" s="1" t="s">
         <v>84</v>
       </c>
@@ -15495,15 +15492,17 @@
       <c r="M55" s="1">
         <v>272</v>
       </c>
+      <c r="W55" s="1">
+        <v>274</v>
+      </c>
+      <c r="X55" s="1">
+        <v>274</v>
+      </c>
       <c r="Y55" s="1">
-        <v>274</v>
-      </c>
-      <c r="Z55" s="1">
-        <v>274</v>
-      </c>
-      <c r="AA55" s="1">
         <v>275</v>
       </c>
+      <c r="Z55" s="70"/>
+      <c r="AA55" s="70"/>
       <c r="AB55" s="70"/>
       <c r="AC55" s="70"/>
       <c r="AD55" s="70"/>
@@ -15513,47 +15512,45 @@
       <c r="AH55" s="70"/>
       <c r="AI55" s="70"/>
       <c r="AJ55" s="70"/>
-      <c r="AK55" s="70"/>
-      <c r="AL55" s="70"/>
-    </row>
-    <row r="56" spans="2:90">
+    </row>
+    <row r="56" spans="2:88">
       <c r="B56" s="1" t="s">
         <v>557</v>
       </c>
       <c r="C56" s="39">
-        <f t="shared" ref="C56" si="103">C54/C55</f>
+        <f t="shared" ref="C56" si="93">C54/C55</f>
         <v>-1.1496350364963503</v>
       </c>
       <c r="D56" s="39">
-        <f t="shared" ref="D56" si="104">D54/D55</f>
+        <f t="shared" ref="D56" si="94">D54/D55</f>
         <v>-0.54744525547445255</v>
       </c>
       <c r="E56" s="39">
-        <f t="shared" ref="E56" si="105">E54/E55</f>
+        <f t="shared" ref="E56" si="95">E54/E55</f>
         <v>-0.62043795620437958</v>
       </c>
       <c r="F56" s="39">
-        <f t="shared" ref="F56" si="106">F54/F55</f>
+        <f t="shared" ref="F56" si="96">F54/F55</f>
         <v>0.71897810218978098</v>
       </c>
       <c r="G56" s="39">
-        <f t="shared" ref="G56:K56" si="107">G54/G55</f>
+        <f t="shared" ref="G56:K56" si="97">G54/G55</f>
         <v>-0.47445255474452552</v>
       </c>
       <c r="H56" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="97"/>
         <v>4.7226277372262775</v>
       </c>
       <c r="I56" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="97"/>
         <v>-0.34909090909090912</v>
       </c>
       <c r="J56" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="97"/>
         <v>1.7636363636363637</v>
       </c>
       <c r="K56" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="97"/>
         <v>0.92363636363636359</v>
       </c>
       <c r="L56" s="39">
@@ -15564,57 +15561,57 @@
         <f>M54/M55</f>
         <v>1.6654411764705883</v>
       </c>
+      <c r="W56" s="39">
+        <f t="shared" ref="W56" si="98">W54/W55</f>
+        <v>-9.985401459854014</v>
+      </c>
+      <c r="X56" s="39">
+        <f>SUM(C56:F56)</f>
+        <v>-1.5985401459854014</v>
+      </c>
       <c r="Y56" s="39">
-        <f t="shared" ref="Y56" si="108">Y54/Y55</f>
-        <v>-9.985401459854014</v>
-      </c>
-      <c r="Z56" s="39">
-        <f t="shared" si="54"/>
-        <v>-1.5985401459854014</v>
-      </c>
-      <c r="AA56" s="39">
-        <f t="shared" si="78"/>
+        <f>SUM(G56:J56)</f>
         <v>5.6627206370272063</v>
       </c>
     </row>
-    <row r="58" spans="2:90">
+    <row r="58" spans="2:88">
       <c r="B58" s="62" t="s">
         <v>558</v>
       </c>
       <c r="C58" s="63">
-        <f t="shared" ref="C58:F58" si="109">1-C42/C39</f>
+        <f t="shared" ref="C58:F58" si="99">1-C42/C39</f>
         <v>-2.4648896531957565E-2</v>
       </c>
       <c r="D58" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v>-5.3099361896080222E-2</v>
       </c>
       <c r="E58" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v>-2.7931813514068704E-2</v>
       </c>
       <c r="F58" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="99"/>
         <v>1.4513788098693414E-3</v>
       </c>
       <c r="G58" s="63">
-        <f t="shared" ref="G58:K58" si="110">1-G42/G39</f>
+        <f t="shared" ref="G58:K58" si="100">1-G42/G39</f>
         <v>-2.1011888305225268E-2</v>
       </c>
       <c r="H58" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="100"/>
         <v>8.1306628516928936E-2</v>
       </c>
       <c r="I58" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="100"/>
         <v>4.0453686200378036E-2</v>
       </c>
       <c r="J58" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="100"/>
         <v>8.2720902409844421E-2</v>
       </c>
       <c r="K58" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="100"/>
         <v>6.7190850607576791E-2</v>
       </c>
       <c r="L58" s="63">
@@ -15625,35 +15622,41 @@
         <f>1-M42/M39</f>
         <v>0.12159863945578231</v>
       </c>
+      <c r="W58" s="63">
+        <f t="shared" ref="W58:Y58" si="101">1-W42/W39</f>
+        <v>-7.2887034578671184E-2</v>
+      </c>
+      <c r="X58" s="63">
+        <f t="shared" si="101"/>
+        <v>-2.4482418665790373E-2</v>
+      </c>
       <c r="Y58" s="63">
-        <f t="shared" ref="Y58:AA58" si="111">1-Y42/Y39</f>
-        <v>-7.2887034578671184E-2</v>
-      </c>
-      <c r="Z58" s="63">
-        <f t="shared" si="111"/>
-        <v>-2.4482418665790373E-2</v>
-      </c>
-      <c r="AA58" s="63">
-        <f t="shared" si="111"/>
+        <f t="shared" si="101"/>
         <v>5.0812579147319514E-2</v>
       </c>
+      <c r="Z58" s="65">
+        <v>0.105</v>
+      </c>
+      <c r="AA58" s="65">
+        <v>0.115</v>
+      </c>
       <c r="AB58" s="65">
-        <v>0.1075</v>
+        <v>0.13</v>
       </c>
       <c r="AC58" s="65">
-        <v>0.12</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="AD58" s="65">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AE58" s="65">
-        <v>0.14499999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="AF58" s="65">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AG58" s="65">
-        <v>0.155</v>
+        <v>0.16</v>
       </c>
       <c r="AH58" s="65">
         <v>0.16</v>
@@ -15664,51 +15667,45 @@
       <c r="AJ58" s="65">
         <v>0.16</v>
       </c>
-      <c r="AK58" s="65">
-        <v>0.16</v>
-      </c>
-      <c r="AL58" s="65">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="59" spans="2:90">
+    </row>
+    <row r="59" spans="2:88">
       <c r="B59" s="62" t="s">
         <v>559</v>
       </c>
       <c r="C59" s="63">
-        <f t="shared" ref="C59:F59" si="112">1-C43/C40</f>
+        <f t="shared" ref="C59:F59" si="102">1-C43/C40</f>
         <v>0.30153015301530151</v>
       </c>
       <c r="D59" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="102"/>
         <v>0.36987402841061379</v>
       </c>
       <c r="E59" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="102"/>
         <v>0.350872007094295</v>
       </c>
       <c r="F59" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="102"/>
         <v>0.37340097044552267</v>
       </c>
       <c r="G59" s="63">
-        <f t="shared" ref="G59:K59" si="113">1-G43/G40</f>
+        <f t="shared" ref="G59:K59" si="103">1-G43/G40</f>
         <v>0.33662822624931354</v>
       </c>
       <c r="H59" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="103"/>
         <v>0.33940149625935168</v>
       </c>
       <c r="I59" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="103"/>
         <v>0.24703284570797679</v>
       </c>
       <c r="J59" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="103"/>
         <v>0.34834324553950724</v>
       </c>
       <c r="K59" s="63">
-        <f t="shared" si="113"/>
+        <f t="shared" si="103"/>
         <v>0.30977835723598435</v>
       </c>
       <c r="L59" s="63">
@@ -15719,32 +15716,38 @@
         <f>1-M43/M40</f>
         <v>0.28931279041330393</v>
       </c>
+      <c r="W59" s="63">
+        <f t="shared" ref="W59:Y59" si="104">1-W43/W40</f>
+        <v>0.33328514636790751</v>
+      </c>
+      <c r="X59" s="63">
+        <f t="shared" si="104"/>
+        <v>0.35144516387424074</v>
+      </c>
       <c r="Y59" s="63">
-        <f t="shared" ref="Y59:AA59" si="114">1-Y43/Y40</f>
-        <v>0.33328514636790751</v>
-      </c>
-      <c r="Z59" s="63">
-        <f t="shared" si="114"/>
-        <v>0.35144516387424074</v>
-      </c>
-      <c r="AA59" s="63">
-        <f t="shared" si="114"/>
+        <f t="shared" si="104"/>
         <v>0.32046549458799978</v>
       </c>
+      <c r="Z59" s="65">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="AA59" s="65">
+        <v>0.32</v>
+      </c>
       <c r="AB59" s="65">
-        <v>0.30499999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="AC59" s="65">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="AD59" s="65">
-        <v>0.35</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="AE59" s="65">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="AF59" s="65">
-        <v>0.36499999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="AG59" s="65">
         <v>0.37</v>
@@ -15758,51 +15761,45 @@
       <c r="AJ59" s="65">
         <v>0.37</v>
       </c>
-      <c r="AK59" s="65">
-        <v>0.37</v>
-      </c>
-      <c r="AL59" s="65">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="60" spans="2:90">
+    </row>
+    <row r="60" spans="2:88">
       <c r="B60" s="37" t="s">
         <v>66</v>
       </c>
       <c r="C60" s="63">
-        <f t="shared" ref="C60:F60" si="115">C45/C41</f>
+        <f t="shared" ref="C60:F60" si="105">C45/C41</f>
         <v>0.13471122837877456</v>
       </c>
       <c r="D60" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="105"/>
         <v>0.14127355585663259</v>
       </c>
       <c r="E60" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="105"/>
         <v>0.12736306349975762</v>
       </c>
       <c r="F60" s="63">
-        <f t="shared" si="115"/>
+        <f t="shared" si="105"/>
         <v>0.16932112283495918</v>
       </c>
       <c r="G60" s="63">
-        <f t="shared" ref="G60:K60" si="116">G45/G41</f>
+        <f t="shared" ref="G60:K60" si="106">G45/G41</f>
         <v>0.15842402534784406</v>
       </c>
       <c r="H60" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="106"/>
         <v>0.20745977571916138</v>
       </c>
       <c r="I60" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="106"/>
         <v>0.12442499719510827</v>
       </c>
       <c r="J60" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="106"/>
         <v>0.20115541244436025</v>
       </c>
       <c r="K60" s="63">
-        <f t="shared" si="116"/>
+        <f t="shared" si="106"/>
         <v>0.18301792828685259</v>
       </c>
       <c r="L60" s="63">
@@ -15813,101 +15810,101 @@
         <f>M45/M41</f>
         <v>0.19039020964991474</v>
       </c>
+      <c r="W60" s="63">
+        <f t="shared" ref="W60:AJ60" si="107">W45/W41</f>
+        <v>0.11661158696971741</v>
+      </c>
+      <c r="X60" s="63">
+        <f t="shared" si="107"/>
+        <v>0.14495020909172959</v>
+      </c>
       <c r="Y60" s="63">
-        <f t="shared" ref="Y60:AL60" si="117">Y45/Y41</f>
-        <v>0.11661158696971741</v>
-      </c>
-      <c r="Z60" s="63">
-        <f t="shared" si="117"/>
-        <v>0.14495020909172959</v>
-      </c>
-      <c r="AA60" s="63">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.17418062115357091</v>
       </c>
+      <c r="Z60" s="65">
+        <f t="shared" si="107"/>
+        <v>0.18825551724986256</v>
+      </c>
+      <c r="AA60" s="65">
+        <f t="shared" si="107"/>
+        <v>0.20020839921117503</v>
+      </c>
       <c r="AB60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.19404191924656772</v>
+        <f t="shared" si="107"/>
+        <v>0.21747906956634092</v>
       </c>
       <c r="AC60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.20313014557187803</v>
+        <f t="shared" si="107"/>
+        <v>0.22673929739213558</v>
       </c>
       <c r="AD60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.22350274822241625</v>
+        <f t="shared" si="107"/>
+        <v>0.23138776055863028</v>
       </c>
       <c r="AE60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.22673929739213558</v>
+        <f t="shared" si="107"/>
+        <v>0.23756449107332558</v>
       </c>
       <c r="AF60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.23138776055863028</v>
+        <f t="shared" si="107"/>
+        <v>0.24378588655650971</v>
       </c>
       <c r="AG60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.23756449107332558</v>
+        <f t="shared" si="107"/>
+        <v>0.24747531664455683</v>
       </c>
       <c r="AH60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.24378588655650971</v>
+        <f t="shared" si="107"/>
+        <v>0.24940734605641088</v>
       </c>
       <c r="AI60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.24747531664455683</v>
+        <f t="shared" si="107"/>
+        <v>0.2513687888212649</v>
       </c>
       <c r="AJ60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.24940734605641088</v>
-      </c>
-      <c r="AK60" s="65">
-        <f t="shared" si="117"/>
-        <v>0.2513687888212649</v>
-      </c>
-      <c r="AL60" s="65">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.25286770146122839</v>
       </c>
     </row>
-    <row r="61" spans="2:90">
+    <row r="61" spans="2:88">
       <c r="B61" s="37" t="s">
         <v>68</v>
       </c>
       <c r="C61" s="63">
-        <f t="shared" ref="C61:F61" si="118">C46/C41</f>
+        <f t="shared" ref="C61:F61" si="108">C46/C41</f>
         <v>0.17384931105247728</v>
       </c>
       <c r="D61" s="63">
-        <f t="shared" si="118"/>
+        <f t="shared" si="108"/>
         <v>0.15666954058381574</v>
       </c>
       <c r="E61" s="63">
-        <f t="shared" si="118"/>
+        <f t="shared" si="108"/>
         <v>0.13754241396025205</v>
       </c>
       <c r="F61" s="63">
-        <f t="shared" si="118"/>
+        <f t="shared" si="108"/>
         <v>0.12462671710133387</v>
       </c>
       <c r="G61" s="63">
-        <f t="shared" ref="G61:K61" si="119">G46/G41</f>
+        <f t="shared" ref="G61:K61" si="109">G46/G41</f>
         <v>0.16558754649400745</v>
       </c>
       <c r="H61" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="109"/>
         <v>0.11433447098976109</v>
       </c>
       <c r="I61" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="109"/>
         <v>0.13755189049702682</v>
       </c>
       <c r="J61" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="109"/>
         <v>0.1198977175868927</v>
       </c>
       <c r="K61" s="63">
-        <f t="shared" si="119"/>
+        <f t="shared" si="109"/>
         <v>0.14790836653386455</v>
       </c>
       <c r="L61" s="63">
@@ -15918,90 +15915,90 @@
         <f>M46/M41</f>
         <v>0.12247968702979235</v>
       </c>
+      <c r="W61" s="63">
+        <f t="shared" ref="W61:Y61" si="110">W46/W41</f>
+        <v>0.18075133202940583</v>
+      </c>
+      <c r="X61" s="63">
+        <f t="shared" si="110"/>
+        <v>0.14576250789734949</v>
+      </c>
       <c r="Y61" s="63">
-        <f t="shared" ref="Y61:AA61" si="120">Y46/Y41</f>
-        <v>0.18075133202940583</v>
-      </c>
-      <c r="Z61" s="63">
-        <f t="shared" si="120"/>
-        <v>0.14576250789734949</v>
-      </c>
-      <c r="AA61" s="63">
-        <f t="shared" si="120"/>
+        <f t="shared" si="110"/>
         <v>0.1325890940317733</v>
       </c>
+      <c r="Z61" s="65">
+        <v>0.1325890940317733</v>
+      </c>
+      <c r="AA61" s="65">
+        <v>0.13</v>
+      </c>
       <c r="AB61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.129</v>
       </c>
       <c r="AC61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.128</v>
       </c>
       <c r="AD61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.127</v>
       </c>
       <c r="AE61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.126</v>
       </c>
       <c r="AF61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.125</v>
       </c>
       <c r="AG61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.125</v>
       </c>
       <c r="AH61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.125</v>
       </c>
       <c r="AI61" s="65">
-        <v>0.1325890940317733</v>
+        <v>0.125</v>
       </c>
       <c r="AJ61" s="65">
-        <v>0.1325890940317733</v>
-      </c>
-      <c r="AK61" s="65">
-        <v>0.1325890940317733</v>
-      </c>
-      <c r="AL61" s="65">
-        <v>0.1325890940317733</v>
-      </c>
-    </row>
-    <row r="62" spans="2:90">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="62" spans="2:88">
       <c r="B62" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="63">
-        <f t="shared" ref="C62:F62" si="121">C47/C41</f>
+        <f t="shared" ref="C62:F62" si="111">C47/C41</f>
         <v>2.9610085019055994E-2</v>
       </c>
       <c r="D62" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="111"/>
         <v>2.6604261608572485E-2</v>
       </c>
       <c r="E62" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="111"/>
         <v>2.7023751817741155E-2</v>
       </c>
       <c r="F62" s="63">
-        <f t="shared" si="121"/>
+        <f t="shared" si="111"/>
         <v>2.5383237109297234E-2</v>
       </c>
       <c r="G62" s="63">
-        <f t="shared" ref="G62:K62" si="122">G47/G41</f>
+        <f t="shared" ref="G62:K62" si="112">G47/G41</f>
         <v>3.2649125223860036E-2</v>
       </c>
       <c r="H62" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="112"/>
         <v>2.8888347147732814E-2</v>
       </c>
       <c r="I62" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="112"/>
         <v>2.7151351957814429E-2</v>
       </c>
       <c r="J62" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="112"/>
         <v>2.5191779524576192E-2</v>
       </c>
       <c r="K62" s="63">
-        <f t="shared" si="122"/>
+        <f t="shared" si="112"/>
         <v>2.9755976095617531E-2</v>
       </c>
       <c r="L62" s="63">
@@ -16012,90 +16009,90 @@
         <f>M47/M41</f>
         <v>3.1096398836392817E-2</v>
       </c>
+      <c r="W62" s="63">
+        <f t="shared" ref="W62:Y62" si="113">W47/W41</f>
+        <v>3.3014095906117216E-2</v>
+      </c>
+      <c r="X62" s="63">
+        <f t="shared" si="113"/>
+        <v>2.6956286290201269E-2</v>
+      </c>
       <c r="Y62" s="63">
-        <f t="shared" ref="Y62:AA62" si="123">Y47/Y41</f>
-        <v>3.3014095906117216E-2</v>
-      </c>
-      <c r="Z62" s="63">
-        <f t="shared" si="123"/>
-        <v>2.6956286290201269E-2</v>
-      </c>
-      <c r="AA62" s="63">
-        <f t="shared" si="123"/>
+        <f t="shared" si="113"/>
         <v>2.8109345928152282E-2</v>
       </c>
+      <c r="Z62" s="65">
+        <v>2.8109345928152282E-2</v>
+      </c>
+      <c r="AA62" s="65">
+        <v>0.03</v>
+      </c>
       <c r="AB62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="AC62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="AD62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="AE62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="AF62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="AG62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="AH62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="AI62" s="65">
-        <v>2.8109345928152282E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="AJ62" s="65">
-        <v>2.8109345928152282E-2</v>
-      </c>
-      <c r="AK62" s="65">
-        <v>2.8109345928152282E-2</v>
-      </c>
-      <c r="AL62" s="65">
-        <v>2.8109345928152282E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="2:90">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="63" spans="2:88">
       <c r="B63" s="37" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="63">
-        <f t="shared" ref="C63:F63" si="124">C48/C41</f>
+        <f t="shared" ref="C63:F63" si="114">C48/C41</f>
         <v>-6.8748167692758724E-2</v>
       </c>
       <c r="D63" s="63">
-        <f t="shared" si="124"/>
+        <f t="shared" si="114"/>
         <v>-4.2000246335755637E-2</v>
       </c>
       <c r="E63" s="63">
-        <f t="shared" si="124"/>
+        <f t="shared" si="114"/>
         <v>-3.7203102278235582E-2</v>
       </c>
       <c r="F63" s="63">
-        <f t="shared" si="124"/>
+        <f t="shared" si="114"/>
         <v>1.9311168624328089E-2</v>
       </c>
       <c r="G63" s="63">
-        <f t="shared" ref="G63:K63" si="125">G48/G41</f>
+        <f t="shared" ref="G63:K63" si="115">G48/G41</f>
         <v>-3.9812646370023422E-2</v>
       </c>
       <c r="H63" s="63">
-        <f t="shared" si="125"/>
+        <f t="shared" si="115"/>
         <v>6.4236957581667475E-2</v>
       </c>
       <c r="I63" s="63">
-        <f t="shared" si="125"/>
+        <f t="shared" si="115"/>
         <v>-4.0278245259732975E-2</v>
       </c>
       <c r="J63" s="63">
-        <f t="shared" si="125"/>
+        <f t="shared" si="115"/>
         <v>5.6065915332891375E-2</v>
       </c>
       <c r="K63" s="63">
-        <f t="shared" si="125"/>
+        <f t="shared" si="115"/>
         <v>5.3535856573705175E-3</v>
       </c>
       <c r="L63" s="63">
@@ -16106,101 +16103,101 @@
         <f>M48/M41</f>
         <v>3.6814123783729565E-2</v>
       </c>
+      <c r="W63" s="63">
+        <f t="shared" ref="W63:Y63" si="116">W48/W41</f>
+        <v>-9.7153840965805621E-2</v>
+      </c>
+      <c r="X63" s="63">
+        <f t="shared" si="116"/>
+        <v>-2.7768585095821172E-2</v>
+      </c>
       <c r="Y63" s="63">
-        <f t="shared" ref="Y63:AA63" si="126">Y48/Y41</f>
-        <v>-9.7153840965805621E-2</v>
-      </c>
-      <c r="Z63" s="63">
-        <f t="shared" si="126"/>
-        <v>-2.7768585095821172E-2</v>
-      </c>
-      <c r="AA63" s="63">
-        <f t="shared" si="126"/>
+        <f t="shared" si="116"/>
         <v>1.3482181193645342E-2</v>
       </c>
+      <c r="Z63" s="65">
+        <f>Z48/Z41</f>
+        <v>2.7557077289936959E-2</v>
+      </c>
+      <c r="AA63" s="65">
+        <f t="shared" ref="AA63:AJ63" si="117">AA48/AA41</f>
+        <v>4.0208399211175028E-2</v>
+      </c>
       <c r="AB63" s="65">
-        <f>AB48/AB41</f>
-        <v>3.3343479286642122E-2</v>
+        <f t="shared" si="117"/>
+        <v>5.7479069566340912E-2</v>
       </c>
       <c r="AC63" s="65">
-        <f t="shared" ref="AC63:AL63" si="127">AC48/AC41</f>
-        <v>4.2431705611952454E-2</v>
+        <f t="shared" si="117"/>
+        <v>6.6739297392135563E-2</v>
       </c>
       <c r="AD63" s="65">
-        <f t="shared" si="127"/>
-        <v>6.2804308262490685E-2</v>
+        <f t="shared" si="117"/>
+        <v>7.1387760558630275E-2</v>
       </c>
       <c r="AE63" s="65">
-        <f t="shared" si="127"/>
-        <v>6.6040857432209998E-2</v>
+        <f t="shared" si="117"/>
+        <v>7.7564491073325595E-2</v>
       </c>
       <c r="AF63" s="65">
-        <f t="shared" si="127"/>
-        <v>7.0689320598704711E-2</v>
+        <f t="shared" si="117"/>
+        <v>8.3785886556509689E-2</v>
       </c>
       <c r="AG63" s="65">
-        <f t="shared" si="127"/>
-        <v>7.6866051113400002E-2</v>
+        <f t="shared" si="117"/>
+        <v>8.9475316644556824E-2</v>
       </c>
       <c r="AH63" s="65">
-        <f t="shared" si="127"/>
-        <v>8.3087446596584097E-2</v>
+        <f t="shared" si="117"/>
+        <v>9.2407346056410891E-2</v>
       </c>
       <c r="AI63" s="65">
-        <f t="shared" si="127"/>
-        <v>8.6776876684631243E-2</v>
+        <f t="shared" si="117"/>
+        <v>9.5368788821264913E-2</v>
       </c>
       <c r="AJ63" s="65">
-        <f t="shared" si="127"/>
-        <v>8.870890609648531E-2</v>
-      </c>
-      <c r="AK63" s="65">
-        <f t="shared" si="127"/>
-        <v>9.0670348861339317E-2</v>
-      </c>
-      <c r="AL63" s="65">
-        <f t="shared" si="127"/>
-        <v>9.2169261501302835E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:90">
+        <f t="shared" si="117"/>
+        <v>9.786770146122839E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:88">
       <c r="B64" s="37" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="63">
-        <f t="shared" ref="C64:F64" si="128">C53/C52</f>
+        <f t="shared" ref="C64:F64" si="118">C53/C52</f>
         <v>0.16626506024096385</v>
       </c>
       <c r="D64" s="63">
-        <f t="shared" si="128"/>
+        <f t="shared" si="118"/>
         <v>-4.5185185185185182</v>
       </c>
       <c r="E64" s="67">
-        <f t="shared" si="128"/>
+        <f t="shared" si="118"/>
         <v>-10.5625</v>
       </c>
       <c r="F64" s="63">
-        <f t="shared" si="128"/>
+        <f t="shared" si="118"/>
         <v>0.37195121951219512</v>
       </c>
       <c r="G64" s="63">
-        <f t="shared" ref="G64:K64" si="129">G53/G52</f>
+        <f t="shared" ref="G64:K64" si="119">G53/G52</f>
         <v>-0.10416666666666667</v>
       </c>
       <c r="H64" s="63">
-        <f t="shared" si="129"/>
+        <f t="shared" si="119"/>
         <v>0.2009987515605493</v>
       </c>
       <c r="I64" s="63">
-        <f t="shared" si="129"/>
+        <f t="shared" si="119"/>
         <v>0.18852459016393441</v>
       </c>
       <c r="J64" s="63">
-        <f t="shared" si="129"/>
+        <f t="shared" si="119"/>
         <v>0.56502242152466364</v>
       </c>
       <c r="K64" s="63">
-        <f t="shared" si="129"/>
+        <f t="shared" si="119"/>
         <v>0.20481927710843373</v>
       </c>
       <c r="L64" s="63">
@@ -16211,23 +16208,29 @@
         <f>M53/M52</f>
         <v>0.39223560910307897</v>
       </c>
+      <c r="W64" s="63">
+        <f t="shared" ref="W64:Y64" si="120">W53/W52</f>
+        <v>-0.10024252223120453</v>
+      </c>
+      <c r="X64" s="63">
+        <f t="shared" si="120"/>
+        <v>-2.6461538461538461</v>
+      </c>
       <c r="Y64" s="63">
-        <f t="shared" ref="Y64:AA64" si="130">Y53/Y52</f>
-        <v>-0.10024252223120453</v>
-      </c>
-      <c r="Z64" s="63">
-        <f t="shared" si="130"/>
-        <v>-2.6461538461538461</v>
-      </c>
-      <c r="AA64" s="63">
-        <f t="shared" si="130"/>
+        <f t="shared" si="120"/>
         <v>0.37575030012004801</v>
       </c>
+      <c r="Z64" s="65">
+        <v>0.245</v>
+      </c>
+      <c r="AA64" s="65">
+        <v>0.22</v>
+      </c>
       <c r="AB64" s="65">
-        <v>0.23499999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="AC64" s="65">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AD64" s="65">
         <v>0.21</v>
@@ -16250,51 +16253,45 @@
       <c r="AJ64" s="65">
         <v>0.21</v>
       </c>
-      <c r="AK64" s="65">
-        <v>0.21</v>
-      </c>
-      <c r="AL64" s="65">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="65" spans="2:90">
+    </row>
+    <row r="65" spans="2:88">
       <c r="B65" s="37" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="63">
-        <f t="shared" ref="C65:F65" si="131">C54/C41</f>
+        <f t="shared" ref="C65:F65" si="121">C54/C41</f>
         <v>-4.6174142480211081E-2</v>
       </c>
       <c r="D65" s="63">
-        <f t="shared" si="131"/>
+        <f t="shared" si="121"/>
         <v>-1.847518167261978E-2</v>
       </c>
       <c r="E65" s="63">
-        <f t="shared" si="131"/>
+        <f t="shared" si="121"/>
         <v>-2.0601066408143482E-2</v>
       </c>
       <c r="F65" s="63">
-        <f t="shared" si="131"/>
+        <f t="shared" si="121"/>
         <v>1.9609794943261E-2</v>
       </c>
       <c r="G65" s="63">
-        <f t="shared" ref="G65:K65" si="132">G54/G41</f>
+        <f t="shared" ref="G65:K65" si="122">G54/G41</f>
         <v>-1.7908802865408458E-2</v>
       </c>
       <c r="H65" s="63">
-        <f t="shared" si="132"/>
+        <f t="shared" si="122"/>
         <v>0.15772793759141882</v>
       </c>
       <c r="I65" s="63">
-        <f t="shared" si="132"/>
+        <f t="shared" si="122"/>
         <v>-1.0770784247728038E-2</v>
       </c>
       <c r="J65" s="63">
-        <f t="shared" si="132"/>
+        <f t="shared" si="122"/>
         <v>4.5932379960223507E-2</v>
       </c>
       <c r="K65" s="63">
-        <f t="shared" si="132"/>
+        <f t="shared" si="122"/>
         <v>3.1623505976095617E-2</v>
       </c>
       <c r="L65" s="63">
@@ -16305,16 +16302,22 @@
         <f>M54/M41</f>
         <v>4.5440866686728858E-2</v>
       </c>
+      <c r="W65" s="63">
+        <f t="shared" ref="W65:Y65" si="123">W54/W41</f>
+        <v>-9.226411276724894E-2</v>
+      </c>
+      <c r="X65" s="63">
+        <f t="shared" si="123"/>
+        <v>-1.3177291735611781E-2</v>
+      </c>
       <c r="Y65" s="63">
-        <f t="shared" ref="Y65:AA65" si="133">Y54/Y41</f>
-        <v>-9.226411276724894E-2</v>
-      </c>
-      <c r="Z65" s="63">
-        <f t="shared" si="133"/>
-        <v>-1.3177291735611781E-2</v>
-      </c>
-      <c r="AA65" s="63">
-        <f t="shared" si="133"/>
+        <f t="shared" si="123"/>
+        <v>4.4453985973951622E-2</v>
+      </c>
+      <c r="Z65" s="65">
+        <v>4.4453985973951622E-2</v>
+      </c>
+      <c r="AA65" s="65">
         <v>4.4453985973951622E-2</v>
       </c>
       <c r="AB65" s="65">
@@ -16344,14 +16347,8 @@
       <c r="AJ65" s="65">
         <v>4.4453985973951622E-2</v>
       </c>
-      <c r="AK65" s="65">
-        <v>4.4453985973951622E-2</v>
-      </c>
-      <c r="AL65" s="65">
-        <v>4.4453985973951622E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:90">
+    </row>
+    <row r="67" spans="2:88">
       <c r="B67" s="1" t="s">
         <v>72</v>
       </c>
@@ -16379,60 +16376,60 @@
       <c r="M67" s="1">
         <v>7945</v>
       </c>
-      <c r="Z67" s="1">
+      <c r="X67" s="1">
         <f>F67</f>
         <v>1551</v>
       </c>
-      <c r="AA67" s="1">
+      <c r="Y67" s="1">
         <f>J67</f>
         <v>8205</v>
       </c>
+      <c r="Z67" s="70">
+        <f>Y67+Z54</f>
+        <v>11099.802586065438</v>
+      </c>
+      <c r="AA67" s="70">
+        <f t="shared" ref="AA67:AJ67" si="124">Z67+AA54</f>
+        <v>14946.187218423907</v>
+      </c>
       <c r="AB67" s="70">
-        <f>AA67+AB54</f>
-        <v>11308.001813322266</v>
+        <f t="shared" si="124"/>
+        <v>20195.012316897741</v>
       </c>
       <c r="AC67" s="70">
-        <f t="shared" ref="AC67:AL67" si="134">AB67+AC54</f>
-        <v>15249.387179510326</v>
+        <f t="shared" si="124"/>
+        <v>26837.119649564207</v>
       </c>
       <c r="AD67" s="70">
-        <f t="shared" si="134"/>
-        <v>20740.402203920406</v>
+        <f t="shared" si="124"/>
+        <v>34932.16520294371</v>
       </c>
       <c r="AE67" s="70">
-        <f t="shared" si="134"/>
-        <v>27399.404706458274</v>
+        <f t="shared" si="124"/>
+        <v>44807.897542785184</v>
       </c>
       <c r="AF67" s="70">
-        <f t="shared" si="134"/>
-        <v>35507.885724070155</v>
+        <f t="shared" si="124"/>
+        <v>56653.770851228997</v>
       </c>
       <c r="AG67" s="70">
-        <f t="shared" si="134"/>
-        <v>45393.039863087972</v>
+        <f t="shared" si="124"/>
+        <v>70673.493951327575</v>
       </c>
       <c r="AH67" s="70">
-        <f t="shared" si="134"/>
-        <v>57244.607606461461</v>
+        <f t="shared" si="124"/>
+        <v>86736.943819776207</v>
       </c>
       <c r="AI67" s="70">
-        <f t="shared" si="134"/>
-        <v>71117.766684783302</v>
+        <f t="shared" si="124"/>
+        <v>105020.4010142167</v>
       </c>
       <c r="AJ67" s="70">
-        <f t="shared" si="134"/>
-        <v>86931.580020268913</v>
-      </c>
-      <c r="AK67" s="70">
-        <f t="shared" si="134"/>
-        <v>104846.98380996374</v>
-      </c>
-      <c r="AL67" s="70">
-        <f t="shared" si="134"/>
-        <v>124953.81124351235</v>
-      </c>
-    </row>
-    <row r="68" spans="2:90">
+        <f t="shared" si="124"/>
+        <v>125626.28146425684</v>
+      </c>
+    </row>
+    <row r="68" spans="2:88">
       <c r="B68" s="1" t="s">
         <v>560</v>
       </c>
@@ -16462,16 +16459,16 @@
       <c r="M68" s="1">
         <v>7374</v>
       </c>
-      <c r="Z68" s="1">
-        <f t="shared" ref="Z68:Z80" si="135">F68</f>
+      <c r="X68" s="1">
+        <f>F68</f>
         <v>7489</v>
       </c>
-      <c r="AA68" s="1">
-        <f t="shared" ref="AA68:AA80" si="136">J68</f>
+      <c r="Y68" s="1">
+        <f>J68</f>
         <v>8177</v>
       </c>
     </row>
-    <row r="69" spans="2:90">
+    <row r="69" spans="2:88">
       <c r="B69" s="1" t="s">
         <v>561</v>
       </c>
@@ -16499,36 +16496,36 @@
       <c r="M69" s="1">
         <v>10032</v>
       </c>
-      <c r="Z69" s="1">
-        <f t="shared" si="135"/>
+      <c r="X69" s="1">
+        <f>F69</f>
         <v>8253</v>
       </c>
-      <c r="AA69" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y69" s="1">
+        <f>J69</f>
         <v>8587</v>
       </c>
-      <c r="AC69" s="45" t="s">
+      <c r="AA69" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="AD69" s="46"/>
+      <c r="AB69" s="46"/>
+      <c r="AC69" s="46"/>
+      <c r="AD69" s="45" t="s">
+        <v>118</v>
+      </c>
       <c r="AE69" s="46"/>
-      <c r="AF69" s="45" t="s">
-        <v>118</v>
+      <c r="AF69" s="47" t="s">
+        <v>119</v>
       </c>
       <c r="AG69" s="46"/>
-      <c r="AH69" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI69" s="46"/>
-      <c r="AJ69" s="48" t="s">
+      <c r="AH69" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="AK69" s="49">
+      <c r="AI69" s="49">
         <v>0.115</v>
       </c>
-      <c r="AL69" s="46"/>
-    </row>
-    <row r="70" spans="2:90">
+      <c r="AJ69" s="46"/>
+    </row>
+    <row r="70" spans="2:88">
       <c r="B70" s="1" t="s">
         <v>562</v>
       </c>
@@ -16556,38 +16553,38 @@
       <c r="M70" s="1">
         <v>9485</v>
       </c>
-      <c r="Z70" s="1">
-        <f t="shared" si="135"/>
+      <c r="X70" s="1">
+        <f>F70</f>
         <v>8339</v>
       </c>
-      <c r="AA70" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y70" s="1">
+        <f>J70</f>
         <v>8621</v>
       </c>
+      <c r="AA70" s="46">
+        <v>2025</v>
+      </c>
+      <c r="AB70" s="46"/>
       <c r="AC70" s="46">
-        <v>2025</v>
-      </c>
-      <c r="AD70" s="46"/>
-      <c r="AE70" s="46">
         <v>2023</v>
       </c>
-      <c r="AF70" s="46">
+      <c r="AD70" s="46">
         <v>2024</v>
       </c>
+      <c r="AE70" s="46"/>
+      <c r="AF70" s="47" t="s">
+        <v>121</v>
+      </c>
       <c r="AG70" s="46"/>
-      <c r="AH70" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI70" s="46"/>
-      <c r="AJ70" s="48" t="s">
+      <c r="AH70" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="AK70" s="49">
+      <c r="AI70" s="49">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="AL70" s="46"/>
-    </row>
-    <row r="71" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AJ70" s="46"/>
+    </row>
+    <row r="71" spans="2:88" ht="14.25" customHeight="1">
       <c r="B71" s="1" t="s">
         <v>563</v>
       </c>
@@ -16615,42 +16612,42 @@
       <c r="M71" s="1">
         <v>934</v>
       </c>
-      <c r="Z71" s="1">
-        <f t="shared" si="135"/>
+      <c r="X71" s="1">
+        <f>F71</f>
         <v>352</v>
       </c>
-      <c r="AA71" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y71" s="1">
+        <f>J71</f>
         <v>564</v>
       </c>
-      <c r="AC71" s="50">
-        <f>AVERAGE(AB48)*(1-AB64)</f>
-        <v>978.78423832226565</v>
-      </c>
-      <c r="AD71" s="46"/>
-      <c r="AE71" s="51">
-        <f>SUM(Z67:Z72)-Z82+Z73+Z75+Z74</f>
+      <c r="AA71" s="50">
+        <f>AVERAGE(Z48)*(1-Z64)</f>
+        <v>798.35256106543682</v>
+      </c>
+      <c r="AB71" s="46"/>
+      <c r="AC71" s="51">
+        <f>SUM(X67:X72)-X82+X73+X75+X74</f>
         <v>30235</v>
       </c>
+      <c r="AD71" s="51">
+        <f>SUM(Y67:Y72)-Y82+Y73+Y75+Y74</f>
+        <v>35778</v>
+      </c>
+      <c r="AE71" s="46"/>
       <c r="AF71" s="51">
-        <f>SUM(AA67:AA72)-AA82+AA73+AA75+AA74</f>
-        <v>35778</v>
+        <f>AVERAGE(AC71:AD71)</f>
+        <v>33006.5</v>
       </c>
       <c r="AG71" s="46"/>
-      <c r="AH71" s="51">
-        <f>AVERAGE(AE71:AF71)</f>
-        <v>33006.5</v>
-      </c>
-      <c r="AI71" s="46"/>
-      <c r="AJ71" s="48" t="s">
+      <c r="AH71" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="AK71" s="49">
+      <c r="AI71" s="49">
         <v>4.1099999999999998E-2</v>
       </c>
-      <c r="AL71" s="46"/>
-    </row>
-    <row r="72" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AJ71" s="46"/>
+    </row>
+    <row r="72" spans="2:88" ht="14.25" customHeight="1">
       <c r="B72" s="1" t="s">
         <v>580</v>
       </c>
@@ -16678,34 +16675,34 @@
       <c r="M72" s="1">
         <v>508</v>
       </c>
-      <c r="Z72" s="1">
-        <f t="shared" si="135"/>
+      <c r="X72" s="1">
+        <f>F72</f>
         <v>1444</v>
       </c>
-      <c r="AA72" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y72" s="1">
+        <f>J72</f>
         <v>0</v>
       </c>
-      <c r="AC72" s="52">
-        <f>AC71/AH71</f>
-        <v>2.9654287437997535E-2</v>
-      </c>
-      <c r="AD72" s="46"/>
-      <c r="AE72" s="51"/>
+      <c r="AA72" s="52">
+        <f>AA71/AF71</f>
+        <v>2.4187737599122499E-2</v>
+      </c>
+      <c r="AB72" s="46"/>
+      <c r="AC72" s="51"/>
+      <c r="AD72" s="51"/>
+      <c r="AE72" s="46"/>
       <c r="AF72" s="51"/>
       <c r="AG72" s="46"/>
-      <c r="AH72" s="51"/>
-      <c r="AI72" s="46"/>
-      <c r="AJ72" s="48" t="s">
+      <c r="AH72" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="AK72" s="49">
-        <f>6.95%-AK71</f>
+      <c r="AI72" s="49">
+        <f>6.95%-AI71</f>
         <v>2.8400000000000009E-2</v>
       </c>
-      <c r="AL72" s="46"/>
-    </row>
-    <row r="73" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AJ72" s="46"/>
+    </row>
+    <row r="73" spans="2:88" ht="14.25" customHeight="1">
       <c r="B73" s="1" t="s">
         <v>564</v>
       </c>
@@ -16733,30 +16730,30 @@
       <c r="M73" s="1">
         <v>5555</v>
       </c>
-      <c r="Z73" s="1">
-        <f t="shared" si="135"/>
+      <c r="X73" s="1">
+        <f>F73</f>
         <v>5228</v>
       </c>
-      <c r="AA73" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y73" s="1">
+        <f>J73</f>
         <v>5150</v>
       </c>
+      <c r="AB73" s="46"/>
+      <c r="AC73" s="46"/>
       <c r="AD73" s="46"/>
       <c r="AE73" s="46"/>
       <c r="AF73" s="46"/>
       <c r="AG73" s="46"/>
-      <c r="AH73" s="46"/>
-      <c r="AI73" s="46"/>
-      <c r="AJ73" s="48" t="s">
+      <c r="AH73" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="AK73" s="46">
+      <c r="AI73" s="46">
         <f>'Notes | Quant Analysis'!K204</f>
         <v>1.59</v>
       </c>
-      <c r="AL73" s="46"/>
-    </row>
-    <row r="74" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AJ73" s="46"/>
+    </row>
+    <row r="74" spans="2:88" ht="14.25" customHeight="1">
       <c r="B74" s="1" t="s">
         <v>565</v>
       </c>
@@ -16784,31 +16781,31 @@
       <c r="M74" s="1">
         <v>4327</v>
       </c>
-      <c r="Z74" s="1">
-        <f t="shared" si="135"/>
+      <c r="X74" s="1">
+        <f>F74</f>
         <v>4437</v>
       </c>
-      <c r="AA74" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y74" s="1">
+        <f>J74</f>
         <v>4263</v>
       </c>
+      <c r="AA74" s="46"/>
+      <c r="AB74" s="46"/>
       <c r="AC74" s="46"/>
       <c r="AD74" s="46"/>
       <c r="AE74" s="46"/>
       <c r="AF74" s="46"/>
       <c r="AG74" s="46"/>
-      <c r="AH74" s="46"/>
-      <c r="AI74" s="46"/>
-      <c r="AJ74" s="48" t="s">
+      <c r="AH74" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="AK74" s="49">
-        <f>+AK71+(AK72*AK73)</f>
+      <c r="AI74" s="49">
+        <f>+AI71+(AI72*AI73)</f>
         <v>8.6256000000000013E-2</v>
       </c>
-      <c r="AL74" s="53"/>
-    </row>
-    <row r="75" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AJ74" s="53"/>
+    </row>
+    <row r="75" spans="2:88" ht="14.25" customHeight="1">
       <c r="B75" s="1" t="s">
         <v>566</v>
       </c>
@@ -16836,23 +16833,23 @@
       <c r="M75" s="1">
         <v>747</v>
       </c>
-      <c r="Z75" s="1">
-        <f t="shared" si="135"/>
+      <c r="X75" s="1">
+        <f>F75</f>
         <v>1042</v>
       </c>
-      <c r="AA75" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y75" s="1">
+        <f>J75</f>
         <v>813</v>
       </c>
+      <c r="AA75" s="46"/>
+      <c r="AB75" s="46"/>
       <c r="AC75" s="46"/>
       <c r="AD75" s="46"/>
       <c r="AE75" s="46"/>
       <c r="AF75" s="46"/>
       <c r="AG75" s="46"/>
-      <c r="AH75" s="46"/>
-      <c r="AI75" s="46"/>
-    </row>
-    <row r="76" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="76" spans="2:88" ht="14.25" customHeight="1">
       <c r="B76" s="1" t="s">
         <v>567</v>
       </c>
@@ -16880,31 +16877,31 @@
       <c r="M76" s="1">
         <v>486</v>
       </c>
-      <c r="Z76" s="1">
-        <f t="shared" si="135"/>
+      <c r="X76" s="1">
+        <f>F76</f>
         <v>621</v>
       </c>
-      <c r="AA76" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y76" s="1">
+        <f>J76</f>
         <v>555</v>
       </c>
+      <c r="AA76" s="53"/>
+      <c r="AB76" s="53"/>
       <c r="AC76" s="53"/>
       <c r="AD76" s="53"/>
       <c r="AE76" s="53"/>
       <c r="AF76" s="53"/>
       <c r="AG76" s="53"/>
-      <c r="AH76" s="53"/>
-      <c r="AI76" s="53"/>
-      <c r="AJ76" s="48" t="s">
+      <c r="AH76" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="AK76" s="50">
-        <f>NPV(AK74,AB54:CJ54)</f>
-        <v>179081.73830516095</v>
-      </c>
-      <c r="AL76" s="46"/>
-    </row>
-    <row r="77" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AI76" s="50">
+        <f>NPV(AI74,Z54:CH54)</f>
+        <v>182006.01775187306</v>
+      </c>
+      <c r="AJ76" s="46"/>
+    </row>
+    <row r="77" spans="2:88" ht="14.25" customHeight="1">
       <c r="B77" s="1" t="s">
         <v>568</v>
       </c>
@@ -16932,33 +16929,33 @@
       <c r="M77" s="1">
         <v>1916</v>
       </c>
-      <c r="Z77" s="1">
-        <f t="shared" si="135"/>
+      <c r="X77" s="1">
+        <f>F77</f>
         <v>3555</v>
       </c>
-      <c r="AA77" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y77" s="1">
+        <f>J77</f>
         <v>2149</v>
       </c>
+      <c r="AA77" s="46"/>
+      <c r="AB77" s="46"/>
       <c r="AC77" s="46"/>
       <c r="AD77" s="46"/>
       <c r="AE77" s="46"/>
       <c r="AF77" s="46"/>
       <c r="AG77" s="46"/>
-      <c r="AH77" s="46"/>
-      <c r="AI77" s="46"/>
-      <c r="AJ77" s="48" t="s">
+      <c r="AH77" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="AK77" s="51">
+      <c r="AI77" s="51">
         <f>Main!C4</f>
         <v>271.32</v>
       </c>
-      <c r="AL77" s="54" t="s">
+      <c r="AJ77" s="54" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="78" spans="2:90" ht="14.25" customHeight="1">
+    <row r="78" spans="2:88" ht="14.25" customHeight="1">
       <c r="B78" s="1" t="s">
         <v>569</v>
       </c>
@@ -16986,31 +16983,31 @@
       <c r="M78" s="1">
         <v>1684</v>
       </c>
-      <c r="Z78" s="1">
-        <f t="shared" si="135"/>
+      <c r="X78" s="1">
+        <f>F78</f>
         <v>1582</v>
       </c>
-      <c r="AA78" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y78" s="1">
+        <f>J78</f>
         <v>1639</v>
       </c>
+      <c r="AA78" s="46"/>
+      <c r="AB78" s="46"/>
       <c r="AC78" s="46"/>
       <c r="AD78" s="46"/>
       <c r="AE78" s="46"/>
       <c r="AF78" s="46"/>
       <c r="AG78" s="46"/>
-      <c r="AH78" s="46"/>
-      <c r="AI78" s="46"/>
-      <c r="AJ78" s="48" t="s">
+      <c r="AH78" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="AK78" s="55">
-        <f>AK76/AK77</f>
-        <v>660.03884087115193</v>
-      </c>
-      <c r="AL78" s="45"/>
-    </row>
-    <row r="79" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AI78" s="55">
+        <f>AI76/AI77</f>
+        <v>670.81681317954099</v>
+      </c>
+      <c r="AJ78" s="45"/>
+    </row>
+    <row r="79" spans="2:88" ht="14.25" customHeight="1">
       <c r="B79" s="1" t="s">
         <v>570</v>
       </c>
@@ -17038,56 +17035,56 @@
       <c r="M79" s="1">
         <v>3406</v>
       </c>
-      <c r="Z79" s="1">
-        <f t="shared" si="135"/>
+      <c r="X79" s="1">
+        <f>F79</f>
         <v>2228</v>
       </c>
-      <c r="AA79" s="1">
-        <f t="shared" si="136"/>
+      <c r="Y79" s="1">
+        <f>J79</f>
         <v>2762</v>
       </c>
+      <c r="AA79" s="46"/>
+      <c r="AB79" s="46"/>
       <c r="AC79" s="46"/>
       <c r="AD79" s="46"/>
       <c r="AE79" s="46"/>
       <c r="AF79" s="46"/>
       <c r="AG79" s="46"/>
-      <c r="AH79" s="46"/>
-      <c r="AI79" s="46"/>
-      <c r="AJ79" s="48" t="s">
+      <c r="AH79" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="AK79" s="55">
+      <c r="AI79" s="55">
         <f>Main!C3</f>
-        <v>663.16</v>
-      </c>
-      <c r="AL79" s="68"/>
-    </row>
-    <row r="80" spans="2:90" s="2" customFormat="1" ht="14.25" customHeight="1">
+        <v>622.65</v>
+      </c>
+      <c r="AJ79" s="68"/>
+    </row>
+    <row r="80" spans="2:88" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="B80" s="2" t="s">
         <v>571</v>
       </c>
       <c r="F80" s="2">
-        <f t="shared" ref="F80:K80" si="137">SUM(F67:F79)</f>
+        <f t="shared" ref="F80:K80" si="125">SUM(F67:F79)</f>
         <v>46121</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="137"/>
+        <f t="shared" si="125"/>
         <v>47872</v>
       </c>
       <c r="H80" s="2">
-        <f t="shared" si="137"/>
+        <f t="shared" si="125"/>
         <v>48050</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="137"/>
+        <f t="shared" si="125"/>
         <v>50853</v>
       </c>
       <c r="J80" s="2">
-        <f t="shared" si="137"/>
+        <f t="shared" si="125"/>
         <v>51485</v>
       </c>
       <c r="K80" s="2">
-        <f t="shared" si="137"/>
+        <f t="shared" si="125"/>
         <v>51559</v>
       </c>
       <c r="L80" s="2">
@@ -17103,33 +17100,35 @@
       <c r="P80" s="34"/>
       <c r="Q80" s="34"/>
       <c r="R80" s="34"/>
-      <c r="Z80" s="2">
-        <f t="shared" si="135"/>
+      <c r="X80" s="2">
+        <f>F80</f>
         <v>46121</v>
       </c>
-      <c r="AA80" s="2">
-        <f t="shared" si="136"/>
+      <c r="Y80" s="2">
+        <f>J80</f>
         <v>51485</v>
       </c>
-      <c r="AB80" s="34"/>
+      <c r="Z80" s="34"/>
+      <c r="AA80" s="53"/>
+      <c r="AB80" s="53"/>
       <c r="AC80" s="53"/>
       <c r="AD80" s="53"/>
       <c r="AE80" s="53"/>
       <c r="AF80" s="53"/>
       <c r="AG80" s="53"/>
-      <c r="AH80" s="53"/>
-      <c r="AI80" s="53"/>
-      <c r="AJ80" s="48" t="s">
+      <c r="AH80" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="AK80" s="49">
-        <f>AK78/AK79-1</f>
-        <v>-4.7064948562157705E-3</v>
-      </c>
-      <c r="AL80" s="56" t="str">
-        <f>IF(AK80&gt;0,"Upside","Downside")</f>
-        <v>Downside</v>
-      </c>
+      <c r="AI80" s="49">
+        <f>AI78/AI79-1</f>
+        <v>7.7357766288510321E-2</v>
+      </c>
+      <c r="AJ80" s="56" t="str">
+        <f>IF(AI80&gt;0,"Upside","Downside")</f>
+        <v>Upside</v>
+      </c>
+      <c r="AK80" s="34"/>
+      <c r="AL80" s="34"/>
       <c r="AM80" s="34"/>
       <c r="AN80" s="34"/>
       <c r="AO80" s="34"/>
@@ -17180,24 +17179,22 @@
       <c r="CH80" s="34"/>
       <c r="CI80" s="34"/>
       <c r="CJ80" s="34"/>
-      <c r="CK80" s="34"/>
-      <c r="CL80" s="34"/>
-    </row>
-    <row r="81" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="81" spans="2:88" ht="14.25" customHeight="1">
+      <c r="AA81" s="53"/>
+      <c r="AB81" s="53"/>
       <c r="AC81" s="53"/>
       <c r="AD81" s="53"/>
       <c r="AE81" s="53"/>
       <c r="AF81" s="53"/>
       <c r="AG81" s="53"/>
-      <c r="AH81" s="53"/>
-      <c r="AI81" s="53"/>
-      <c r="AJ81" s="75" t="str" cm="1">
-        <f t="array" ref="AJ81">_xlfn.IFS(AK80&gt;=25%,"Strong Buy",AK80&gt;=10.00001%,"Buy",AND(AK80&lt;=10%,AK80&gt;=-4.9999%),"Hold",AND(AK80&lt;=-5%,AK80&gt;=-14.999999%),"Sell",AK80&lt;=-15%,"Strong Sell")</f>
+      <c r="AH81" s="75" t="str" cm="1">
+        <f t="array" ref="AH81">_xlfn.IFS(AI80&gt;=25%,"Strong Buy",AI80&gt;=10.00001%,"Buy",AND(AI80&lt;=10%,AI80&gt;=-4.9999%),"Hold",AND(AI80&lt;=-5%,AI80&gt;=-14.999999%),"Sell",AI80&lt;=-15%,"Strong Sell")</f>
         <v>Hold</v>
       </c>
-      <c r="AK81" s="75"/>
-    </row>
-    <row r="82" spans="2:90" ht="14.25" customHeight="1">
+      <c r="AI81" s="75"/>
+    </row>
+    <row r="82" spans="2:88" ht="14.25" customHeight="1">
       <c r="B82" s="1" t="s">
         <v>572</v>
       </c>
@@ -17225,16 +17222,16 @@
       <c r="M82" s="1">
         <v>9543</v>
       </c>
-      <c r="Z82" s="1">
-        <f t="shared" ref="Z82:Z91" si="138">F82</f>
+      <c r="X82" s="1">
+        <f>F82</f>
         <v>7900</v>
       </c>
-      <c r="AA82" s="1">
-        <f t="shared" ref="AA82:AA91" si="139">J82</f>
+      <c r="Y82" s="1">
+        <f>J82</f>
         <v>8602</v>
       </c>
     </row>
-    <row r="83" spans="2:90" ht="14.25" customHeight="1">
+    <row r="83" spans="2:88" ht="14.25" customHeight="1">
       <c r="B83" s="1" t="s">
         <v>573</v>
       </c>
@@ -17266,16 +17263,16 @@
       <c r="M83" s="1">
         <v>20151</v>
       </c>
-      <c r="Z83" s="1">
-        <f t="shared" si="138"/>
+      <c r="X83" s="1">
+        <f>F83</f>
         <v>15606</v>
       </c>
-      <c r="AA83" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y83" s="1">
+        <f>J83</f>
         <v>17587</v>
       </c>
     </row>
-    <row r="84" spans="2:90" ht="14.25" customHeight="1">
+    <row r="84" spans="2:88" ht="14.25" customHeight="1">
       <c r="B84" s="1" t="s">
         <v>574</v>
       </c>
@@ -17303,16 +17300,16 @@
       <c r="M84" s="1">
         <v>5499</v>
       </c>
-      <c r="Z84" s="1">
-        <f t="shared" si="138"/>
+      <c r="X84" s="1">
+        <f>F84</f>
         <v>4352</v>
       </c>
-      <c r="AA84" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y84" s="1">
+        <f>J84</f>
         <v>5496</v>
       </c>
     </row>
-    <row r="85" spans="2:90" ht="14.25" customHeight="1">
+    <row r="85" spans="2:88" ht="14.25" customHeight="1">
       <c r="B85" s="1" t="s">
         <v>581</v>
       </c>
@@ -17340,16 +17337,16 @@
       <c r="M85" s="1">
         <v>80</v>
       </c>
-      <c r="Z85" s="1">
-        <f t="shared" si="138"/>
+      <c r="X85" s="1">
+        <f>F85</f>
         <v>1448</v>
       </c>
-      <c r="AA85" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y85" s="1">
+        <f>J85</f>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:90" ht="14.25" customHeight="1">
+    <row r="86" spans="2:88" ht="14.25" customHeight="1">
       <c r="B86" s="1" t="s">
         <v>569</v>
       </c>
@@ -17377,16 +17374,16 @@
       <c r="M86" s="1">
         <v>820</v>
       </c>
-      <c r="Z86" s="1">
-        <f t="shared" si="138"/>
+      <c r="X86" s="1">
+        <f>F86</f>
         <v>382</v>
       </c>
-      <c r="AA86" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y86" s="1">
+        <f>J86</f>
         <v>827</v>
       </c>
     </row>
-    <row r="87" spans="2:90" ht="14.25" customHeight="1">
+    <row r="87" spans="2:88" ht="14.25" customHeight="1">
       <c r="B87" s="1" t="s">
         <v>575</v>
       </c>
@@ -17414,16 +17411,16 @@
       <c r="M87" s="1">
         <v>3195</v>
       </c>
-      <c r="Z87" s="1">
-        <f t="shared" si="138"/>
+      <c r="X87" s="1">
+        <f>F87</f>
         <v>3273</v>
       </c>
-      <c r="AA87" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y87" s="1">
+        <f>J87</f>
         <v>3264</v>
       </c>
     </row>
-    <row r="88" spans="2:90" ht="14.25" customHeight="1">
+    <row r="88" spans="2:88" ht="14.25" customHeight="1">
       <c r="B88" s="1" t="s">
         <v>576</v>
       </c>
@@ -17451,41 +17448,41 @@
       <c r="M88" s="1">
         <v>5382</v>
       </c>
-      <c r="Z88" s="1">
-        <f t="shared" si="138"/>
+      <c r="X88" s="1">
+        <f>F88</f>
         <v>4780</v>
       </c>
-      <c r="AA88" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y88" s="1">
+        <f>J88</f>
         <v>5116</v>
       </c>
     </row>
-    <row r="89" spans="2:90" s="2" customFormat="1" ht="14.25" customHeight="1">
+    <row r="89" spans="2:88" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="B89" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F89" s="2">
-        <f t="shared" ref="F89:K89" si="140">SUM(F82:F88)</f>
+        <f t="shared" ref="F89:K89" si="126">SUM(F82:F88)</f>
         <v>37741</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" si="126"/>
         <v>37892</v>
       </c>
       <c r="H89" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" si="126"/>
         <v>38003</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" si="126"/>
         <v>40336</v>
       </c>
       <c r="J89" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" si="126"/>
         <v>40892</v>
       </c>
       <c r="K89" s="2">
-        <f t="shared" si="140"/>
+        <f t="shared" si="126"/>
         <v>41887</v>
       </c>
       <c r="L89" s="2">
@@ -17501,14 +17498,16 @@
       <c r="P89" s="34"/>
       <c r="Q89" s="34"/>
       <c r="R89" s="34"/>
-      <c r="Z89" s="2">
-        <f t="shared" si="138"/>
+      <c r="X89" s="2">
+        <f>F89</f>
         <v>37741</v>
       </c>
-      <c r="AA89" s="2">
-        <f t="shared" si="139"/>
+      <c r="Y89" s="2">
+        <f>J89</f>
         <v>40892</v>
       </c>
+      <c r="Z89" s="34"/>
+      <c r="AA89" s="34"/>
       <c r="AB89" s="34"/>
       <c r="AC89" s="34"/>
       <c r="AD89" s="34"/>
@@ -17570,10 +17569,8 @@
       <c r="CH89" s="34"/>
       <c r="CI89" s="34"/>
       <c r="CJ89" s="34"/>
-      <c r="CK89" s="34"/>
-      <c r="CL89" s="34"/>
-    </row>
-    <row r="90" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="90" spans="2:88" ht="14.25" customHeight="1">
       <c r="B90" s="1" t="s">
         <v>578</v>
       </c>
@@ -17601,41 +17598,41 @@
       <c r="M90" s="1">
         <v>9729</v>
       </c>
-      <c r="Z90" s="1">
-        <f t="shared" si="138"/>
+      <c r="X90" s="1">
+        <f>F90</f>
         <v>8380</v>
       </c>
-      <c r="AA90" s="1">
-        <f t="shared" si="139"/>
+      <c r="Y90" s="1">
+        <f>J90</f>
         <v>10593</v>
       </c>
     </row>
-    <row r="91" spans="2:90" s="2" customFormat="1" ht="14.25" customHeight="1">
+    <row r="91" spans="2:88" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="B91" s="2" t="s">
         <v>579</v>
       </c>
       <c r="F91" s="2">
-        <f t="shared" ref="F91:K91" si="141">F89+F90</f>
+        <f t="shared" ref="F91:K91" si="127">F89+F90</f>
         <v>46121</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="127"/>
         <v>47872</v>
       </c>
       <c r="H91" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="127"/>
         <v>48052</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="127"/>
         <v>50853</v>
       </c>
       <c r="J91" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="127"/>
         <v>51485</v>
       </c>
       <c r="K91" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="127"/>
         <v>51559</v>
       </c>
       <c r="L91" s="2">
@@ -17651,14 +17648,16 @@
       <c r="P91" s="34"/>
       <c r="Q91" s="34"/>
       <c r="R91" s="34"/>
-      <c r="Z91" s="2">
-        <f t="shared" si="138"/>
+      <c r="X91" s="2">
+        <f>F91</f>
         <v>46121</v>
       </c>
-      <c r="AA91" s="2">
-        <f t="shared" si="139"/>
+      <c r="Y91" s="2">
+        <f>J91</f>
         <v>51485</v>
       </c>
+      <c r="Z91" s="34"/>
+      <c r="AA91" s="34"/>
       <c r="AB91" s="34"/>
       <c r="AC91" s="34"/>
       <c r="AD91" s="34"/>
@@ -17720,36 +17719,34 @@
       <c r="CH91" s="34"/>
       <c r="CI91" s="34"/>
       <c r="CJ91" s="34"/>
-      <c r="CK91" s="34"/>
-      <c r="CL91" s="34"/>
-    </row>
-    <row r="92" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="93" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="92" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="93" spans="2:88" ht="14.25" customHeight="1">
       <c r="B93" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F93" s="39">
-        <f t="shared" ref="F93:K93" si="142">SUM(F67:F72)/SUM(F82:F85)</f>
+        <f t="shared" ref="F93:K93" si="128">SUM(F67:F72)/SUM(F82:F85)</f>
         <v>0.9359175595441207</v>
       </c>
       <c r="G93" s="39">
-        <f t="shared" si="142"/>
+        <f t="shared" si="128"/>
         <v>0.99078465916790892</v>
       </c>
       <c r="H93" s="39">
-        <f t="shared" si="142"/>
+        <f t="shared" si="128"/>
         <v>1.0569757440220195</v>
       </c>
       <c r="I93" s="39">
-        <f t="shared" si="142"/>
+        <f t="shared" si="128"/>
         <v>1.0610911885245902</v>
       </c>
       <c r="J93" s="39">
-        <f t="shared" si="142"/>
+        <f t="shared" si="128"/>
         <v>1.0779233075587817</v>
       </c>
       <c r="K93" s="39">
-        <f t="shared" si="142"/>
+        <f t="shared" si="128"/>
         <v>1.038560411311054</v>
       </c>
       <c r="L93" s="39">
@@ -17760,41 +17757,41 @@
         <f>SUM(M67:M72)/SUM(M82:M85)</f>
         <v>1.0284920477418988</v>
       </c>
-      <c r="Z93" s="39">
-        <f t="shared" ref="Z93:AA93" si="143">SUM(Z67:Z72)/SUM(Z82:Z85)</f>
+      <c r="X93" s="39">
+        <f t="shared" ref="X93:Y93" si="129">SUM(X67:X72)/SUM(X82:X85)</f>
         <v>0.9359175595441207</v>
       </c>
-      <c r="AA93" s="39">
-        <f t="shared" si="143"/>
+      <c r="Y93" s="39">
+        <f t="shared" si="129"/>
         <v>1.0779233075587817</v>
       </c>
     </row>
-    <row r="94" spans="2:90" ht="14.25" customHeight="1">
+    <row r="94" spans="2:88" ht="14.25" customHeight="1">
       <c r="B94" s="1" t="s">
         <v>74</v>
       </c>
       <c r="F94" s="39">
-        <f t="shared" ref="F94:K94" si="144">(SUM(F67:F72)-F69)/SUM(F82:F85)</f>
+        <f t="shared" ref="F94:K94" si="130">(SUM(F67:F72)-F69)/SUM(F82:F85)</f>
         <v>0.65430287313178193</v>
       </c>
       <c r="G94" s="39">
-        <f t="shared" si="144"/>
+        <f t="shared" si="130"/>
         <v>0.69064236346388397</v>
       </c>
       <c r="H94" s="39">
-        <f t="shared" si="144"/>
+        <f t="shared" si="130"/>
         <v>0.73542060897987271</v>
       </c>
       <c r="I94" s="39">
-        <f t="shared" si="144"/>
+        <f t="shared" si="130"/>
         <v>0.76085425204918034</v>
       </c>
       <c r="J94" s="39">
-        <f t="shared" si="144"/>
+        <f t="shared" si="130"/>
         <v>0.80691178791226137</v>
       </c>
       <c r="K94" s="39">
-        <f t="shared" si="144"/>
+        <f t="shared" si="130"/>
         <v>0.75835475578406175</v>
       </c>
       <c r="L94" s="39">
@@ -17805,41 +17802,41 @@
         <f>(SUM(M67:M72)-M69)/SUM(M82:M85)</f>
         <v>0.74408187565560058</v>
       </c>
-      <c r="Z94" s="39">
-        <f t="shared" ref="Z94:AA94" si="145">(SUM(Z67:Z72)-Z69)/SUM(Z82:Z85)</f>
+      <c r="X94" s="39">
+        <f t="shared" ref="X94:Y94" si="131">(SUM(X67:X72)-X69)/SUM(X82:X85)</f>
         <v>0.65430287313178193</v>
       </c>
-      <c r="AA94" s="39">
-        <f t="shared" si="145"/>
+      <c r="Y94" s="39">
+        <f t="shared" si="131"/>
         <v>0.80691178791226137</v>
       </c>
     </row>
-    <row r="95" spans="2:90" ht="14.25" customHeight="1">
+    <row r="95" spans="2:88" ht="14.25" customHeight="1">
       <c r="B95" s="1" t="s">
         <v>75</v>
       </c>
       <c r="F95" s="39">
-        <f t="shared" ref="F95:K95" si="146">F67/SUM(F82:F85)</f>
+        <f t="shared" ref="F95:K95" si="132">F67/SUM(F82:F85)</f>
         <v>5.2924315839759775E-2</v>
       </c>
       <c r="G95" s="39">
-        <f t="shared" si="146"/>
+        <f t="shared" si="132"/>
         <v>0.11027917061932511</v>
       </c>
       <c r="H95" s="39">
-        <f t="shared" si="146"/>
+        <f t="shared" si="132"/>
         <v>0.19883020815413727</v>
       </c>
       <c r="I95" s="39">
-        <f t="shared" si="146"/>
+        <f t="shared" si="132"/>
         <v>0.23677638319672131</v>
       </c>
       <c r="J95" s="39">
-        <f t="shared" si="146"/>
+        <f t="shared" si="132"/>
         <v>0.25895534164431117</v>
       </c>
       <c r="K95" s="39">
-        <f t="shared" si="146"/>
+        <f t="shared" si="132"/>
         <v>0.24810258293548781</v>
       </c>
       <c r="L95" s="39">
@@ -17850,41 +17847,41 @@
         <f>M67/SUM(M82:M85)</f>
         <v>0.22524310379043461</v>
       </c>
-      <c r="Z95" s="39">
-        <f t="shared" ref="Z95:AA95" si="147">Z67/SUM(Z82:Z85)</f>
+      <c r="X95" s="39">
+        <f t="shared" ref="X95:Y95" si="133">X67/SUM(X82:X85)</f>
         <v>5.2924315839759775E-2</v>
       </c>
-      <c r="AA95" s="39">
-        <f t="shared" si="147"/>
+      <c r="Y95" s="39">
+        <f t="shared" si="133"/>
         <v>0.25895534164431117</v>
       </c>
     </row>
-    <row r="96" spans="2:90" ht="14.25" customHeight="1">
+    <row r="96" spans="2:88" ht="14.25" customHeight="1">
       <c r="B96" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F96" s="39">
-        <f t="shared" ref="F96:K96" si="148">F41/F91</f>
+        <f t="shared" ref="F96:K96" si="134">F41/F91</f>
         <v>0.21781834739055961</v>
       </c>
       <c r="G96" s="39">
-        <f t="shared" si="148"/>
+        <f t="shared" si="134"/>
         <v>0.15163352272727273</v>
       </c>
       <c r="H96" s="39">
-        <f t="shared" si="148"/>
+        <f t="shared" si="134"/>
         <v>0.17073170731707318</v>
       </c>
       <c r="I96" s="39">
-        <f t="shared" si="148"/>
+        <f t="shared" si="134"/>
         <v>0.17526989558138162</v>
       </c>
       <c r="J96" s="39">
-        <f t="shared" si="148"/>
+        <f t="shared" si="134"/>
         <v>0.2050888608332524</v>
       </c>
       <c r="K96" s="39">
-        <f t="shared" si="148"/>
+        <f t="shared" si="134"/>
         <v>0.15578269555266783</v>
       </c>
       <c r="L96" s="39">
@@ -17895,41 +17892,41 @@
         <f>M41/M91</f>
         <v>0.18325704516627145</v>
       </c>
-      <c r="Z96" s="39">
-        <f t="shared" ref="Z96:AA96" si="149">Z41/Z91</f>
+      <c r="X96" s="39">
+        <f t="shared" ref="X96:Y96" si="135">X41/X91</f>
         <v>0.72069122525530671</v>
       </c>
-      <c r="AA96" s="39">
-        <f t="shared" si="149"/>
+      <c r="Y96" s="39">
+        <f t="shared" si="135"/>
         <v>0.67854714965523943</v>
       </c>
     </row>
-    <row r="97" spans="2:90" ht="14.25" customHeight="1">
+    <row r="97" spans="2:88" ht="14.25" customHeight="1">
       <c r="B97" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F97" s="39">
-        <f t="shared" ref="F97:K97" si="150">F69/AVERAGE(SUM(C44:F44))</f>
+        <f t="shared" ref="F97:K97" si="136">F69/AVERAGE(SUM(C44:F44))</f>
         <v>0.29038387108124275</v>
       </c>
       <c r="G97" s="39">
-        <f t="shared" si="150"/>
+        <f t="shared" si="136"/>
         <v>0.30946309428162222</v>
       </c>
       <c r="H97" s="39">
-        <f t="shared" si="150"/>
+        <f t="shared" si="136"/>
         <v>0.33192456582732538</v>
       </c>
       <c r="I97" s="39">
-        <f t="shared" si="150"/>
+        <f t="shared" si="136"/>
         <v>0.32604311543810849</v>
       </c>
       <c r="J97" s="39">
-        <f t="shared" si="150"/>
+        <f t="shared" si="136"/>
         <v>0.29764298093587521</v>
       </c>
       <c r="K97" s="39">
-        <f t="shared" si="150"/>
+        <f t="shared" si="136"/>
         <v>0.31245947513906425</v>
       </c>
       <c r="L97" s="39">
@@ -17940,41 +17937,41 @@
         <f>M69/AVERAGE(SUM(J44:M44))</f>
         <v>0.3307289091088913</v>
       </c>
-      <c r="Z97" s="39">
-        <f t="shared" ref="Z97:AA97" si="151">Z69/AVERAGE(SUM(W42:Z43))</f>
+      <c r="X97" s="39">
+        <f t="shared" ref="X97:Y97" si="137">X69/AVERAGE(SUM(U42:X43))</f>
         <v>0.15110679824962925</v>
       </c>
-      <c r="AA97" s="39">
-        <f t="shared" si="151"/>
+      <c r="Y97" s="39">
+        <f t="shared" si="137"/>
         <v>0.10287898211269124</v>
       </c>
     </row>
-    <row r="98" spans="2:90" ht="14.25" customHeight="1">
+    <row r="98" spans="2:88" ht="14.25" customHeight="1">
       <c r="B98" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F98" s="63">
-        <f t="shared" ref="F98:K98" si="152">F54/F91</f>
+        <f t="shared" ref="F98:K98" si="138">F54/F91</f>
         <v>4.2713731272088634E-3</v>
       </c>
       <c r="G98" s="63">
-        <f t="shared" si="152"/>
+        <f t="shared" si="138"/>
         <v>-2.7155748663101604E-3</v>
       </c>
       <c r="H98" s="63">
-        <f t="shared" si="152"/>
+        <f t="shared" si="138"/>
         <v>2.6929160076583702E-2</v>
       </c>
       <c r="I98" s="63">
-        <f t="shared" si="152"/>
+        <f t="shared" si="138"/>
         <v>-1.8877942304288832E-3</v>
       </c>
       <c r="J98" s="63">
-        <f t="shared" si="152"/>
+        <f t="shared" si="138"/>
         <v>9.4202194814023508E-3</v>
       </c>
       <c r="K98" s="63">
-        <f t="shared" si="152"/>
+        <f t="shared" si="138"/>
         <v>4.9263950037820746E-3</v>
       </c>
       <c r="L98" s="63">
@@ -17985,41 +17982,41 @@
         <f>M54/M91</f>
         <v>8.32735895880439E-3</v>
       </c>
-      <c r="Z98" s="63">
-        <f t="shared" ref="Z98:AA98" si="153">Z54/Z91</f>
+      <c r="X98" s="63">
+        <f t="shared" ref="X98:Y98" si="139">X54/X91</f>
         <v>-9.4967585264846815E-3</v>
       </c>
-      <c r="AA98" s="63">
-        <f t="shared" si="153"/>
+      <c r="Y98" s="63">
+        <f t="shared" si="139"/>
         <v>3.0164125473438864E-2</v>
       </c>
     </row>
-    <row r="99" spans="2:90" ht="14.25" customHeight="1">
+    <row r="99" spans="2:88" ht="14.25" customHeight="1">
       <c r="B99" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F99" s="63">
-        <f t="shared" ref="F99:K99" si="154">F54/F90</f>
+        <f t="shared" ref="F99:K99" si="140">F54/F90</f>
         <v>2.3508353221957042E-2</v>
       </c>
       <c r="G99" s="63">
-        <f t="shared" si="154"/>
+        <f t="shared" si="140"/>
         <v>-1.3026052104208416E-2</v>
       </c>
       <c r="H99" s="63">
-        <f t="shared" si="154"/>
+        <f t="shared" si="140"/>
         <v>0.12876903174445217</v>
       </c>
       <c r="I99" s="63">
-        <f t="shared" si="154"/>
+        <f t="shared" si="140"/>
         <v>-9.1280783493391648E-3</v>
       </c>
       <c r="J99" s="63">
-        <f t="shared" si="154"/>
+        <f t="shared" si="140"/>
         <v>4.5784952327008403E-2</v>
       </c>
       <c r="K99" s="63">
-        <f t="shared" si="154"/>
+        <f t="shared" si="140"/>
         <v>2.6261373035566585E-2</v>
       </c>
       <c r="L99" s="63">
@@ -18030,54 +18027,54 @@
         <f>M54/M90</f>
         <v>4.6561825470243602E-2</v>
       </c>
-      <c r="Z99" s="63">
-        <f t="shared" ref="Z99:AA99" si="155">Z54/Z90</f>
+      <c r="X99" s="63">
+        <f t="shared" ref="X99:Y99" si="141">X54/X90</f>
         <v>-5.2267303102625298E-2</v>
       </c>
-      <c r="AA99" s="63">
-        <f t="shared" si="155"/>
+      <c r="Y99" s="63">
+        <f t="shared" si="141"/>
         <v>0.14660624940998773</v>
       </c>
     </row>
-    <row r="100" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="101" spans="2:90" ht="14.25" customHeight="1">
+    <row r="100" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="101" spans="2:88" ht="14.25" customHeight="1">
       <c r="B101" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C101" s="1">
-        <f t="shared" ref="C101:K101" si="156">C54</f>
+        <f t="shared" ref="C101:K101" si="142">C54</f>
         <v>-315</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>-150</v>
       </c>
       <c r="E101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>-170</v>
       </c>
       <c r="F101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>197</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>-130</v>
       </c>
       <c r="H101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>1294</v>
       </c>
       <c r="I101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>-96</v>
       </c>
       <c r="J101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>485</v>
       </c>
       <c r="K101" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="142"/>
         <v>254</v>
       </c>
       <c r="L101" s="1">
@@ -18088,16 +18085,16 @@
         <f>M54</f>
         <v>453</v>
       </c>
-      <c r="Z101" s="1">
-        <f t="shared" ref="Z101:Z104" si="157">SUM(C101:F101)</f>
+      <c r="X101" s="1">
+        <f t="shared" ref="X101:X104" si="143">SUM(C101:F101)</f>
         <v>-438</v>
       </c>
-      <c r="AA101" s="1">
-        <f t="shared" ref="AA101:AA104" si="158">SUM(G101:J101)</f>
+      <c r="Y101" s="1">
+        <f t="shared" ref="Y101:Y104" si="144">SUM(G101:J101)</f>
         <v>1553</v>
       </c>
     </row>
-    <row r="102" spans="2:90" s="2" customFormat="1" ht="14.25" customHeight="1">
+    <row r="102" spans="2:88" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="B102" s="2" t="s">
         <v>81</v>
       </c>
@@ -18140,14 +18137,16 @@
       <c r="P102" s="34"/>
       <c r="Q102" s="34"/>
       <c r="R102" s="34"/>
-      <c r="Z102" s="2">
-        <f t="shared" si="157"/>
+      <c r="X102" s="2">
+        <f t="shared" si="143"/>
         <v>1188</v>
       </c>
-      <c r="AA102" s="2">
-        <f t="shared" si="158"/>
+      <c r="Y102" s="2">
+        <f t="shared" si="144"/>
         <v>2583</v>
       </c>
+      <c r="Z102" s="34"/>
+      <c r="AA102" s="34"/>
       <c r="AB102" s="34"/>
       <c r="AC102" s="34"/>
       <c r="AD102" s="34"/>
@@ -18209,10 +18208,8 @@
       <c r="CH102" s="34"/>
       <c r="CI102" s="34"/>
       <c r="CJ102" s="34"/>
-      <c r="CK102" s="34"/>
-      <c r="CL102" s="34"/>
-    </row>
-    <row r="103" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="103" spans="2:88" ht="14.25" customHeight="1">
       <c r="B103" s="1" t="s">
         <v>82</v>
       </c>
@@ -18249,16 +18246,16 @@
       <c r="M103" s="1">
         <v>-247</v>
       </c>
-      <c r="Z103" s="1">
-        <f t="shared" si="157"/>
+      <c r="X103" s="1">
+        <f t="shared" si="143"/>
         <v>-744</v>
       </c>
-      <c r="AA103" s="1">
-        <f t="shared" si="158"/>
+      <c r="Y103" s="1">
+        <f t="shared" si="144"/>
         <v>-883</v>
       </c>
     </row>
-    <row r="104" spans="2:90" s="2" customFormat="1" ht="14.25" customHeight="1">
+    <row r="104" spans="2:88" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="B104" s="2" t="s">
         <v>83</v>
       </c>
@@ -18267,43 +18264,43 @@
         <v>-814</v>
       </c>
       <c r="D104" s="2">
-        <f t="shared" ref="D104:L104" si="159">D102+D103</f>
+        <f t="shared" ref="D104:L104" si="145">D102+D103</f>
         <v>-447</v>
       </c>
       <c r="E104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>51</v>
       </c>
       <c r="F104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>1654</v>
       </c>
       <c r="G104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>-661</v>
       </c>
       <c r="H104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>825</v>
       </c>
       <c r="I104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>964</v>
       </c>
       <c r="J104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>572</v>
       </c>
       <c r="K104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>974</v>
       </c>
       <c r="L104" s="2">
-        <f t="shared" si="159"/>
+        <f t="shared" si="145"/>
         <v>194</v>
       </c>
       <c r="M104" s="2">
-        <f t="shared" ref="M104" si="160">M102+M103</f>
+        <f t="shared" ref="M104" si="146">M102+M103</f>
         <v>734</v>
       </c>
       <c r="N104" s="34"/>
@@ -18311,14 +18308,16 @@
       <c r="P104" s="34"/>
       <c r="Q104" s="34"/>
       <c r="R104" s="34"/>
-      <c r="Z104" s="2">
-        <f t="shared" si="157"/>
+      <c r="X104" s="2">
+        <f t="shared" si="143"/>
         <v>444</v>
       </c>
-      <c r="AA104" s="2">
-        <f t="shared" si="158"/>
+      <c r="Y104" s="2">
+        <f t="shared" si="144"/>
         <v>1700</v>
       </c>
+      <c r="Z104" s="34"/>
+      <c r="AA104" s="34"/>
       <c r="AB104" s="34"/>
       <c r="AC104" s="34"/>
       <c r="AD104" s="34"/>
@@ -18380,47 +18379,45 @@
       <c r="CH104" s="34"/>
       <c r="CI104" s="34"/>
       <c r="CJ104" s="34"/>
-      <c r="CK104" s="34"/>
-      <c r="CL104" s="34"/>
-    </row>
-    <row r="105" spans="2:90" ht="14.25" customHeight="1">
+    </row>
+    <row r="105" spans="2:88" ht="14.25" customHeight="1">
       <c r="B105" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C105" s="1">
-        <f t="shared" ref="C105:K105" si="161">C55</f>
+        <f t="shared" ref="C105:K105" si="147">C55</f>
         <v>274</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>274</v>
       </c>
       <c r="E105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>274</v>
       </c>
       <c r="F105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>274</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>274</v>
       </c>
       <c r="H105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>274</v>
       </c>
       <c r="I105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>275</v>
       </c>
       <c r="J105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>275</v>
       </c>
       <c r="K105" s="1">
-        <f t="shared" si="161"/>
+        <f t="shared" si="147"/>
         <v>275</v>
       </c>
       <c r="L105" s="1">
@@ -18431,16 +18428,16 @@
         <f>M55</f>
         <v>272</v>
       </c>
-      <c r="Z105" s="1">
-        <f>Z55</f>
+      <c r="X105" s="1">
+        <f>X55</f>
         <v>274</v>
       </c>
-      <c r="AA105" s="1">
-        <f>AA55</f>
+      <c r="Y105" s="1">
+        <f>Y55</f>
         <v>275</v>
       </c>
     </row>
-    <row r="106" spans="2:90" ht="14.25" customHeight="1">
+    <row r="106" spans="2:88" ht="14.25" customHeight="1">
       <c r="B106" s="1" t="s">
         <v>85</v>
       </c>
@@ -18449,68 +18446,68 @@
         <v>-2.9708029197080292</v>
       </c>
       <c r="D106" s="39">
-        <f t="shared" ref="D106:L106" si="162">D104/D105</f>
+        <f t="shared" ref="D106:L106" si="148">D104/D105</f>
         <v>-1.6313868613138687</v>
       </c>
       <c r="E106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>0.18613138686131386</v>
       </c>
       <c r="F106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>6.0364963503649633</v>
       </c>
       <c r="G106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>-2.4124087591240877</v>
       </c>
       <c r="H106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>3.0109489051094891</v>
       </c>
       <c r="I106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>3.5054545454545454</v>
       </c>
       <c r="J106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>2.08</v>
       </c>
       <c r="K106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>3.541818181818182</v>
       </c>
       <c r="L106" s="39">
-        <f t="shared" si="162"/>
+        <f t="shared" si="148"/>
         <v>0.71323529411764708</v>
       </c>
       <c r="M106" s="39">
-        <f t="shared" ref="M106" si="163">M104/M105</f>
+        <f t="shared" ref="M106" si="149">M104/M105</f>
         <v>2.6985294117647061</v>
       </c>
-      <c r="Z106" s="39">
-        <f>Z104/Z105</f>
+      <c r="X106" s="39">
+        <f>X104/X105</f>
         <v>1.6204379562043796</v>
       </c>
-      <c r="AA106" s="39">
-        <f>AA104/AA105</f>
+      <c r="Y106" s="39">
+        <f>Y104/Y105</f>
         <v>6.1818181818181817</v>
       </c>
     </row>
-    <row r="107" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="108" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="109" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="110" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="111" spans="2:90" ht="14.25" customHeight="1"/>
-    <row r="112" spans="2:90" ht="14.25" customHeight="1"/>
+    <row r="107" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="108" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="109" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="110" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="111" spans="2:88" ht="14.25" customHeight="1"/>
+    <row r="112" spans="2:88" ht="14.25" customHeight="1"/>
     <row r="113" ht="14.25" customHeight="1"/>
     <row r="114" ht="14.25" customHeight="1"/>
     <row r="115" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="AJ81:AK81"/>
+    <mergeCell ref="AH81:AI81"/>
   </mergeCells>
-  <conditionalFormatting sqref="AJ81">
+  <conditionalFormatting sqref="AH81">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -18522,26 +18519,26 @@
       </colorScale>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Strong Sell">
-      <formula>NOT(ISERROR(SEARCH("Strong Sell",AJ81)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Strong Sell",AH81)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Sell">
-      <formula>NOT(ISERROR(SEARCH("Sell",AJ81)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Sell",AH81)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Hold">
-      <formula>NOT(ISERROR(SEARCH("Hold",AJ81)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Hold",AH81)))</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="1" priority="5" operator="beginsWith" text="Buy">
-      <formula>LEFT(AJ81,LEN("Buy"))="Buy"</formula>
+      <formula>LEFT(AH81,LEN("Buy"))="Buy"</formula>
     </cfRule>
     <cfRule type="beginsWith" dxfId="0" priority="6" operator="beginsWith" text="Strong">
-      <formula>LEFT(AJ81,LEN("Strong"))="Strong"</formula>
+      <formula>LEFT(AH81,LEN("Strong"))="Strong"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="AC10:AL10 AA11:AB11 AB12 AA13:AB13 AA12 K8:L10 G8:J10 G30:M33 C35:M37 Y35:AA37 Z30:AA33" evalError="1"/>
-    <ignoredError sqref="AA4:AA5 Y6 F93:M99 Z102:AA106" formulaRange="1"/>
-    <ignoredError sqref="C19:J19 C23:J23 I20 I21 I22 C27:J27 I24 I25 I26 I28 E28:F28 Z44" formula="1"/>
+    <ignoredError sqref="AA10:AJ10 Y11:Z11 Z12 Y13:Z13 Y12 K8:L10 G8:J10 G30:M33 C35:M37 W35:Y37 X30:Y33" evalError="1"/>
+    <ignoredError sqref="Y4:Y5 W6 F93:M99 X102:Y106" formulaRange="1"/>
+    <ignoredError sqref="C19:J19 C23:J23 I20 I21 I22 C27:J27 I24 I25 I26 I28 E28:F28 X44" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/GEV_Model.xlsx
+++ b/GEV_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Industrials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C56978-8308-4E34-A25F-46AA1D03A8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B4E14D-E3F4-4702-9C6A-7B9B61DD0A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
